--- a/tame_output/ON/bt/strategyON_20240719.xlsx
+++ b/tame_output/ON/bt/strategyON_20240719.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>22.9%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>110.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,27 +992,27 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.3%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.1%</t>
+          <t>-66.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.5%</t>
+          <t>455.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-503.2%</t>
+          <t>-499.1%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-145.9%</t>
+          <t>-144.2%</t>
         </is>
       </c>
     </row>
@@ -1237,17 +1237,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,57 +1298,57 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.8%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-136.7%</t>
+          <t>-135.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-122.4%</t>
+          <t>-118.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.3%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.2%</t>
+          <t>-18.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-15.6%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.303024231880388</v>
+        <v>-3.430052028835363</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.148075267107371</v>
+        <v>1.09726414832538</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6673167825078846</v>
+        <v>0.5402889855529089</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.870031453678004</v>
+        <v>2.793814775505019</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.347413701209815</v>
+        <v>-3.474441498164791</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.132192955300201</v>
+        <v>1.08138183651821</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.622927313178457</v>
+        <v>0.4958995162234813</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.845271248004948</v>
+        <v>2.769054569831963</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.234742482973565</v>
+        <v>-3.361770279928541</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.172337151106424</v>
+        <v>1.121526032324433</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.6085707344597315</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.907949687458421</v>
+        <v>2.831733009285436</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.122365481790892</v>
+        <v>-3.249393278745868</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.22277924741016</v>
+        <v>1.17196812862817</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.6085707344597315</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.913440983289088</v>
+        <v>2.837224305116103</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.150145879692245</v>
+        <v>-3.277173676647221</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.223164290018158</v>
+        <v>1.172353171236167</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.707818133513354</v>
+        <v>0.5807903365583784</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.908269946316816</v>
+        <v>2.83205326814383</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.233147160717524</v>
+        <v>-3.3601749576725</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.028319497608699</v>
+        <v>0.9775083788267089</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.5622194520312047</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.735483135601165</v>
+        <v>2.659266457428179</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.341761239160856</v>
+        <v>-3.468789036115831</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.105023526950573</v>
+        <v>1.054212408168582</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.5622194520312047</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.85563279632037</v>
+        <v>2.779416118147385</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.306352200912713</v>
+        <v>-3.433379997867688</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.133700168352153</v>
+        <v>1.082889049570162</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.5622194520312047</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.870145822422693</v>
+        <v>2.793929144249708</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.267968538354562</v>
+        <v>-3.394996335309537</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.146473074717782</v>
+        <v>1.095661955935791</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7276309115443315</v>
+        <v>0.6006031145893559</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.890595461299953</v>
+        <v>2.814378783126967</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.090852208319395</v>
+        <v>-3.217880005274371</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.21404863557715</v>
+        <v>1.16323751679516</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7276309115443315</v>
+        <v>0.6006031145893559</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.887324490145255</v>
+        <v>2.811107811972269</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.135944453152941</v>
+        <v>-3.262972250107917</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.196695129405645</v>
+        <v>1.145884010623655</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6657348683749417</v>
+        <v>0.5387070714199661</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.850870256005534</v>
+        <v>2.774653577832549</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.956569031914174</v>
+        <v>-3.083596828869149</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.262232273207566</v>
+        <v>1.211421154425576</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8225116265456603</v>
+        <v>0.6954838295906848</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.93872328621438</v>
+        <v>2.862506608041394</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.00158324543478</v>
+        <v>-3.128611042389756</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.225034043130914</v>
+        <v>1.174222924348923</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7921627312310557</v>
+        <v>0.6651349342760802</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.901321404357207</v>
+        <v>2.825104726184221</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.268587755707215</v>
+        <v>-3.395615552662191</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.123923801360885</v>
+        <v>1.073112682578895</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5977996931881071</v>
+        <v>0.4707718962331316</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.790395143870383</v>
+        <v>2.714178465697398</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.369785537144388</v>
+        <v>-3.496813334099364</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.082648610682517</v>
+        <v>1.031837491900527</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.529390879642788</v>
+        <v>0.4023630826878124</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.748553777639693</v>
+        <v>2.672337099466707</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.363274570530075</v>
+        <v>-3.490302367485051</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.082852958882559</v>
+        <v>1.032041840100569</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.529390879642788</v>
+        <v>0.4023630826878124</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.74615373919401</v>
+        <v>2.669937061021024</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.344236442822778</v>
+        <v>-3.471264239777754</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.086992929173723</v>
+        <v>1.036181810391733</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4712072683115934</v>
+        <v>0.3441794713566179</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.707768291603538</v>
+        <v>2.631551613430553</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.375363073973396</v>
+        <v>-3.502390870928372</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.252124145652157</v>
+        <v>1.201313026870166</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4712072683115934</v>
+        <v>0.3441794713566179</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.885350160542218</v>
+        <v>2.809133482369233</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.389229835307313</v>
+        <v>-3.516257632262289</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.247410770104723</v>
+        <v>1.196599651322733</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4333493515777705</v>
+        <v>0.3063215546227949</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.863468739488058</v>
+        <v>2.787252061315073</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.344425663767383</v>
+        <v>-3.471453460722359</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.271340969117621</v>
+        <v>1.220529850335631</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4333493515777705</v>
+        <v>0.3063215546227949</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.869477269884984</v>
+        <v>2.793260591711999</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.196682693532381</v>
+        <v>-3.323710490487357</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.228388378488821</v>
+        <v>1.177577259706831</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6011567088126537</v>
+        <v>0.4741289118576781</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.868111905503114</v>
+        <v>2.791895227330128</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.298697376063602</v>
+        <v>-3.425725173018578</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.190376127007814</v>
+        <v>1.139565008225824</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6011567088126537</v>
+        <v>0.4741289118576781</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.870905527034595</v>
+        <v>2.794688848861609</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.292544670010818</v>
+        <v>-3.419572466965794</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.193499557820586</v>
+        <v>1.142688439038596</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.607309414865438</v>
+        <v>0.4802816179104624</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.875259499057924</v>
+        <v>2.799042820884938</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.309353968161319</v>
+        <v>-3.436381765116295</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.185856315300496</v>
+        <v>1.135045196518505</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5905001167149364</v>
+        <v>0.4634723197599607</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.864254396907733</v>
+        <v>2.788037718734747</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.247055969385197</v>
+        <v>-3.374083766340173</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.277111068607765</v>
+        <v>1.226299949825775</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5905001167149364</v>
+        <v>0.4634723197599607</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.930589950704554</v>
+        <v>2.854373272531568</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.04526577172004</v>
+        <v>-3.172293568675015</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.160119149387956</v>
+        <v>1.109308030605965</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7885183088840908</v>
+        <v>0.6614905119291151</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.851692867720173</v>
+        <v>2.775476189547188</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.880452768641192</v>
+        <v>-3.007480565596168</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.29633458294167</v>
+        <v>1.245523464159679</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9533313119629377</v>
+        <v>0.8263035150079621</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.020870901889657</v>
+        <v>2.944654223716671</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.978193313266167</v>
+        <v>-3.105221110221143</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.271866101207723</v>
+        <v>1.221054982425733</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9374420338299576</v>
+        <v>0.8104142368749818</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.025965071125913</v>
+        <v>2.949748392952927</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.154531073389096</v>
+        <v>-3.281558870344072</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.199866977983223</v>
+        <v>1.149055859201233</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7611042737070282</v>
+        <v>0.6340764767520524</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.918698395876826</v>
+        <v>2.842481717703841</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.078109026957169</v>
+        <v>-3.205136823912145</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.228927414595923</v>
+        <v>1.178116295813932</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7611042737070282</v>
+        <v>0.6340764767520524</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.917190013916755</v>
+        <v>2.84097333574377</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.033735895318601</v>
+        <v>-3.160763692273576</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.246539534686786</v>
+        <v>1.195728415904796</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8054774053455968</v>
+        <v>0.678449608390621</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.943676760335332</v>
+        <v>2.867460082162347</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.910901674431433</v>
+        <v>-3.037929471386409</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.290067017180244</v>
+        <v>1.239255898398254</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8054774053455968</v>
+        <v>0.678449608390621</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.938070554473923</v>
+        <v>2.861853876300937</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.863245943870377</v>
+        <v>-2.990273740825353</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.315511066432471</v>
+        <v>1.264699947650481</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8531331359066524</v>
+        <v>0.7261053389516766</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.973045749838361</v>
+        <v>2.896829071665375</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.762727785371623</v>
+        <v>-2.889755582326599</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.360610703206698</v>
+        <v>1.309799584424707</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.953651294405407</v>
+        <v>0.8266234974504312</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.038249018312338</v>
+        <v>2.962032340139353</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.823394375774012</v>
+        <v>-2.950422172728988</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.323098739521614</v>
+        <v>1.272287620739624</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8719529776868733</v>
+        <v>0.7449251807318975</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.975984700757091</v>
+        <v>2.899768022584105</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.778555974165614</v>
+        <v>-2.90558377112059</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.345131802775602</v>
+        <v>1.294320683993612</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8764964106317428</v>
+        <v>0.749468613676767</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.982808463134641</v>
+        <v>2.906591784961655</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.879314609922612</v>
+        <v>-3.006342406877588</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.30898928810388</v>
+        <v>1.25817816932189</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7876708419047374</v>
+        <v>0.6606430449497616</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.933674061529516</v>
+        <v>2.85745738335653</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.835111772836712</v>
+        <v>-2.962139569791688</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.332550025466078</v>
+        <v>1.281738906684088</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8318736789906378</v>
+        <v>0.704845882035662</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.966075366308893</v>
+        <v>2.889858688135907</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.872090800500155</v>
+        <v>-2.999118597455131</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.316168414869948</v>
+        <v>1.265357296087958</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8688475807819683</v>
+        <v>0.7418197838269925</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.986669707852939</v>
+        <v>2.910453029679953</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.713799382960883</v>
+        <v>-2.840827179915859</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.430732747068697</v>
+        <v>1.379921628286706</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8688475807819683</v>
+        <v>0.7418197838269925</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.037917473035979</v>
+        <v>2.961700794862993</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.506157379326407</v>
+        <v>-2.633185176281382</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.51223025311674</v>
+        <v>1.46141913433475</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.076489584416445</v>
+        <v>0.9494617874614687</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.160943379810917</v>
+        <v>3.084726701637932</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.455125286603879</v>
+        <v>-2.582153083558854</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.527591318444022</v>
+        <v>1.476780199662031</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.127521677138973</v>
+        <v>1.000493880183997</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.186510863682704</v>
+        <v>3.110294185509718</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.389901105476673</v>
+        <v>-2.516928902431649</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.570868394987609</v>
+        <v>1.520057276205619</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.192745858266178</v>
+        <v>1.065718061311202</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.242832776451732</v>
+        <v>3.166616098278747</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.352474085405539</v>
+        <v>-2.479501882360515</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.581800175315343</v>
+        <v>1.530989056533352</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.19799739629536</v>
+        <v>1.070969599340384</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.241944671568522</v>
+        <v>3.165727993395536</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.372585741440247</v>
+        <v>-2.499613538395223</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.5750123052327</v>
+        <v>1.524201186450709</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.209024741292779</v>
+        <v>1.081996944337803</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.249817870898214</v>
+        <v>3.173601192725228</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.318840927013043</v>
+        <v>-2.445868723968018</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.757068002024792</v>
+        <v>1.706256883242802</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.219088050733241</v>
+        <v>1.092060253778265</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.416413627583702</v>
+        <v>3.340196949410716</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.24405866598803</v>
+        <v>-2.371086462943006</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.907093815652614</v>
+        <v>1.856282696870624</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.293870311758254</v>
+        <v>1.166842514803278</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.581395893416526</v>
+        <v>3.505179215243541</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.217974581724222</v>
+        <v>-2.345002378679198</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.909235425371997</v>
+        <v>1.858424306590007</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.293870311758254</v>
+        <v>1.166842514803278</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.573103869430385</v>
+        <v>3.4968871912574</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.139843400875275</v>
+        <v>-2.266871197830251</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.938681093295355</v>
+        <v>1.887869974513365</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.368047122641939</v>
+        <v>1.241019325686962</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.615803151544376</v>
+        <v>3.53958647337139</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.130950939481992</v>
+        <v>-2.257978736436968</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.959792483579459</v>
+        <v>1.908981364797469</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.368047122641939</v>
+        <v>1.241019325686962</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.633357557271167</v>
+        <v>3.557140879098181</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.29942705645187</v>
+        <v>-2.426454853406846</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.884257084196092</v>
+        <v>1.833445965414102</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.340099286925358</v>
+        <v>1.213071489970382</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.608443903245802</v>
+        <v>3.532227225072817</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.601627527590287</v>
+        <v>-1.728655324545262</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.144646592928587</v>
+        <v>2.093835474146597</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.269751227554947</v>
+        <v>1.142723430599971</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.547504764811418</v>
+        <v>3.471288086638432</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.578906423907134</v>
+        <v>-1.70593422086211</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.144399056898753</v>
+        <v>2.093587938116763</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.269751227554947</v>
+        <v>1.142723430599971</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.538168787308322</v>
+        <v>3.461952109135337</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.57718138061709</v>
+        <v>-1.704209177572066</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.303995200065939</v>
+        <v>2.253184081283949</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.271476270844991</v>
+        <v>1.144448473890015</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.698109939133518</v>
+        <v>3.621893260960532</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.731962387395346</v>
+        <v>-1.858990184350322</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.279160619848284</v>
+        <v>2.228349501066294</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.238108596790515</v>
+        <v>1.111080799835539</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.715167157194479</v>
+        <v>3.638950479021493</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.724907697180172</v>
+        <v>-1.851935494135148</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.278657851923898</v>
+        <v>2.227846733141909</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.245163287005689</v>
+        <v>1.118135490050712</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.716075327313128</v>
+        <v>3.639858649140142</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.697956472853684</v>
+        <v>-1.82498426980866</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.299444495299236</v>
+        <v>2.248633376517245</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.260043633033408</v>
+        <v>1.133015836078431</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.735009688574501</v>
+        <v>3.658793010401515</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.83390948091</v>
+        <v>-1.960937277864976</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.429166424221669</v>
+        <v>2.378355305439678</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.260043633033408</v>
+        <v>1.133015836078431</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.919112820719461</v>
+        <v>3.842896142546475</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.856317598714872</v>
+        <v>-1.983345395669848</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.412319872002713</v>
+        <v>2.361508753220723</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.260043633033408</v>
+        <v>1.133015836078431</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.911229515622454</v>
+        <v>3.835012837449468</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.004323366194272</v>
+        <v>-2.131351163149247</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.355171564560591</v>
+        <v>2.3043604457786</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.173316624169866</v>
+        <v>1.04628882721489</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.861247309853967</v>
+        <v>3.785030631680981</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.013764292082802</v>
+        <v>-2.140792089037777</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.407648911927026</v>
+        <v>2.356837793145035</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.295743741713258</v>
+        <v>1.168715944758282</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.990957298101849</v>
+        <v>3.914740619928863</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.066037899418443</v>
+        <v>-2.193065696373419</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.38963056353807</v>
+        <v>2.33881944475608</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.243470134377616</v>
+        <v>1.11644233742264</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.962484228245764</v>
+        <v>3.886267550072779</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.142367877019349</v>
+        <v>-2.269395673974325</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.357210385391483</v>
+        <v>2.306399266609493</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.243470134377616</v>
+        <v>1.11644233742264</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.96059604113954</v>
+        <v>3.884379362966554</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.25412482963465</v>
+        <v>-2.381152626589626</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.307327833948225</v>
+        <v>2.256516715166235</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.131713181762315</v>
+        <v>1.004685384807339</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.888362099173222</v>
+        <v>3.812145421000236</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.252283810576399</v>
+        <v>-2.379311607531374</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.306498251781678</v>
+        <v>2.255687132999687</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.132981408433784</v>
+        <v>1.005953611478807</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.887557045386255</v>
+        <v>3.811340367213269</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.384585102673952</v>
+        <v>-2.511612899628928</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.266651141808575</v>
+        <v>2.215840023026585</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.132981408433784</v>
+        <v>1.005953611478807</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.900630452252174</v>
+        <v>3.824413774079188</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.386146745488812</v>
+        <v>-2.513174542443788</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.266026484682631</v>
+        <v>2.215215365900641</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.132981408433784</v>
+        <v>1.005953611478807</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.900630452252174</v>
+        <v>3.824413774079188</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.414047532598285</v>
+        <v>-2.541075329553261</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.253390210965844</v>
+        <v>2.202579092183854</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.098384484290849</v>
+        <v>0.9713566873358727</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.878396338893415</v>
+        <v>3.802179660720429</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.536573635301179</v>
+        <v>-2.663601432256155</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.201144213861885</v>
+        <v>2.150333095079895</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9758583815879551</v>
+        <v>0.8488305846329788</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.801645121248877</v>
+        <v>3.725428443075891</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.556634956577685</v>
+        <v>-2.683662753532662</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.259825644941786</v>
+        <v>2.209014526159796</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9557970603114481</v>
+        <v>0.8287692633564718</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.856314288073476</v>
+        <v>3.780097609900491</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.813355774572509</v>
+        <v>-2.940383571527486</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.297449036745704</v>
+        <v>2.246637917963713</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8473824861676332</v>
+        <v>0.720354689212657</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.931577262589035</v>
+        <v>3.855360584416049</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.96734219234865</v>
+        <v>-3.094369989303626</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.304834738780888</v>
+        <v>2.254023619998897</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8473824861676332</v>
+        <v>0.720354689212657</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.000557531734675</v>
+        <v>3.924340853561689</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.916820288520984</v>
+        <v>-3.04384808547596</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.311094702432075</v>
+        <v>2.260283583650084</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8473824861676332</v>
+        <v>0.720354689212657</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.986608733854795</v>
+        <v>3.91039205568181</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.169295442528708</v>
+        <v>-3.296323239483685</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.221975129884399</v>
+        <v>2.171164011102408</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8473824861676332</v>
+        <v>0.720354689212657</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.998479222910209</v>
+        <v>3.922262544737224</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.438768244450416</v>
+        <v>-3.565796041405393</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.11539654363466</v>
+        <v>2.064585424852669</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8473824861676332</v>
+        <v>0.720354689212657</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.999689757429153</v>
+        <v>3.923473079256167</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.596312316179858</v>
+        <v>-3.723340113134834</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.056500657170204</v>
+        <v>2.005689538388213</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7804806810273588</v>
+        <v>0.6534528840723826</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.96367041657231</v>
+        <v>3.887453738399324</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.725162866881904</v>
+        <v>-3.85219066383688</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.000038289625575</v>
+        <v>1.949227170843584</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7394872721766372</v>
+        <v>0.612459475221661</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.934152223998066</v>
+        <v>3.857935545825081</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.842130559520795</v>
+        <v>-3.969158356475771</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.115455269269063</v>
+        <v>2.064644150487072</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7394872721766372</v>
+        <v>0.612459475221661</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.09635628069711</v>
+        <v>4.020139602524125</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.926848501741749</v>
+        <v>-4.053876298696725</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.076414730344496</v>
+        <v>2.025603611562505</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6543712432485909</v>
+        <v>0.5273434462936146</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.040133301304097</v>
+        <v>3.963916623131111</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.008783320010632</v>
+        <v>-4.135811116965608</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.053870220605433</v>
+        <v>2.003059101823442</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6444364976615107</v>
+        <v>0.5174087007065344</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.04440187152034</v>
+        <v>3.968185193347354</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.95504514661037</v>
+        <v>-4.082072943565346</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.08429112842144</v>
+        <v>2.03348000963945</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6981746710617728</v>
+        <v>0.5711468741067965</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.0855704140164</v>
+        <v>4.009353735843414</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.845038863133148</v>
+        <v>-3.972066660088124</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.120446529056505</v>
+        <v>2.069635410274514</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.721379242979048</v>
+        <v>0.5943514460240718</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.09164604441094</v>
+        <v>4.015429366237955</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.701979287392223</v>
+        <v>-3.829007084347199</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.181920370074849</v>
+        <v>2.131109251292858</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7293926695690273</v>
+        <v>0.602364872614051</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.100704111086902</v>
+        <v>4.024487432913916</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.737891417382802</v>
+        <v>3.509404106257511</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.415875952251657</v>
+        <v>-3.375132820057849</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.303622587013611</v>
+        <v>2.319919839891134</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.015496004709592</v>
+        <v>1.0562391369034</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.279626995053777</v>
+        <v>4.304072874370062</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240719.xlsx
+++ b/tame_output/ON/bt/strategyON_20240719.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.8%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.5%</t>
+          <t>-67.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.6%</t>
+          <t>455.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-499.1%</t>
+          <t>-514.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-144.2%</t>
+          <t>-150.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,52 +1298,52 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-118.4%</t>
+          <t>-133.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>82.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,27 +1481,27 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.1%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-15.6%</t>
+          <t>-24.8%</t>
         </is>
       </c>
     </row>
@@ -48218,16 +48218,16 @@
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.375132820057849</v>
+        <v>-3.527560358875362</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.319919839891134</v>
+        <v>2.258948824364129</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.0562391369034</v>
+        <v>0.9038115980858883</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.304072874370062</v>
+        <v>4.212616351079554</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240719.xlsx
+++ b/tame_output/ON/bt/strategyON_20240719.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>50.5%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>110.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.4%</t>
+          <t>122.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-650.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,17 +992,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-48.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.2%</t>
+          <t>460.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-514.3%</t>
+          <t>-507.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-260.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-36.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-20.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.3%</t>
+          <t>-147.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-269.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.0%</t>
+          <t>-135.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-133.6%</t>
+          <t>-127.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.6%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-162.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-20.8%</t>
         </is>
       </c>
     </row>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1878921395489951</v>
+        <v>0.1267217999702719</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.197370603618793</v>
+        <v>3.172902467787304</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.568940374610322</v>
+        <v>1.507770035031599</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.063934396879136</v>
+        <v>4.027232193131902</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.04923935230080001</v>
+        <v>-0.1104096918795232</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.137459091376417</v>
+        <v>3.112990955544928</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.568940374610322</v>
+        <v>1.507770035031599</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.098875481376678</v>
+        <v>4.062173277629444</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.04420176157321348</v>
+        <v>-0.1053721011519367</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.13805156785279</v>
+        <v>3.1135834320213</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.62458483087664</v>
+        <v>1.563414491297916</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.130839595321806</v>
+        <v>4.094137391574573</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.3013957962812702</v>
+        <v>-0.3625661358599934</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.013920335593304</v>
+        <v>2.989452199761815</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.367390796168583</v>
+        <v>1.30622045658986</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.95526955612071</v>
+        <v>3.918567352373476</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3671631863306823</v>
+        <v>-0.4283335259094055</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.988630988704009</v>
+        <v>2.96416285287252</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.367390796168583</v>
+        <v>1.30622045658986</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.95628716525118</v>
+        <v>3.919584961503945</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5724078633879268</v>
+        <v>-0.6335782029666501</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.897161149868867</v>
+        <v>2.872693014037378</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.367390796168583</v>
+        <v>1.30622045658986</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.946915197238935</v>
+        <v>3.910212993491701</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6541797638156785</v>
+        <v>-0.7153501033944019</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.854535115653005</v>
+        <v>2.830066979821515</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.394426369574719</v>
+        <v>1.333256029995996</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.953219267237856</v>
+        <v>3.916517063490621</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7213888716875563</v>
+        <v>-0.7825592112662796</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.832416789337956</v>
+        <v>2.807948653506467</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.394426369574719</v>
+        <v>1.333256029995996</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.957984584071558</v>
+        <v>3.921282380324324</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7099996350327549</v>
+        <v>-0.7711699746114782</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.834797280119117</v>
+        <v>2.810329144287627</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.405815606229521</v>
+        <v>1.344645266650798</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.962642922183679</v>
+        <v>3.925940718436445</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.127753658579592</v>
+        <v>-1.188923998158315</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.665622562205445</v>
+        <v>2.641154426373956</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9880615826826838</v>
+        <v>0.9268912431039608</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.70991739956064</v>
+        <v>3.673215195813406</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.417885325185023</v>
+        <v>-1.479055664763747</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.549436112162195</v>
+        <v>2.524967976330705</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.012143377422864</v>
+        <v>0.9509730378441407</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.72423269300367</v>
+        <v>3.687530489256436</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.625889383538101</v>
+        <v>-1.687059723116824</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.471126633374889</v>
+        <v>2.4466584975434</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.012143377422864</v>
+        <v>0.9509730378441407</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.729124837557595</v>
+        <v>3.692422633810361</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.688067794699071</v>
+        <v>-1.749238134277794</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.441336725248489</v>
+        <v>2.416868589417</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9499649662618935</v>
+        <v>0.8887946266831706</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.686899247199001</v>
+        <v>3.650197043451767</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.054136521843724</v>
+        <v>-2.115306861422447</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.287993533697077</v>
+        <v>2.263525397865588</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5838962391172409</v>
+        <v>0.5227258995385179</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.460342310218659</v>
+        <v>3.423640106471424</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.262627303295408</v>
+        <v>-2.323797642874131</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.224935510855171</v>
+        <v>2.200467375023682</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3754054576655564</v>
+        <v>0.3142351180868335</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.355586131086416</v>
+        <v>3.318883927339182</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.50982848806063</v>
+        <v>-2.570998827639353</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.134153787357651</v>
+        <v>2.109685651526162</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3955588111643689</v>
+        <v>0.3343884715856459</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.375776893594272</v>
+        <v>3.339074689847038</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.002213516084727</v>
+        <v>-3.063383855663449</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.938306168191745</v>
+        <v>1.913838032360256</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.1579965564384508</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.081452268823546</v>
+        <v>3.044750065076312</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.387393907014799</v>
+        <v>-3.448564246593522</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.782776550632579</v>
+        <v>1.75830841480109</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.1579965564384508</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.079994807636409</v>
+        <v>3.043292603889176</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.637264587029381</v>
+        <v>-3.698434926608103</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.684597402081363</v>
+        <v>1.660129266249873</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.06056349702926461</v>
+        <v>-0.1217338366079876</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.103521562989304</v>
+        <v>3.06681935924207</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.843776363916402</v>
+        <v>-3.904946703495125</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.598098749982812</v>
+        <v>1.573630614151323</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.3282456134950091</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.975720555513349</v>
+        <v>2.939018351766115</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.163120438996904</v>
+        <v>-4.224290778575627</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.472134046650871</v>
+        <v>1.447665910819381</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.3282456134950091</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.977493482213608</v>
+        <v>2.940791278466374</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.594926232146691</v>
+        <v>-4.656096571725414</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.28574461685836</v>
+        <v>1.261276481026871</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4034927703575531</v>
+        <v>-0.4646631099362761</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.881975871816252</v>
+        <v>2.845273668069018</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-4.890790565857967</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.155683658375941</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3971565031282979</v>
+        <v>-0.4583268427070209</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>2.837360203408662</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-5.226453213088419</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>1.019999191139725</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.5262578281959257</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>2.795182203771284</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.241727203712568</v>
+        <v>-5.302897543291291</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.020377155124307</v>
+        <v>0.9959090192928177</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3846419795235408</v>
+        <v>-0.4458123191022638</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>2.849937069461723</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.668024925930037</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.8491125812431504</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.7421231034012763</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.671405113888147</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-6.076613703110716</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.6844386143856376</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.150711880581955</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.425013391594499</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.129203775554858</v>
+        <v>-6.190374115133581</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6585880178794419</v>
+        <v>0.6341198820479526</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.150711880581955</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.42019882406596</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.545595649841855</v>
+        <v>-6.606765989420579</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4900253187735202</v>
+        <v>0.4655571829420309</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.150711880581955</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.418192874674837</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-6.851037390147648</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.378107313319882</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.150711880581955</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.428451565343516</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.995118069805685</v>
+        <v>-7.056288409384408</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3165746066023623</v>
+        <v>0.2921064707708729</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.150711880581955</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.424551130489212</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.043320887048029</v>
+        <v>-7.104491226626752</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2956983997604259</v>
+        <v>0.2712302639289366</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.150711880581955</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.422956050544212</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.339982228858227</v>
+        <v>-7.40115256843695</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1808128389655548</v>
+        <v>0.1563447031340659</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.219455016315833</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.385489145033093</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.526701937167529</v>
+        <v>-7.587872276746253</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1020986511074309</v>
+        <v>0.07763051527594156</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.219455016315833</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.38146284049869</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.909703325910161</v>
+        <v>-7.970873665488884</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.05120400571120598</v>
+        <v>-0.07567214154269486</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.219455016315833</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.381360739177106</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.914189771111549</v>
+        <v>-7.975360110690272</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05042706782033113</v>
+        <v>-0.07489520365182045</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.223941461517222</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.381240388027703</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.273720093615552</v>
+        <v>-8.334890433194275</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1888888935238819</v>
+        <v>-0.2133570293553713</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.223941461517222</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.386590691325753</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.324069157069774</v>
+        <v>-8.385239496648497</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2011124989483934</v>
+        <v>-0.2255806347798823</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.274290524971444</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.364297273210398</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.42168843449117</v>
+        <v>-8.482858774069893</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2371184592951829</v>
+        <v>-0.2615865951266723</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.371909802392841</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.308767457379328</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.475759933999528</v>
+        <v>-8.536930273578252</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.255853502776954</v>
+        <v>-0.2803216386084433</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.4259813019012</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.279218113995885</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.680018109329392</v>
+        <v>-8.741188448908115</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3320435757902573</v>
+        <v>-0.3565117116217467</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.553620246515189</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.208147944346134</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.713670947837866</v>
+        <v>-8.774841287416589</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3410221567092107</v>
+        <v>-0.3654902925407</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.654033614432227</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.152382478080348</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.640201116170417</v>
+        <v>-8.70137145574914</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.29626252254881</v>
+        <v>-0.3207306583802989</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.580563782764778</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.211836078574238</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.81532553355696</v>
+        <v>-8.876495873135683</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3517570687559104</v>
+        <v>-0.3762252045873997</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.755688200151322</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.121316648889828</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.04977762757145</v>
+        <v>-9.110947967150173</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4527570712633024</v>
+        <v>-0.4772252070947913</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.755688200151322</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.114097483988232</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.215322698176619</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5011791544478572</v>
+        <v>-0.5256472902793461</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.860062931177768</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.044800454598389</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.268108853776946</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5211778268494314</v>
+        <v>-0.5456459626809207</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.955738417760165</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>1.988510952487506</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.394145647145235</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5688988155676324</v>
+        <v>-0.5933669513991218</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.930486794950423</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.006355654802467</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.337073875249304</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5420797711228591</v>
+        <v>-0.5665479069543484</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.930486794950423</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.010345990488867</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.478745716973425</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6002237347112489</v>
+        <v>-0.6246918705427382</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.930486794950423</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.008870763590126</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.42915487254859</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5653339867764431</v>
+        <v>-0.5898021226079324</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.880895950525589</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.053678680409898</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.280236538076734</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5188177866343833</v>
+        <v>-0.5432859224658726</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.849646359790416</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.059377301204319</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-9.054391385357324</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.4433687883419002</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.807719684203252</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.094112379592826</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-8.929812729019732</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.3923981812508042</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.807719684203252</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.095251524148885</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-8.982708017064018</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.4109225223064112</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.802764338114806</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.100858505964061</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-8.910574841776137</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.3763355479526225</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.802764338114806</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.106592210202697</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-8.83920844916649</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.3575262533026287</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.731397945505158</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.139674783374621</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.745749415181265</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.3300261210214464</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.731397945505158</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.129791302061713</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.478507614312868</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.2249639611734611</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.731397945505158</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.127956741562339</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.380600575636377</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.1861014606763258</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.663412195644602</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.168447876505212</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.356647034660419</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.1758515381404488</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.639458654668644</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.18348850723628</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-8.092587096337622</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.08348787897308219</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.375398716345848</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.328664154068206</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.385507472832784</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.1965569367685522</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.375398716345848</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.325877120407905</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.345323174466594</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.2129742800028698</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.335214417979657</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.350331323315461</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.181923303527231</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.2777010495993717</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.171814547040294</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.447738067099835</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-6.948442081297633</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.3790179673290632</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.9383333248106958</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.595751229275447</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-6.798775690290118</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.4359923134191104</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.8454298335681598</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.648601113708009</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.666500216659231</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.4842699896184919</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.7131543599372732</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.723333884633568</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.510761884099489</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.5493803833300253</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5574160273775316</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.81959194485705</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.261762085415908</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.6618866440271165</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.5574160273775316</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.832498286080709</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.367352075189013</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.4916747185186559</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.663006017150636</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.641168362617627</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.38608697730761</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.5327250995483035</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.6686020268107673</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.686355098698635</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.23814693590001</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.4720221934231756</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.6482811109022097</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.578668725555602</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.185177413646022</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5089641519027821</v>
+        <v>0.4844960160712928</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5953115886482209</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.601736452654517</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.141629006875331</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5194229025159651</v>
+        <v>0.4949547666844758</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5953115886482209</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.594775840559424</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.04709546081784</v>
+        <v>-6.108265800396563</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5472305394886159</v>
+        <v>0.5227624036571266</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5953115886482209</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.609238194940567</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.938836323695318</v>
+        <v>-6.000006663274041</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5850663147968196</v>
+        <v>0.5605981789653303</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5953115886482209</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.603770315399762</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.815545188878187</v>
+        <v>-5.87671552845691</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6318808627342487</v>
+        <v>0.6074127269027594</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.4720204538310904</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.675243090300617</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.794395989974744</v>
+        <v>-5.855566329553467</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6480415205329515</v>
+        <v>0.6235733847014622</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.450871254927647</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.695633587880008</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.550630547991299</v>
+        <v>-5.611800887570022</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7413284056733795</v>
+        <v>0.7168602698418907</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.450871254927647</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.691414296227059</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.448867727714005</v>
+        <v>-5.510038067292728</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7841578477043138</v>
+        <v>0.7596897118728245</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4376521865352183</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.701470051182532</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.19901733376493</v>
+        <v>-5.260187673343653</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8768400802676455</v>
+        <v>0.8523719444361566</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4376521865352183</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.694212126166234</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.023125241297498</v>
+        <v>-5.084295580876221</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9507960407752671</v>
+        <v>0.9263279049437778</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4376521865352183</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.697811249686883</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.851678778275034</v>
+        <v>-4.912849117853757</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.032702132038806</v>
+        <v>1.008233996207317</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.2662057235127552</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.814006633554914</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.777389212536695</v>
+        <v>-4.838559552115418</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.061438435950439</v>
+        <v>1.03697030011895</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.1919161577744159</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.857600850614215</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.713753470302761</v>
+        <v>-4.774923809881484</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.09158753389833</v>
+        <v>1.067119398066841</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1282804155404814</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.900477097008893</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.663497050555564</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.117352496412494</v>
+        <v>1.092884360581004</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1282804155404814</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.881671355792689</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.36189621417198</v>
+        <v>-4.423066553750703</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.215267771759315</v>
+        <v>1.190799635927826</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1121500812643789</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>3.027672730500482</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.289653646000786</v>
+        <v>-4.350823985579509</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.248094112862613</v>
+        <v>1.223625977031124</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1121500812643789</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>3.031602044335302</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.236655323719398</v>
+        <v>-4.297825663298121</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.269972025692508</v>
+        <v>1.245503889861019</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1674863402663178</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>3.065482383653806</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.127850438239671</v>
+        <v>-4.189020777818394</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.310492051104393</v>
+        <v>1.286023915272903</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1674863402663178</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>3.062480454873799</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.90782964020266</v>
+        <v>-3.968999979781383</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.400079407329811</v>
+        <v>1.375611271498322</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.308706185334298</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.148791398925201</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.774961951139382</v>
+        <v>-3.836132290718105</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.469120665756946</v>
+        <v>1.444652529925456</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.308706185334298</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.164685581727025</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.654788867774883</v>
+        <v>-3.715959207353606</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518335743543047</v>
+        <v>1.493867607711558</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.4288792686987969</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.237935276186026</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.510116722675146</v>
+        <v>-3.571287062253869</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586292704144382</v>
+        <v>1.561824568312893</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.5735514137985344</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.334826665807308</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.569991550032838</v>
+        <v>-3.631161889611561</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.548380264602731</v>
+        <v>1.523912128771242</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.5136765864408422</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.284939260794119</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.450171319122</v>
+        <v>-3.511341658700724</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.611597526201274</v>
+        <v>1.587129390369785</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.5136765864408422</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.300228430028327</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.452641025583806</v>
+        <v>-3.51381136516253</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.518253842938994</v>
+        <v>1.493785707107504</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.5112068799790361</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.206390805473685</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.521011211907816</v>
+        <v>-3.582181551486539</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.410167629894691</v>
+        <v>1.385699494063202</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5204825790152511</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.131218086380716</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.534799264754863</v>
+        <v>-3.595969604333586</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.395089117387764</v>
+        <v>1.370620981556274</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5204825790152511</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.121654795012607</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.565792424083568</v>
+        <v>-3.626962763662291</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.207401418696668</v>
+        <v>1.182933282865179</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5204825790152511</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.983066563800228</v>
+        <v>2.946364360052994</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.390318164291099</v>
+        <v>-3.451488503869822</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.282158354605444</v>
+        <v>1.257690218773954</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5204825790152511</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.987633795792016</v>
+        <v>2.950931592044781</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.501254416932348</v>
+        <v>-3.562424756511071</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.213525882310151</v>
+        <v>1.189057746478662</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5204825790152511</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.963375824553223</v>
+        <v>2.926673620805988</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.467590871460066</v>
+        <v>-3.528761211038789</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.155529613900514</v>
+        <v>1.131061478069025</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.554146124487533</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.912112265238041</v>
+        <v>2.875410061490808</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.407738252256343</v>
+        <v>-3.468908591835066</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.189643048014136</v>
+        <v>1.165174912182646</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.554146124487533</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.922284651670174</v>
+        <v>2.88558244792294</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.321494789229965</v>
+        <v>-3.382665128808688</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.219086703798547</v>
+        <v>1.194618567967058</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.554146124487533</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.917230922244034</v>
+        <v>2.8805287184968</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.366801608628945</v>
+        <v>-3.427971948207668</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.19273975148348</v>
+        <v>1.168271615651991</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.5133359614783022</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.884520599883021</v>
+        <v>2.847818396135787</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.395834713331247</v>
+        <v>-3.45700505290997</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.181678382635661</v>
+        <v>1.157210246804172</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.5133359614783022</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.885072472916123</v>
+        <v>2.848370269168889</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.430052028835363</v>
+        <v>-3.364194571459111</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.09726414832538</v>
+        <v>1.123607131275882</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5402889855529089</v>
+        <v>0.6061464429291615</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.793814775505019</v>
+        <v>2.83332924993077</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.474441498164791</v>
+        <v>-3.408584040788538</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.08138183651821</v>
+        <v>1.107724819468711</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4958995162234813</v>
+        <v>0.5617569735997339</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.769054569831963</v>
+        <v>2.808569044257714</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.361770279928541</v>
+        <v>-3.295912822552288</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.121526032324433</v>
+        <v>1.147869015274934</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6085707344597315</v>
+        <v>0.674428191835984</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.831733009285436</v>
+        <v>2.871247483711187</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.249393278745868</v>
+        <v>-3.183535821369615</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.17196812862817</v>
+        <v>1.198311111578671</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6085707344597315</v>
+        <v>0.674428191835984</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.837224305116103</v>
+        <v>2.876738779541855</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498864</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.277173676647221</v>
+        <v>-3.211316219270969</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.172353171236167</v>
+        <v>1.198696154186668</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5807903365583784</v>
+        <v>0.6466477939346309</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.83205326814383</v>
+        <v>2.871567742569582</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.3601749576725</v>
+        <v>-3.294317500296247</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9775083788267089</v>
+        <v>1.00385136177721</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5622194520312047</v>
+        <v>0.6280769094074572</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.659266457428179</v>
+        <v>2.698780931853931</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.468789036115831</v>
+        <v>-3.402931578739579</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.054212408168582</v>
+        <v>1.080555391119083</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5622194520312047</v>
+        <v>0.6280769094074572</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.779416118147385</v>
+        <v>2.818930592573137</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.433379997867688</v>
+        <v>-3.367522540491436</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.082889049570162</v>
+        <v>1.109232032520663</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5622194520312047</v>
+        <v>0.6280769094074572</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.793929144249708</v>
+        <v>2.83344361867546</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.394996335309537</v>
+        <v>-3.329138877933285</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.095661955935791</v>
+        <v>1.122004938886292</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6006031145893559</v>
+        <v>0.6664605719656084</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.814378783126967</v>
+        <v>2.853893257552719</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.217880005274371</v>
+        <v>-3.152022547898119</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.16323751679516</v>
+        <v>1.189580499745661</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6006031145893559</v>
+        <v>0.6664605719656084</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.811107811972269</v>
+        <v>2.850622286398021</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.262972250107917</v>
+        <v>-3.197114792731664</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.145884010623655</v>
+        <v>1.172226993574156</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5387070714199661</v>
+        <v>0.6045645287962186</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.774653577832549</v>
+        <v>2.8141680522583</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.083596828869149</v>
+        <v>-3.017739371492897</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.211421154425576</v>
+        <v>1.237764137376077</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6954838295906848</v>
+        <v>0.7613412869669373</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.862506608041394</v>
+        <v>2.902021082467146</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.128611042389756</v>
+        <v>-3.062753585013503</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.174222924348923</v>
+        <v>1.200565907299424</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6651349342760802</v>
+        <v>0.7309923916523327</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.825104726184221</v>
+        <v>2.864619200609972</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.395615552662191</v>
+        <v>-3.329758095285938</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.073112682578895</v>
+        <v>1.099455665529396</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4707718962331316</v>
+        <v>0.536629353609384</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.714178465697398</v>
+        <v>2.753692940123149</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.496813334099364</v>
+        <v>-3.430955876723111</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.031837491900527</v>
+        <v>1.058180474851028</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4023630826878124</v>
+        <v>0.4682205400640648</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.672337099466707</v>
+        <v>2.711851573892459</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.490302367485051</v>
+        <v>-3.424444910108798</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.032041840100569</v>
+        <v>1.05838482305107</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4023630826878124</v>
+        <v>0.4682205400640648</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.669937061021024</v>
+        <v>2.709451535446776</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.471264239777754</v>
+        <v>-3.405406782401501</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.036181810391733</v>
+        <v>1.062524793342234</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3441794713566179</v>
+        <v>0.4100369287328703</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.631551613430553</v>
+        <v>2.671066087856304</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.502390870928372</v>
+        <v>-3.436533413552119</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.201313026870166</v>
+        <v>1.227656009820667</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3441794713566179</v>
+        <v>0.4100369287328703</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.809133482369233</v>
+        <v>2.848647956794985</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.516257632262289</v>
+        <v>-3.450400174886036</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.196599651322733</v>
+        <v>1.222942634273234</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3063215546227949</v>
+        <v>0.3721790119990473</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.787252061315073</v>
+        <v>2.826766535740824</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.471453460722359</v>
+        <v>-3.405596003346107</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.220529850335631</v>
+        <v>1.246872833286132</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3063215546227949</v>
+        <v>0.3721790119990473</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.793260591711999</v>
+        <v>2.83277506613775</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.323710490487357</v>
+        <v>-3.257853033111104</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.177577259706831</v>
+        <v>1.203920242657332</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4741289118576781</v>
+        <v>0.5399863692339305</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.791895227330128</v>
+        <v>2.83140970175588</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.425725173018578</v>
+        <v>-3.359867715642325</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.139565008225824</v>
+        <v>1.165907991176325</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4741289118576781</v>
+        <v>0.5399863692339305</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.794688848861609</v>
+        <v>2.834203323287361</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.419572466965794</v>
+        <v>-3.353715009589541</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.142688439038596</v>
+        <v>1.169031421989097</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4802816179104624</v>
+        <v>0.5461390752867148</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.799042820884938</v>
+        <v>2.838557295310689</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.436381765116295</v>
+        <v>-3.370524307740042</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.135045196518505</v>
+        <v>1.161388179469006</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4634723197599607</v>
+        <v>0.5293297771362131</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.788037718734747</v>
+        <v>2.827552193160499</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.374083766340173</v>
+        <v>-3.308226308963921</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.226299949825775</v>
+        <v>1.252642932776276</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4634723197599607</v>
+        <v>0.5293297771362131</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.854373272531568</v>
+        <v>2.89388774695732</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.172293568675015</v>
+        <v>-3.106436111298763</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.109308030605965</v>
+        <v>1.135651013556466</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6614905119291151</v>
+        <v>0.7273479693053675</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.775476189547188</v>
+        <v>2.81499066397294</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.007480565596168</v>
+        <v>-2.941623108219916</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.245523464159679</v>
+        <v>1.27186644711018</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8263035150079621</v>
+        <v>0.8921609723842144</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.944654223716671</v>
+        <v>2.984168698142423</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.105221110221143</v>
+        <v>-3.03936365284489</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.221054982425733</v>
+        <v>1.247397965376234</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8104142368749818</v>
+        <v>0.8762716942512343</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.949748392952927</v>
+        <v>2.989262867378678</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.281558870344072</v>
+        <v>-3.215701412967819</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.149055859201233</v>
+        <v>1.175398842151734</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6340764767520524</v>
+        <v>0.6999339341283048</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.842481717703841</v>
+        <v>2.881996192129592</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.205136823912145</v>
+        <v>-3.139279366535892</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.178116295813932</v>
+        <v>1.204459278764433</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6340764767520524</v>
+        <v>0.6999339341283048</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.84097333574377</v>
+        <v>2.880487810169521</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.160763692273576</v>
+        <v>-3.094906234897324</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.195728415904796</v>
+        <v>1.222071398855297</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.678449608390621</v>
+        <v>0.7443070657668734</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.867460082162347</v>
+        <v>2.906974556588098</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.037929471386409</v>
+        <v>-2.972072014010156</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.239255898398254</v>
+        <v>1.265598881348755</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.678449608390621</v>
+        <v>0.7443070657668734</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.861853876300937</v>
+        <v>2.901368350726689</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.990273740825353</v>
+        <v>-2.924416283449101</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.264699947650481</v>
+        <v>1.291042930600982</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7261053389516766</v>
+        <v>0.7919627963279291</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.896829071665375</v>
+        <v>2.936343546091127</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.889755582326599</v>
+        <v>-2.823898124950346</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.309799584424707</v>
+        <v>1.336142567375208</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8266234974504312</v>
+        <v>0.8924809548266837</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.962032340139353</v>
+        <v>3.001546814565105</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.950422172728988</v>
+        <v>-2.884564715352735</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.272287620739624</v>
+        <v>1.298630603690125</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7449251807318975</v>
+        <v>0.81078263810815</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.899768022584105</v>
+        <v>2.939282497009856</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.90558377112059</v>
+        <v>-2.839726313744337</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.294320683993612</v>
+        <v>1.320663666944113</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.749468613676767</v>
+        <v>0.8153260710530195</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.906591784961655</v>
+        <v>2.946106259387407</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.006342406877588</v>
+        <v>-2.940484949501335</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.25817816932189</v>
+        <v>1.284521152272391</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6606430449497616</v>
+        <v>0.726500502326014</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.85745738335653</v>
+        <v>2.896971857782281</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.962139569791688</v>
+        <v>-2.896282112415435</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.281738906684088</v>
+        <v>1.308081889634589</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.704845882035662</v>
+        <v>0.7707033394119145</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.889858688135907</v>
+        <v>2.929373162561659</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.999118597455131</v>
+        <v>-2.933261140078878</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.265357296087958</v>
+        <v>1.291700279038459</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7418197838269925</v>
+        <v>0.807677241203245</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.910453029679953</v>
+        <v>2.949967504105705</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284878</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.840827179915859</v>
+        <v>-2.774969722539606</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.379921628286706</v>
+        <v>1.406264611237207</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7418197838269925</v>
+        <v>0.807677241203245</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.961700794862993</v>
+        <v>3.001215269288744</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.633185176281382</v>
+        <v>-2.56732771890513</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.46141913433475</v>
+        <v>1.487762117285251</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9494617874614687</v>
+        <v>1.015319244837721</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.084726701637932</v>
+        <v>3.124241176063683</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475136</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.582153083558854</v>
+        <v>-2.516295626182602</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.476780199662031</v>
+        <v>1.503123182612532</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.000493880183997</v>
+        <v>1.066351337560249</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.110294185509718</v>
+        <v>3.14980865993547</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.516928902431649</v>
+        <v>-2.451071445055396</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.520057276205619</v>
+        <v>1.546400259156119</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.065718061311202</v>
+        <v>1.131575518687455</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.166616098278747</v>
+        <v>3.206130572704498</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.479501882360515</v>
+        <v>-2.413644424984262</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.530989056533352</v>
+        <v>1.557332039483853</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.070969599340384</v>
+        <v>1.136827056716637</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.165727993395536</v>
+        <v>3.205242467821288</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.499613538395223</v>
+        <v>-2.43375608101897</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.524201186450709</v>
+        <v>1.55054416940121</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.081996944337803</v>
+        <v>1.147854401714056</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.173601192725228</v>
+        <v>3.21311566715098</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.445868723968018</v>
+        <v>-2.380011266591766</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.706256883242802</v>
+        <v>1.732599866193303</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.092060253778265</v>
+        <v>1.157917711154518</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.340196949410716</v>
+        <v>3.379711423836468</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.371086462943006</v>
+        <v>-2.305229005566753</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.856282696870624</v>
+        <v>1.882625679821125</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.166842514803278</v>
+        <v>1.23269997217953</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.505179215243541</v>
+        <v>3.544693689669292</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.345002378679198</v>
+        <v>-2.279144921302945</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.858424306590007</v>
+        <v>1.884767289540508</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.166842514803278</v>
+        <v>1.23269997217953</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.4968871912574</v>
+        <v>3.536401665683151</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.266871197830251</v>
+        <v>-2.201013740453998</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.887869974513365</v>
+        <v>1.914212957463866</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.241019325686962</v>
+        <v>1.306876783063215</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.53958647337139</v>
+        <v>3.579100947797142</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.257978736436968</v>
+        <v>-2.192121279060715</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.908981364797469</v>
+        <v>1.93532434774797</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.241019325686962</v>
+        <v>1.306876783063215</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.557140879098181</v>
+        <v>3.596655353523933</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.426454853406846</v>
+        <v>-2.360597396030593</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.833445965414102</v>
+        <v>1.859788948364603</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.213071489970382</v>
+        <v>1.278928947346634</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.532227225072817</v>
+        <v>3.571741699498569</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.728655324545262</v>
+        <v>-1.66279786716901</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.093835474146597</v>
+        <v>2.120178457097098</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.142723430599971</v>
+        <v>1.208580887976224</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.471288086638432</v>
+        <v>3.510802561064184</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.70593422086211</v>
+        <v>-1.640076763485857</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.093587938116763</v>
+        <v>2.119930921067264</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.142723430599971</v>
+        <v>1.208580887976224</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.461952109135337</v>
+        <v>3.501466583561089</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.704209177572066</v>
+        <v>-1.638351720195814</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.253184081283949</v>
+        <v>2.279527064234451</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.144448473890015</v>
+        <v>1.210305931266267</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.621893260960532</v>
+        <v>3.661407735386284</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.858990184350322</v>
+        <v>-1.793132726974069</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.228349501066294</v>
+        <v>2.254692484016795</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.111080799835539</v>
+        <v>1.176938257211791</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.638950479021493</v>
+        <v>3.678464953447245</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.851935494135148</v>
+        <v>-1.786078036758895</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.227846733141909</v>
+        <v>2.25418971609241</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.118135490050712</v>
+        <v>1.183992947426965</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.639858649140142</v>
+        <v>3.679373123565894</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.82498426980866</v>
+        <v>-1.759126812432407</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.248633376517245</v>
+        <v>2.274976359467746</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.133015836078431</v>
+        <v>1.198873293454684</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.658793010401515</v>
+        <v>3.698307484827267</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.960937277864976</v>
+        <v>-1.895079820488723</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.378355305439678</v>
+        <v>2.40469828839018</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.133015836078431</v>
+        <v>1.198873293454684</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.842896142546475</v>
+        <v>3.882410616972227</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.983345395669848</v>
+        <v>-1.917487938293595</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.361508753220723</v>
+        <v>2.387851736171224</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.133015836078431</v>
+        <v>1.198873293454684</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.835012837449468</v>
+        <v>3.87452731187522</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.131351163149247</v>
+        <v>-2.065493705772995</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.3043604457786</v>
+        <v>2.330703428729101</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.04628882721489</v>
+        <v>1.112146284591143</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.785030631680981</v>
+        <v>3.824545106106732</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.140792089037777</v>
+        <v>-2.074934631661525</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.356837793145035</v>
+        <v>2.383180776095537</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.168715944758282</v>
+        <v>1.234573402134534</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.914740619928863</v>
+        <v>3.954255094354615</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.193065696373419</v>
+        <v>-2.127208238997166</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.33881944475608</v>
+        <v>2.365162427706581</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.11644233742264</v>
+        <v>1.182299794798893</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.886267550072779</v>
+        <v>3.925782024498531</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.269395673974325</v>
+        <v>-2.203538216598072</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.306399266609493</v>
+        <v>2.332742249559994</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.11644233742264</v>
+        <v>1.182299794798893</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.884379362966554</v>
+        <v>3.923893837392306</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.381152626589626</v>
+        <v>-2.315295169213373</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.256516715166235</v>
+        <v>2.282859698116736</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.004685384807339</v>
+        <v>1.070542842183592</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.812145421000236</v>
+        <v>3.851659895425987</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.379311607531374</v>
+        <v>-2.313454150155122</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.255687132999687</v>
+        <v>2.282030115950188</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.005953611478807</v>
+        <v>1.07181106885506</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.811340367213269</v>
+        <v>3.850854841639021</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.511612899628928</v>
+        <v>-2.445755442252675</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.215840023026585</v>
+        <v>2.242183005977086</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.005953611478807</v>
+        <v>1.07181106885506</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.824413774079188</v>
+        <v>3.863928248504939</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.513174542443788</v>
+        <v>-2.447317085067535</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.215215365900641</v>
+        <v>2.241558348851142</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.005953611478807</v>
+        <v>1.07181106885506</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.824413774079188</v>
+        <v>3.863928248504939</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.541075329553261</v>
+        <v>-2.475217872177008</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.202579092183854</v>
+        <v>2.228922075134355</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9713566873358727</v>
+        <v>1.037214144712125</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.802179660720429</v>
+        <v>3.84169413514618</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.663601432256155</v>
+        <v>-2.597743974879902</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.150333095079895</v>
+        <v>2.176676078030396</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8488305846329788</v>
+        <v>0.9146880420092316</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.725428443075891</v>
+        <v>3.764942917501643</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.683662753532662</v>
+        <v>-2.617805296156409</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.209014526159796</v>
+        <v>2.235357509110297</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8287692633564718</v>
+        <v>0.8946267207327245</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.780097609900491</v>
+        <v>3.819612084326243</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.940383571527486</v>
+        <v>-2.874526114151233</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.246637917963713</v>
+        <v>2.272980900914214</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.720354689212657</v>
+        <v>0.7862121465889097</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.855360584416049</v>
+        <v>3.894875058841801</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.094369989303626</v>
+        <v>-3.028512531927373</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.254023619998897</v>
+        <v>2.280366602949398</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.720354689212657</v>
+        <v>0.7862121465889097</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.924340853561689</v>
+        <v>3.96385532798744</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.04384808547596</v>
+        <v>-2.977990628099707</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.260283583650084</v>
+        <v>2.286626566600585</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.720354689212657</v>
+        <v>0.7862121465889097</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.91039205568181</v>
+        <v>3.949906530107562</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.296323239483685</v>
+        <v>-3.230465782107432</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.171164011102408</v>
+        <v>2.197506994052909</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.720354689212657</v>
+        <v>0.7862121465889097</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.922262544737224</v>
+        <v>3.961777019162975</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.565796041405393</v>
+        <v>-3.49993858402914</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.064585424852669</v>
+        <v>2.09092840780317</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.720354689212657</v>
+        <v>0.7862121465889097</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.923473079256167</v>
+        <v>3.962987553681919</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.723340113134834</v>
+        <v>-3.657482655758581</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.005689538388213</v>
+        <v>2.032032521338714</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6534528840723826</v>
+        <v>0.7193103414486353</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.887453738399324</v>
+        <v>3.926968212825075</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.85219066383688</v>
+        <v>-3.786333206460628</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.949227170843584</v>
+        <v>1.975570153794085</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.612459475221661</v>
+        <v>0.6783169325979137</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.857935545825081</v>
+        <v>3.897450020250832</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.969158356475771</v>
+        <v>-3.903300899099519</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.064644150487072</v>
+        <v>2.090987133437573</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.612459475221661</v>
+        <v>0.6783169325979137</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.020139602524125</v>
+        <v>4.059654076949877</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.053876298696725</v>
+        <v>-3.988018841320472</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.025603611562505</v>
+        <v>2.051946594513006</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5273434462936146</v>
+        <v>0.5932009036698673</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.963916623131111</v>
+        <v>4.003431097556863</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.135811116965608</v>
+        <v>-4.069953659589356</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.003059101823442</v>
+        <v>2.029402084773944</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5174087007065344</v>
+        <v>0.5832661580827871</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.968185193347354</v>
+        <v>4.007699667773106</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.082072943565346</v>
+        <v>-4.016215486189093</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.03348000963945</v>
+        <v>2.059822992589951</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.5711468741067965</v>
+        <v>0.6370043314830492</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.009353735843414</v>
+        <v>4.048868210269165</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.972066660088124</v>
+        <v>-3.906209202711872</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.069635410274514</v>
+        <v>2.095978393225015</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5943514460240718</v>
+        <v>0.6602089034003245</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.015429366237955</v>
+        <v>4.054943840663706</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.829007084347199</v>
+        <v>-3.763149626970946</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.131109251292858</v>
+        <v>2.15745223424336</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.602364872614051</v>
+        <v>0.6682223299903037</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.024487432913916</v>
+        <v>4.064001907339668</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.509404106257511</v>
+        <v>3.785653626608132</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.527560358875362</v>
+        <v>-3.461702901499109</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.258948824364129</v>
+        <v>2.28529180731463</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.9038115980858883</v>
+        <v>0.969669055462141</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.212616351079554</v>
+        <v>4.252130825505306</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240719.xlsx
+++ b/tame_output/ON/bt/strategyON_20240719.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>22.6%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,32 +844,32 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.1%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.7%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-650.7%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.4%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>-68.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>460.6%</t>
+          <t>455.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-507.7%</t>
+          <t>-514.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-260.7%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-20.4%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-147.7%</t>
+          <t>-150.3%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-269.8%</t>
+          <t>-263.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.6%</t>
+          <t>-135.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-127.0%</t>
+          <t>-133.6%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
+          <t>2024-07-19</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,66 +1447,66 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-162.3%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-24.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-100.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2029"/>
+  <dimension ref="A1:G2030"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511402</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1267217999702719</v>
+        <v>0.1878921395489951</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.172902467787304</v>
+        <v>3.197370603618793</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.507770035031599</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.027232193131902</v>
+        <v>4.063934396879136</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.1104096918795232</v>
+        <v>-0.04923935230080001</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.112990955544928</v>
+        <v>3.137459091376417</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.507770035031599</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.062173277629444</v>
+        <v>4.098875481376678</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.1053721011519367</v>
+        <v>-0.04420176157321348</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.1135834320213</v>
+        <v>3.13805156785279</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.563414491297916</v>
+        <v>1.62458483087664</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.094137391574573</v>
+        <v>4.130839595321806</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.3625661358599934</v>
+        <v>-0.3013957962812702</v>
       </c>
       <c r="E1841" t="n">
-        <v>2.989452199761815</v>
+        <v>3.013920335593304</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.30622045658986</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.918567352373476</v>
+        <v>3.95526955612071</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.4283335259094055</v>
+        <v>-0.3671631863306823</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.96416285287252</v>
+        <v>2.988630988704009</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.30622045658986</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.919584961503945</v>
+        <v>3.95628716525118</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.6335782029666501</v>
+        <v>-0.5724078633879268</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.872693014037378</v>
+        <v>2.897161149868867</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.30622045658986</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.910212993491701</v>
+        <v>3.946915197238935</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.7153501033944019</v>
+        <v>-0.6541797638156785</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.830066979821515</v>
+        <v>2.854535115653005</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.333256029995996</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.916517063490621</v>
+        <v>3.953219267237856</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7825592112662796</v>
+        <v>-0.7213888716875563</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.807948653506467</v>
+        <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.333256029995996</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.921282380324324</v>
+        <v>3.957984584071558</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7711699746114782</v>
+        <v>-0.7099996350327549</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.810329144287627</v>
+        <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.344645266650798</v>
+        <v>1.405815606229521</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.925940718436445</v>
+        <v>3.962642922183679</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.188923998158315</v>
+        <v>-1.127753658579592</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.641154426373956</v>
+        <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9268912431039608</v>
+        <v>0.9880615826826838</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.673215195813406</v>
+        <v>3.70991739956064</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.479055664763747</v>
+        <v>-1.417885325185023</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.524967976330705</v>
+        <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9509730378441407</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.687530489256436</v>
+        <v>3.72423269300367</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.687059723116824</v>
+        <v>-1.625889383538101</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.4466584975434</v>
+        <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9509730378441407</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.692422633810361</v>
+        <v>3.729124837557595</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.749238134277794</v>
+        <v>-1.688067794699071</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.416868589417</v>
+        <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8887946266831706</v>
+        <v>0.9499649662618935</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.650197043451767</v>
+        <v>3.686899247199001</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.115306861422447</v>
+        <v>-2.054136521843724</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.263525397865588</v>
+        <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5227258995385179</v>
+        <v>0.5838962391172409</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.423640106471424</v>
+        <v>3.460342310218659</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.323797642874131</v>
+        <v>-2.262627303295408</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.200467375023682</v>
+        <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3142351180868335</v>
+        <v>0.3754054576655564</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.318883927339182</v>
+        <v>3.355586131086416</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.570998827639353</v>
+        <v>-2.50982848806063</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.109685651526162</v>
+        <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3343884715856459</v>
+        <v>0.3955588111643689</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.339074689847038</v>
+        <v>3.375776893594272</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.063383855663449</v>
+        <v>-3.002213516084727</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.913838032360256</v>
+        <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1579965564384508</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.044750065076312</v>
+        <v>3.081452268823546</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.448564246593522</v>
+        <v>-3.387393907014799</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.75830841480109</v>
+        <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1579965564384508</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.043292603889176</v>
+        <v>3.079994807636409</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.698434926608103</v>
+        <v>-3.637264587029381</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.660129266249873</v>
+        <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1217338366079876</v>
+        <v>-0.06056349702926461</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.06681935924207</v>
+        <v>3.103521562989304</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.904946703495125</v>
+        <v>-3.843776363916402</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.573630614151323</v>
+        <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3282456134950091</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.939018351766115</v>
+        <v>2.975720555513349</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.224290778575627</v>
+        <v>-4.163120438996904</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.447665910819381</v>
+        <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3282456134950091</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.940791278466374</v>
+        <v>2.977493482213608</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.656096571725414</v>
+        <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.261276481026871</v>
+        <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4646631099362761</v>
+        <v>-0.4034927703575531</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.845273668069018</v>
+        <v>2.881975871816252</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.890790565857967</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.155683658375941</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.4583268427070209</v>
+        <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.837360203408662</v>
+        <v>2.874062407155896</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.226453213088419</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.019999191139725</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5262578281959257</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.795182203771284</v>
+        <v>2.831884407518518</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.302897543291291</v>
+        <v>-5.241727203712568</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.9959090192928177</v>
+        <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.4458123191022638</v>
+        <v>-0.3846419795235408</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.849937069461723</v>
+        <v>2.886639273208957</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.668024925930037</v>
+        <v>-5.606854586351314</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8491125812431504</v>
+        <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7421231034012763</v>
+        <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.671405113888147</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.076613703110716</v>
+        <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.6844386143856376</v>
+        <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.150711880581955</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.425013391594499</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.190374115133581</v>
+        <v>-6.129203775554858</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6341198820479526</v>
+        <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.150711880581955</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.42019882406596</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.606765989420579</v>
+        <v>-6.545595649841855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4655571829420309</v>
+        <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.150711880581955</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.418192874674837</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.851037390147648</v>
+        <v>-6.789867050568925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.378107313319882</v>
+        <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.150711880581955</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.428451565343516</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.056288409384408</v>
+        <v>-6.995118069805685</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2921064707708729</v>
+        <v>0.3165746066023623</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.150711880581955</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.424551130489212</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.104491226626752</v>
+        <v>-7.043320887048029</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2712302639289366</v>
+        <v>0.2956983997604259</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.150711880581955</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.422956050544212</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.40115256843695</v>
+        <v>-7.339982228858227</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1563447031340659</v>
+        <v>0.1808128389655548</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.219455016315833</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.385489145033093</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.587872276746253</v>
+        <v>-7.526701937167529</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.07763051527594156</v>
+        <v>0.1020986511074309</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.219455016315833</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.38146284049869</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.970873665488884</v>
+        <v>-7.909703325910161</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.07567214154269486</v>
+        <v>-0.05120400571120598</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.219455016315833</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.381360739177106</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.975360110690272</v>
+        <v>-7.914189771111549</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.07489520365182045</v>
+        <v>-0.05042706782033113</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.223941461517222</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.381240388027703</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.334890433194275</v>
+        <v>-8.273720093615552</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.2133570293553713</v>
+        <v>-0.1888888935238819</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.223941461517222</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.386590691325753</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.385239496648497</v>
+        <v>-8.324069157069774</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2255806347798823</v>
+        <v>-0.2011124989483934</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.274290524971444</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.364297273210398</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.482858774069893</v>
+        <v>-8.42168843449117</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2615865951266723</v>
+        <v>-0.2371184592951829</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.371909802392841</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.308767457379328</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.536930273578252</v>
+        <v>-8.475759933999528</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2803216386084433</v>
+        <v>-0.255853502776954</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.4259813019012</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.279218113995885</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.741188448908115</v>
+        <v>-8.680018109329392</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3565117116217467</v>
+        <v>-0.3320435757902573</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.553620246515189</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.208147944346134</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.774841287416589</v>
+        <v>-8.713670947837866</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3654902925407</v>
+        <v>-0.3410221567092107</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.654033614432227</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.152382478080348</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.70137145574914</v>
+        <v>-8.640201116170417</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3207306583802989</v>
+        <v>-0.29626252254881</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.580563782764778</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.211836078574238</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.876495873135683</v>
+        <v>-8.81532553355696</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3762252045873997</v>
+        <v>-0.3517570687559104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.755688200151322</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.121316648889828</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.110947967150173</v>
+        <v>-9.04977762757145</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4772252070947913</v>
+        <v>-0.4527570712633024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.755688200151322</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.114097483988232</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.215322698176619</v>
+        <v>-9.154152358597896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5256472902793461</v>
+        <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.860062931177768</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.044800454598389</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.268108853776946</v>
+        <v>-9.206938514198223</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5456459626809207</v>
+        <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.955738417760165</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.988510952487506</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.394145647145235</v>
+        <v>-9.332975307566512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5933669513991218</v>
+        <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.930486794950423</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.006355654802467</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.337073875249304</v>
+        <v>-9.275903535670581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5665479069543484</v>
+        <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.930486794950423</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.010345990488867</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.478745716973425</v>
+        <v>-9.417575377394702</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6246918705427382</v>
+        <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.930486794950423</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.008870763590126</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.42915487254859</v>
+        <v>-9.367984532969867</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5898021226079324</v>
+        <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.880895950525589</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.053678680409898</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.280236538076734</v>
+        <v>-9.219066198498011</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5432859224658726</v>
+        <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.849646359790416</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.059377301204319</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.054391385357324</v>
+        <v>-8.993221045778601</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4433687883419002</v>
+        <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.807719684203252</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.094112379592826</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.929812729019732</v>
+        <v>-8.868642389441009</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3923981812508042</v>
+        <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.807719684203252</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.095251524148885</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.982708017064018</v>
+        <v>-8.921537677485295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4109225223064112</v>
+        <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.802764338114806</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.100858505964061</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.910574841776137</v>
+        <v>-8.849404502197414</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3763355479526225</v>
+        <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.802764338114806</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.106592210202697</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.83920844916649</v>
+        <v>-8.778038109587767</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3575262533026287</v>
+        <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.731397945505158</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.139674783374621</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.745749415181265</v>
+        <v>-8.684579075602542</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3300261210214464</v>
+        <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.731397945505158</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.129791302061713</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.478507614312868</v>
+        <v>-8.417337274734145</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2249639611734611</v>
+        <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.731397945505158</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.127956741562339</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.380600575636377</v>
+        <v>-8.319430236057654</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1861014606763258</v>
+        <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.663412195644602</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.168447876505212</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.356647034660419</v>
+        <v>-8.295476695081696</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1758515381404488</v>
+        <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.639458654668644</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.18348850723628</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.092587096337622</v>
+        <v>-8.031416756758899</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.08348787897308219</v>
+        <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.375398716345848</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.328664154068206</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.385507472832784</v>
+        <v>-7.324337133254061</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1965569367685522</v>
+        <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.375398716345848</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.325877120407905</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.345323174466594</v>
+        <v>-7.284152834887871</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2129742800028698</v>
+        <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.335214417979657</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.350331323315461</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.181923303527231</v>
+        <v>-7.120752963948508</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2777010495993717</v>
+        <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.171814547040294</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.447738067099835</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.948442081297633</v>
+        <v>-6.88727174171891</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3790179673290632</v>
+        <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9383333248106958</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.595751229275447</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.798775690290118</v>
+        <v>-6.737605350711394</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4359923134191104</v>
+        <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8454298335681598</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.648601113708009</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.666500216659231</v>
+        <v>-6.605329877080508</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4842699896184919</v>
+        <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7131543599372732</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.723333884633568</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.510761884099489</v>
+        <v>-6.449591544520766</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5493803833300253</v>
+        <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5574160273775316</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.81959194485705</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.261762085415908</v>
+        <v>-6.200591745837185</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6618866440271165</v>
+        <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5574160273775316</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.832498286080709</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.367352075189013</v>
+        <v>-6.30618173561029</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4916747185186559</v>
+        <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.663006017150636</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.641168362617627</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.38608697730761</v>
+        <v>-6.324916637728887</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5327250995483035</v>
+        <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6686020268107673</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.686355098698635</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.23814693590001</v>
+        <v>-6.176976596321287</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4720221934231756</v>
+        <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6482811109022097</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.578668725555602</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.185177413646022</v>
+        <v>-6.124007074067299</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4844960160712928</v>
+        <v>0.5089641519027821</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5953115886482209</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.601736452654517</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.141629006875331</v>
+        <v>-6.080458667296608</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4949547666844758</v>
+        <v>0.5194229025159651</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5953115886482209</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.594775840559424</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.108265800396563</v>
+        <v>-6.04709546081784</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5227624036571266</v>
+        <v>0.5472305394886159</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5953115886482209</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.609238194940567</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.000006663274041</v>
+        <v>-5.938836323695318</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5605981789653303</v>
+        <v>0.5850663147968196</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5953115886482209</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.603770315399762</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.87671552845691</v>
+        <v>-5.815545188878187</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6074127269027594</v>
+        <v>0.6318808627342487</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4720204538310904</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.675243090300617</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.855566329553467</v>
+        <v>-5.794395989974744</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6235733847014622</v>
+        <v>0.6480415205329515</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.450871254927647</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.695633587880008</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.611800887570022</v>
+        <v>-5.550630547991299</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7168602698418907</v>
+        <v>0.7413284056733795</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.450871254927647</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.691414296227059</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.510038067292728</v>
+        <v>-5.448867727714005</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7596897118728245</v>
+        <v>0.7841578477043138</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4376521865352183</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.701470051182532</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.260187673343653</v>
+        <v>-5.19901733376493</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8523719444361566</v>
+        <v>0.8768400802676455</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4376521865352183</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.694212126166234</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.084295580876221</v>
+        <v>-5.023125241297498</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9263279049437778</v>
+        <v>0.9507960407752671</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4376521865352183</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.697811249686883</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.912849117853757</v>
+        <v>-4.851678778275034</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.008233996207317</v>
+        <v>1.032702132038806</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2662057235127552</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.814006633554914</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.838559552115418</v>
+        <v>-4.777389212536695</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.03697030011895</v>
+        <v>1.061438435950439</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1919161577744159</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.857600850614215</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.774923809881484</v>
+        <v>-4.713753470302761</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.067119398066841</v>
+        <v>1.09158753389833</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1282804155404814</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.900477097008893</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.663497050555564</v>
+        <v>-4.602326710976841</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.092884360581004</v>
+        <v>1.117352496412494</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1282804155404814</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.881671355792689</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.423066553750703</v>
+        <v>-4.36189621417198</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.190799635927826</v>
+        <v>1.215267771759315</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1121500812643789</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.027672730500482</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.350823985579509</v>
+        <v>-4.289653646000786</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.223625977031124</v>
+        <v>1.248094112862613</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1121500812643789</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.031602044335302</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.297825663298121</v>
+        <v>-4.236655323719398</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.245503889861019</v>
+        <v>1.269972025692508</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1674863402663178</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.065482383653806</v>
+        <v>3.10218458740104</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.189020777818394</v>
+        <v>-4.127850438239671</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.286023915272903</v>
+        <v>1.310492051104393</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1674863402663178</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.062480454873799</v>
+        <v>3.099182658621033</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.968999979781383</v>
+        <v>-3.90782964020266</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.375611271498322</v>
+        <v>1.400079407329811</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.308706185334298</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.148791398925201</v>
+        <v>3.185493602672435</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.836132290718105</v>
+        <v>-3.774961951139382</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.444652529925456</v>
+        <v>1.469120665756946</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.308706185334298</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.164685581727025</v>
+        <v>3.201387785474259</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.715959207353606</v>
+        <v>-3.654788867774883</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.493867607711558</v>
+        <v>1.518335743543047</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4288792686987969</v>
+        <v>0.4900496082775201</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.237935276186026</v>
+        <v>3.27463747993326</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.571287062253869</v>
+        <v>-3.510116722675146</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.561824568312893</v>
+        <v>1.586292704144382</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5735514137985344</v>
+        <v>0.6347217533772576</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.334826665807308</v>
+        <v>3.371528869554542</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.631161889611561</v>
+        <v>-3.569991550032838</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.523912128771242</v>
+        <v>1.548380264602731</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5136765864408422</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.284939260794119</v>
+        <v>3.321641464541353</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.511341658700724</v>
+        <v>-3.450171319122</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.587129390369785</v>
+        <v>1.611597526201274</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5136765864408422</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.300228430028327</v>
+        <v>3.336930633775562</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.51381136516253</v>
+        <v>-3.452641025583806</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.493785707107504</v>
+        <v>1.518253842938994</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5112068799790361</v>
+        <v>0.5723772195577592</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.206390805473685</v>
+        <v>3.243093009220919</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.582181551486539</v>
+        <v>-3.521011211907816</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.385699494063202</v>
+        <v>1.410167629894691</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5204825790152511</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.131218086380716</v>
+        <v>3.16792029012795</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.595969604333586</v>
+        <v>-3.534799264754863</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.370620981556274</v>
+        <v>1.395089117387764</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5204825790152511</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.121654795012607</v>
+        <v>3.158356998759841</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.626962763662291</v>
+        <v>-3.565792424083568</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.182933282865179</v>
+        <v>1.207401418696668</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5204825790152511</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.946364360052994</v>
+        <v>2.983066563800228</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.451488503869822</v>
+        <v>-3.390318164291099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.257690218773954</v>
+        <v>1.282158354605444</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5204825790152511</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.950931592044781</v>
+        <v>2.987633795792016</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.562424756511071</v>
+        <v>-3.501254416932348</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.189057746478662</v>
+        <v>1.213525882310151</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5204825790152511</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.926673620805988</v>
+        <v>2.963375824553223</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.528761211038789</v>
+        <v>-3.467590871460066</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.131061478069025</v>
+        <v>1.155529613900514</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.554146124487533</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.875410061490808</v>
+        <v>2.912112265238041</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.468908591835066</v>
+        <v>-3.407738252256343</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.165174912182646</v>
+        <v>1.189643048014136</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.554146124487533</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.88558244792294</v>
+        <v>2.922284651670174</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.382665128808688</v>
+        <v>-3.321494789229965</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.194618567967058</v>
+        <v>1.219086703798547</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.554146124487533</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.8805287184968</v>
+        <v>2.917230922244034</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.427971948207668</v>
+        <v>-3.366801608628945</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.168271615651991</v>
+        <v>1.19273975148348</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5133359614783022</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.847818396135787</v>
+        <v>2.884520599883021</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.45700505290997</v>
+        <v>-3.395834713331247</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.157210246804172</v>
+        <v>1.181678382635661</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5133359614783022</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.848370269168889</v>
+        <v>2.885072472916123</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.364194571459111</v>
+        <v>-3.430052028835363</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.123607131275882</v>
+        <v>1.09726414832538</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6061464429291615</v>
+        <v>0.5402889855529089</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.83332924993077</v>
+        <v>2.793814775505019</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.408584040788538</v>
+        <v>-3.474441498164791</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.107724819468711</v>
+        <v>1.08138183651821</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5617569735997339</v>
+        <v>0.4958995162234813</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.808569044257714</v>
+        <v>2.769054569831963</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.295912822552288</v>
+        <v>-3.361770279928541</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.147869015274934</v>
+        <v>1.121526032324433</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.674428191835984</v>
+        <v>0.6085707344597315</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.871247483711187</v>
+        <v>2.831733009285436</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.183535821369615</v>
+        <v>-3.249393278745868</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.198311111578671</v>
+        <v>1.17196812862817</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.674428191835984</v>
+        <v>0.6085707344597315</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.876738779541855</v>
+        <v>2.837224305116103</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.211316219270969</v>
+        <v>-3.277173676647221</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.198696154186668</v>
+        <v>1.172353171236167</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6466477939346309</v>
+        <v>0.5807903365583784</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.871567742569582</v>
+        <v>2.83205326814383</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.294317500296247</v>
+        <v>-3.3601749576725</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.00385136177721</v>
+        <v>0.9775083788267089</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6280769094074572</v>
+        <v>0.5622194520312047</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.698780931853931</v>
+        <v>2.659266457428179</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.402931578739579</v>
+        <v>-3.468789036115831</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.080555391119083</v>
+        <v>1.054212408168582</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6280769094074572</v>
+        <v>0.5622194520312047</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.818930592573137</v>
+        <v>2.779416118147385</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.367522540491436</v>
+        <v>-3.433379997867688</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.109232032520663</v>
+        <v>1.082889049570162</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6280769094074572</v>
+        <v>0.5622194520312047</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.83344361867546</v>
+        <v>2.793929144249708</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.329138877933285</v>
+        <v>-3.394996335309537</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.122004938886292</v>
+        <v>1.095661955935791</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6664605719656084</v>
+        <v>0.6006031145893559</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.853893257552719</v>
+        <v>2.814378783126967</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.152022547898119</v>
+        <v>-3.217880005274371</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.189580499745661</v>
+        <v>1.16323751679516</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6664605719656084</v>
+        <v>0.6006031145893559</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.850622286398021</v>
+        <v>2.811107811972269</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.197114792731664</v>
+        <v>-3.262972250107917</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.172226993574156</v>
+        <v>1.145884010623655</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6045645287962186</v>
+        <v>0.5387070714199661</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.8141680522583</v>
+        <v>2.774653577832549</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.017739371492897</v>
+        <v>-3.083596828869149</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.237764137376077</v>
+        <v>1.211421154425576</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7613412869669373</v>
+        <v>0.6954838295906848</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.902021082467146</v>
+        <v>2.862506608041394</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.062753585013503</v>
+        <v>-3.128611042389756</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.200565907299424</v>
+        <v>1.174222924348923</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7309923916523327</v>
+        <v>0.6651349342760802</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.864619200609972</v>
+        <v>2.825104726184221</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.329758095285938</v>
+        <v>-3.395615552662191</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.099455665529396</v>
+        <v>1.073112682578895</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.536629353609384</v>
+        <v>0.4707718962331316</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.753692940123149</v>
+        <v>2.714178465697398</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.430955876723111</v>
+        <v>-3.496813334099364</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.058180474851028</v>
+        <v>1.031837491900527</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4682205400640648</v>
+        <v>0.4023630826878124</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.711851573892459</v>
+        <v>2.672337099466707</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.424444910108798</v>
+        <v>-3.490302367485051</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.05838482305107</v>
+        <v>1.032041840100569</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4682205400640648</v>
+        <v>0.4023630826878124</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.709451535446776</v>
+        <v>2.669937061021024</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.405406782401501</v>
+        <v>-3.471264239777754</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.062524793342234</v>
+        <v>1.036181810391733</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4100369287328703</v>
+        <v>0.3441794713566179</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.671066087856304</v>
+        <v>2.631551613430553</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.436533413552119</v>
+        <v>-3.502390870928372</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.227656009820667</v>
+        <v>1.201313026870166</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4100369287328703</v>
+        <v>0.3441794713566179</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.848647956794985</v>
+        <v>2.809133482369233</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.450400174886036</v>
+        <v>-3.516257632262289</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.222942634273234</v>
+        <v>1.196599651322733</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3721790119990473</v>
+        <v>0.3063215546227949</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.826766535740824</v>
+        <v>2.787252061315073</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.405596003346107</v>
+        <v>-3.471453460722359</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.246872833286132</v>
+        <v>1.220529850335631</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3721790119990473</v>
+        <v>0.3063215546227949</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.83277506613775</v>
+        <v>2.793260591711999</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.257853033111104</v>
+        <v>-3.323710490487357</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.203920242657332</v>
+        <v>1.177577259706831</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5399863692339305</v>
+        <v>0.4741289118576781</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.83140970175588</v>
+        <v>2.791895227330128</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.359867715642325</v>
+        <v>-3.425725173018578</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.165907991176325</v>
+        <v>1.139565008225824</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5399863692339305</v>
+        <v>0.4741289118576781</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.834203323287361</v>
+        <v>2.794688848861609</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.353715009589541</v>
+        <v>-3.419572466965794</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.169031421989097</v>
+        <v>1.142688439038596</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5461390752867148</v>
+        <v>0.4802816179104624</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.838557295310689</v>
+        <v>2.799042820884938</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.370524307740042</v>
+        <v>-3.436381765116295</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.161388179469006</v>
+        <v>1.135045196518505</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5293297771362131</v>
+        <v>0.4634723197599607</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.827552193160499</v>
+        <v>2.788037718734747</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.308226308963921</v>
+        <v>-3.374083766340173</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.252642932776276</v>
+        <v>1.226299949825775</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5293297771362131</v>
+        <v>0.4634723197599607</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.89388774695732</v>
+        <v>2.854373272531568</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.106436111298763</v>
+        <v>-3.172293568675015</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.135651013556466</v>
+        <v>1.109308030605965</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7273479693053675</v>
+        <v>0.6614905119291151</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.81499066397294</v>
+        <v>2.775476189547188</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.941623108219916</v>
+        <v>-3.007480565596168</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.27186644711018</v>
+        <v>1.245523464159679</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8921609723842144</v>
+        <v>0.8263035150079621</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.984168698142423</v>
+        <v>2.944654223716671</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.03936365284489</v>
+        <v>-3.105221110221143</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.247397965376234</v>
+        <v>1.221054982425733</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8762716942512343</v>
+        <v>0.8104142368749818</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.989262867378678</v>
+        <v>2.949748392952927</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.215701412967819</v>
+        <v>-3.281558870344072</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.175398842151734</v>
+        <v>1.149055859201233</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6999339341283048</v>
+        <v>0.6340764767520524</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.881996192129592</v>
+        <v>2.842481717703841</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.139279366535892</v>
+        <v>-3.205136823912145</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.204459278764433</v>
+        <v>1.178116295813932</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6999339341283048</v>
+        <v>0.6340764767520524</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.880487810169521</v>
+        <v>2.84097333574377</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.094906234897324</v>
+        <v>-3.160763692273576</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.222071398855297</v>
+        <v>1.195728415904796</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7443070657668734</v>
+        <v>0.678449608390621</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.906974556588098</v>
+        <v>2.867460082162347</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.972072014010156</v>
+        <v>-3.037929471386409</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.265598881348755</v>
+        <v>1.239255898398254</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7443070657668734</v>
+        <v>0.678449608390621</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.901368350726689</v>
+        <v>2.861853876300937</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.924416283449101</v>
+        <v>-2.990273740825353</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.291042930600982</v>
+        <v>1.264699947650481</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7919627963279291</v>
+        <v>0.7261053389516766</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.936343546091127</v>
+        <v>2.896829071665375</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.823898124950346</v>
+        <v>-2.889755582326599</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.336142567375208</v>
+        <v>1.309799584424707</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8924809548266837</v>
+        <v>0.8266234974504312</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.001546814565105</v>
+        <v>2.962032340139353</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.884564715352735</v>
+        <v>-2.950422172728988</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.298630603690125</v>
+        <v>1.272287620739624</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.81078263810815</v>
+        <v>0.7449251807318975</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.939282497009856</v>
+        <v>2.899768022584105</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.839726313744337</v>
+        <v>-2.90558377112059</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.320663666944113</v>
+        <v>1.294320683993612</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8153260710530195</v>
+        <v>0.749468613676767</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.946106259387407</v>
+        <v>2.906591784961655</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.940484949501335</v>
+        <v>-3.006342406877588</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.284521152272391</v>
+        <v>1.25817816932189</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.726500502326014</v>
+        <v>0.6606430449497616</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.896971857782281</v>
+        <v>2.85745738335653</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.896282112415435</v>
+        <v>-2.962139569791688</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.308081889634589</v>
+        <v>1.281738906684088</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7707033394119145</v>
+        <v>0.704845882035662</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.929373162561659</v>
+        <v>2.889858688135907</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.933261140078878</v>
+        <v>-2.999118597455131</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.291700279038459</v>
+        <v>1.265357296087958</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.807677241203245</v>
+        <v>0.7418197838269925</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.949967504105705</v>
+        <v>2.910453029679953</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.774969722539606</v>
+        <v>-2.840827179915859</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.406264611237207</v>
+        <v>1.379921628286706</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.807677241203245</v>
+        <v>0.7418197838269925</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.001215269288744</v>
+        <v>2.961700794862993</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.56732771890513</v>
+        <v>-2.633185176281382</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.487762117285251</v>
+        <v>1.46141913433475</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.015319244837721</v>
+        <v>0.9494617874614687</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.124241176063683</v>
+        <v>3.084726701637932</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.516295626182602</v>
+        <v>-2.582153083558854</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.503123182612532</v>
+        <v>1.476780199662031</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.066351337560249</v>
+        <v>1.000493880183997</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.14980865993547</v>
+        <v>3.110294185509718</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.451071445055396</v>
+        <v>-2.516928902431649</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.546400259156119</v>
+        <v>1.520057276205619</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.131575518687455</v>
+        <v>1.065718061311202</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.206130572704498</v>
+        <v>3.166616098278747</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.413644424984262</v>
+        <v>-2.479501882360515</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.557332039483853</v>
+        <v>1.530989056533352</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.136827056716637</v>
+        <v>1.070969599340384</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.205242467821288</v>
+        <v>3.165727993395536</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.43375608101897</v>
+        <v>-2.499613538395223</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.55054416940121</v>
+        <v>1.524201186450709</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.147854401714056</v>
+        <v>1.081996944337803</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.21311566715098</v>
+        <v>3.173601192725228</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.380011266591766</v>
+        <v>-2.445868723968018</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.732599866193303</v>
+        <v>1.706256883242802</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.157917711154518</v>
+        <v>1.092060253778265</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.379711423836468</v>
+        <v>3.340196949410716</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.305229005566753</v>
+        <v>-2.371086462943006</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.882625679821125</v>
+        <v>1.856282696870624</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.23269997217953</v>
+        <v>1.166842514803278</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.544693689669292</v>
+        <v>3.505179215243541</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.279144921302945</v>
+        <v>-2.345002378679198</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.884767289540508</v>
+        <v>1.858424306590007</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.23269997217953</v>
+        <v>1.166842514803278</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.536401665683151</v>
+        <v>3.4968871912574</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.201013740453998</v>
+        <v>-2.266871197830251</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.914212957463866</v>
+        <v>1.887869974513365</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.306876783063215</v>
+        <v>1.241019325686962</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.579100947797142</v>
+        <v>3.53958647337139</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.192121279060715</v>
+        <v>-2.257978736436968</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.93532434774797</v>
+        <v>1.908981364797469</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.306876783063215</v>
+        <v>1.241019325686962</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.596655353523933</v>
+        <v>3.557140879098181</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.360597396030593</v>
+        <v>-2.426454853406846</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.859788948364603</v>
+        <v>1.833445965414102</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.278928947346634</v>
+        <v>1.213071489970382</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.571741699498569</v>
+        <v>3.532227225072817</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.66279786716901</v>
+        <v>-1.728655324545262</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.120178457097098</v>
+        <v>2.093835474146597</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.208580887976224</v>
+        <v>1.142723430599971</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.510802561064184</v>
+        <v>3.471288086638432</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.640076763485857</v>
+        <v>-1.70593422086211</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.119930921067264</v>
+        <v>2.093587938116763</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.208580887976224</v>
+        <v>1.142723430599971</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.501466583561089</v>
+        <v>3.461952109135337</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.638351720195814</v>
+        <v>-1.704209177572066</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.279527064234451</v>
+        <v>2.253184081283949</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.210305931266267</v>
+        <v>1.144448473890015</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.661407735386284</v>
+        <v>3.621893260960532</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.793132726974069</v>
+        <v>-1.858990184350322</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.254692484016795</v>
+        <v>2.228349501066294</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.176938257211791</v>
+        <v>1.111080799835539</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.678464953447245</v>
+        <v>3.638950479021493</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.786078036758895</v>
+        <v>-1.851935494135148</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.25418971609241</v>
+        <v>2.227846733141909</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.183992947426965</v>
+        <v>1.118135490050712</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.679373123565894</v>
+        <v>3.639858649140142</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.759126812432407</v>
+        <v>-1.82498426980866</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.274976359467746</v>
+        <v>2.248633376517245</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.198873293454684</v>
+        <v>1.133015836078431</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.698307484827267</v>
+        <v>3.658793010401515</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.895079820488723</v>
+        <v>-1.960937277864976</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.40469828839018</v>
+        <v>2.378355305439678</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.198873293454684</v>
+        <v>1.133015836078431</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.882410616972227</v>
+        <v>3.842896142546475</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.917487938293595</v>
+        <v>-1.983345395669848</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.387851736171224</v>
+        <v>2.361508753220723</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.198873293454684</v>
+        <v>1.133015836078431</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.87452731187522</v>
+        <v>3.835012837449468</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.065493705772995</v>
+        <v>-2.131351163149247</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.330703428729101</v>
+        <v>2.3043604457786</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.112146284591143</v>
+        <v>1.04628882721489</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.824545106106732</v>
+        <v>3.785030631680981</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.074934631661525</v>
+        <v>-2.140792089037777</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.383180776095537</v>
+        <v>2.356837793145035</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.234573402134534</v>
+        <v>1.168715944758282</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.954255094354615</v>
+        <v>3.914740619928863</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.127208238997166</v>
+        <v>-2.193065696373419</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.365162427706581</v>
+        <v>2.33881944475608</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.182299794798893</v>
+        <v>1.11644233742264</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.925782024498531</v>
+        <v>3.886267550072779</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.203538216598072</v>
+        <v>-2.269395673974325</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.332742249559994</v>
+        <v>2.306399266609493</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.182299794798893</v>
+        <v>1.11644233742264</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.923893837392306</v>
+        <v>3.884379362966554</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.315295169213373</v>
+        <v>-2.381152626589626</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.282859698116736</v>
+        <v>2.256516715166235</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.070542842183592</v>
+        <v>1.004685384807339</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.851659895425987</v>
+        <v>3.812145421000236</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.313454150155122</v>
+        <v>-2.379311607531374</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.282030115950188</v>
+        <v>2.255687132999687</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.07181106885506</v>
+        <v>1.005953611478807</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.850854841639021</v>
+        <v>3.811340367213269</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.445755442252675</v>
+        <v>-2.511612899628928</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.242183005977086</v>
+        <v>2.215840023026585</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.07181106885506</v>
+        <v>1.005953611478807</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.863928248504939</v>
+        <v>3.824413774079188</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.447317085067535</v>
+        <v>-2.513174542443788</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.241558348851142</v>
+        <v>2.215215365900641</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.07181106885506</v>
+        <v>1.005953611478807</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.863928248504939</v>
+        <v>3.824413774079188</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.475217872177008</v>
+        <v>-2.541075329553261</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.228922075134355</v>
+        <v>2.202579092183854</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.037214144712125</v>
+        <v>0.9713566873358727</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.84169413514618</v>
+        <v>3.802179660720429</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.597743974879902</v>
+        <v>-2.663601432256155</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.176676078030396</v>
+        <v>2.150333095079895</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9146880420092316</v>
+        <v>0.8488305846329788</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.764942917501643</v>
+        <v>3.725428443075891</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.617805296156409</v>
+        <v>-2.683662753532662</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.235357509110297</v>
+        <v>2.209014526159796</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8946267207327245</v>
+        <v>0.8287692633564718</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.819612084326243</v>
+        <v>3.780097609900491</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.874526114151233</v>
+        <v>-2.940383571527486</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.272980900914214</v>
+        <v>2.246637917963713</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.7862121465889097</v>
+        <v>0.720354689212657</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.894875058841801</v>
+        <v>3.855360584416049</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.028512531927373</v>
+        <v>-3.094369989303626</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.280366602949398</v>
+        <v>2.254023619998897</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.7862121465889097</v>
+        <v>0.720354689212657</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.96385532798744</v>
+        <v>3.924340853561689</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.977990628099707</v>
+        <v>-3.04384808547596</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.286626566600585</v>
+        <v>2.260283583650084</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.7862121465889097</v>
+        <v>0.720354689212657</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.949906530107562</v>
+        <v>3.91039205568181</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.230465782107432</v>
+        <v>-3.296323239483685</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.197506994052909</v>
+        <v>2.171164011102408</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.7862121465889097</v>
+        <v>0.720354689212657</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.961777019162975</v>
+        <v>3.922262544737224</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.49993858402914</v>
+        <v>-3.565796041405393</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.09092840780317</v>
+        <v>2.064585424852669</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.7862121465889097</v>
+        <v>0.720354689212657</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.962987553681919</v>
+        <v>3.923473079256167</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.657482655758581</v>
+        <v>-3.723340113134834</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.032032521338714</v>
+        <v>2.005689538388213</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7193103414486353</v>
+        <v>0.6534528840723826</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.926968212825075</v>
+        <v>3.887453738399324</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.786333206460628</v>
+        <v>-3.85219066383688</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.975570153794085</v>
+        <v>1.949227170843584</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6783169325979137</v>
+        <v>0.612459475221661</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.897450020250832</v>
+        <v>3.857935545825081</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.903300899099519</v>
+        <v>-3.969158356475771</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.090987133437573</v>
+        <v>2.064644150487072</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6783169325979137</v>
+        <v>0.612459475221661</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.059654076949877</v>
+        <v>4.020139602524125</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.988018841320472</v>
+        <v>-4.053876298696725</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.051946594513006</v>
+        <v>2.025603611562505</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5932009036698673</v>
+        <v>0.5273434462936146</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.003431097556863</v>
+        <v>3.963916623131111</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.069953659589356</v>
+        <v>-4.135811116965608</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.029402084773944</v>
+        <v>2.003059101823442</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5832661580827871</v>
+        <v>0.5174087007065344</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.007699667773106</v>
+        <v>3.968185193347354</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.016215486189093</v>
+        <v>-4.082072943565346</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.059822992589951</v>
+        <v>2.03348000963945</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6370043314830492</v>
+        <v>0.5711468741067965</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.048868210269165</v>
+        <v>4.009353735843414</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.906209202711872</v>
+        <v>-3.972066660088124</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.095978393225015</v>
+        <v>2.069635410274514</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.6602089034003245</v>
+        <v>0.5943514460240718</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.054943840663706</v>
+        <v>4.015429366237955</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.763149626970946</v>
+        <v>-3.829007084347199</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.15745223424336</v>
+        <v>2.131109251292858</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.6682223299903037</v>
+        <v>0.602364872614051</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.064001907339668</v>
+        <v>4.024487432913916</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,45 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.785653626608132</v>
+        <v>3.77725157243693</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.461702901499109</v>
+        <v>-3.527560358875362</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.28529180731463</v>
+        <v>2.258948824364129</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.969669055462141</v>
+        <v>0.9038115980858883</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.252130825505306</v>
+        <v>4.212616351079554</v>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" s="2" t="n">
+        <v>45492</v>
+      </c>
+      <c r="B2030" t="n">
+        <v>3.507155144905421</v>
+      </c>
+      <c r="C2030" t="n">
+        <v>3.459661610718886</v>
+      </c>
+      <c r="D2030" t="n">
+        <v>-3.527560358875362</v>
+      </c>
+      <c r="E2030" t="n">
+        <v>2.258948824364129</v>
+      </c>
+      <c r="F2030" t="n">
+        <v>0.9038115980858883</v>
+      </c>
+      <c r="G2030" t="n">
+        <v>3.452725407705254</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240719.xlsx
+++ b/tame_output/ON/bt/strategyON_20240719.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>49.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>77.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>38.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>62.4%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>30.9%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>57.0%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>31.4%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.0%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>48.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>109.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.3%</t>
+          <t>122.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.0%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-640.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-47.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.3%</t>
+          <t>-66.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.1%</t>
+          <t>454.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-514.3%</t>
+          <t>-497.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-258.2%</t>
+          <t>-256.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>115.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.3%</t>
+          <t>-143.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-263.7%</t>
+          <t>-269.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.0%</t>
+          <t>-133.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-133.6%</t>
+          <t>-127.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>75.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-158.6%</t>
+          <t>-162.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.6%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-17.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-100.8%</t>
+          <t>-86.3%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1878921395489951</v>
+        <v>0.1267217999702719</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.197370603618793</v>
+        <v>3.172902467787304</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.568940374610322</v>
+        <v>1.507770035031599</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.063934396879136</v>
+        <v>4.027232193131902</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.04923935230080001</v>
+        <v>-0.009461906236936657</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.137459091376417</v>
+        <v>3.153370069801962</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.568940374610322</v>
+        <v>1.507770035031599</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.098875481376678</v>
+        <v>4.062173277629444</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.04420176157321348</v>
+        <v>-0.00442431550935013</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.13805156785279</v>
+        <v>3.153962546278335</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.62458483087664</v>
+        <v>1.563414491297916</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.130839595321806</v>
+        <v>4.094137391574573</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.3013957962812702</v>
+        <v>-0.2616183502174069</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.013920335593304</v>
+        <v>3.02983131401885</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.367390796168583</v>
+        <v>1.30622045658986</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.95526955612071</v>
+        <v>3.918567352373476</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3671631863306823</v>
+        <v>-0.3273857402668189</v>
       </c>
       <c r="E1842" t="n">
-        <v>2.988630988704009</v>
+        <v>3.004541967129555</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.367390796168583</v>
+        <v>1.30622045658986</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.95628716525118</v>
+        <v>3.919584961503945</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5724078633879268</v>
+        <v>-0.5326304173240635</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.897161149868867</v>
+        <v>2.913072128294413</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.367390796168583</v>
+        <v>1.30622045658986</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.946915197238935</v>
+        <v>3.910212993491701</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6541797638156785</v>
+        <v>-0.6144023177518152</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.854535115653005</v>
+        <v>2.87044609407855</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.394426369574719</v>
+        <v>1.333256029995996</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.953219267237856</v>
+        <v>3.916517063490621</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.7213888716875563</v>
+        <v>-0.6816114256236929</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.832416789337956</v>
+        <v>2.848327767763501</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.394426369574719</v>
+        <v>1.333256029995996</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.957984584071558</v>
+        <v>3.921282380324324</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.7099996350327549</v>
+        <v>-0.6702221889688915</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.834797280119117</v>
+        <v>2.850708258544662</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.405815606229521</v>
+        <v>1.344645266650798</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.962642922183679</v>
+        <v>3.925940718436445</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.127753658579592</v>
+        <v>-1.087976212515729</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.665622562205445</v>
+        <v>2.681533540630991</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9880615826826838</v>
+        <v>0.9268912431039608</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.70991739956064</v>
+        <v>3.673215195813406</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.417885325185023</v>
+        <v>-1.37810787912116</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.549436112162195</v>
+        <v>2.56534709058774</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.012143377422864</v>
+        <v>0.9509730378441407</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.72423269300367</v>
+        <v>3.687530489256436</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.625889383538101</v>
+        <v>-1.586111937474237</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.471126633374889</v>
+        <v>2.487037611800434</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.012143377422864</v>
+        <v>0.9509730378441407</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.729124837557595</v>
+        <v>3.692422633810361</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.688067794699071</v>
+        <v>-1.648290348635207</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.441336725248489</v>
+        <v>2.457247703674034</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.9499649662618935</v>
+        <v>0.8887946266831706</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.686899247199001</v>
+        <v>3.650197043451767</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.054136521843724</v>
+        <v>-2.01435907577986</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.287993533697077</v>
+        <v>2.303904512122622</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5838962391172409</v>
+        <v>0.5227258995385179</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.460342310218659</v>
+        <v>3.423640106471424</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.262627303295408</v>
+        <v>-2.222849857231545</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.224935510855171</v>
+        <v>2.240846489280717</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3754054576655564</v>
+        <v>0.3142351180868335</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.355586131086416</v>
+        <v>3.318883927339182</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.50982848806063</v>
+        <v>-2.470051041996767</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.134153787357651</v>
+        <v>2.150064765783196</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3955588111643689</v>
+        <v>0.3343884715856459</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.375776893594272</v>
+        <v>3.339074689847038</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.002213516084727</v>
+        <v>-2.962436070020864</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.938306168191745</v>
+        <v>1.95421714661729</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.1579965564384508</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.081452268823546</v>
+        <v>3.044750065076312</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.387393907014799</v>
+        <v>-3.347616460950936</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.782776550632579</v>
+        <v>1.798687529058124</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.09682621685972786</v>
+        <v>-0.1579965564384508</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.079994807636409</v>
+        <v>3.043292603889176</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.637264587029381</v>
+        <v>-3.597487140965518</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.684597402081363</v>
+        <v>1.700508380506908</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.06056349702926461</v>
+        <v>-0.1217338366079876</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.103521562989304</v>
+        <v>3.06681935924207</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.843776363916402</v>
+        <v>-3.803998917852539</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.598098749982812</v>
+        <v>1.614009728408357</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.3282456134950091</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.975720555513349</v>
+        <v>2.939018351766115</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.163120438996904</v>
+        <v>-4.123342992933041</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.472134046650871</v>
+        <v>1.488045025076416</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2670752739162861</v>
+        <v>-0.3282456134950091</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.977493482213608</v>
+        <v>2.940791278466374</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.594926232146691</v>
+        <v>-4.555148786082828</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.28574461685836</v>
+        <v>1.301655595283905</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4034927703575531</v>
+        <v>-0.4646631099362761</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.881975871816252</v>
+        <v>2.845273668069018</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.829620226279244</v>
+        <v>-4.78984278021538</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.18015179420743</v>
+        <v>1.196062772632975</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.3971565031282979</v>
+        <v>-0.4583268427070209</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.874062407155896</v>
+        <v>2.837360203408662</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.165282873509696</v>
+        <v>-5.125505427445833</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.044467326971214</v>
+        <v>1.060378305396759</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4650874886172027</v>
+        <v>-0.5262578281959257</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.831884407518518</v>
+        <v>2.795182203771284</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.241727203712568</v>
+        <v>-5.201949757648705</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.020377155124307</v>
+        <v>1.036288133549852</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.3846419795235408</v>
+        <v>-0.4458123191022638</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.886639273208957</v>
+        <v>2.849937069461723</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.606854586351314</v>
+        <v>-5.567077140287451</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.8735807170746397</v>
+        <v>0.889491695500185</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.6809527638225534</v>
+        <v>-0.7421231034012763</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.708107317635381</v>
+        <v>2.671405113888147</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.015443363531993</v>
+        <v>-5.975665917468129</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7089067502171269</v>
+        <v>0.7248177286426727</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.150711880581955</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.461715595341733</v>
+        <v>2.425013391594499</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.129203775554858</v>
+        <v>-6.089426329490994</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6585880178794419</v>
+        <v>0.6744989963049872</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.150711880581955</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.456901027813193</v>
+        <v>2.42019882406596</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.545595649841855</v>
+        <v>-6.505818203777991</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.4900253187735202</v>
+        <v>0.5059362971990655</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.150711880581955</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.454895078422071</v>
+        <v>2.418192874674837</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.789867050568925</v>
+        <v>-6.750089604505061</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4025754491513713</v>
+        <v>0.4184864275769167</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.150711880581955</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.46515376909075</v>
+        <v>2.428451565343516</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.995118069805685</v>
+        <v>-6.955340623741821</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3165746066023623</v>
+        <v>0.332485585027908</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.150711880581955</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.461253334236445</v>
+        <v>2.424551130489212</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.043320887048029</v>
+        <v>-7.003543440984165</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2956983997604259</v>
+        <v>0.3116093781859712</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.089541541003232</v>
+        <v>-1.150711880581955</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.459658254291446</v>
+        <v>2.422956050544212</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.339982228858227</v>
+        <v>-7.300204782794363</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1808128389655548</v>
+        <v>0.1967238173911006</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.219455016315833</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.422191348780327</v>
+        <v>2.385489145033093</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.526701937167529</v>
+        <v>-7.486924491103665</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1020986511074309</v>
+        <v>0.1180096295329762</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.219455016315833</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.418165044245924</v>
+        <v>2.38146284049869</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.909703325910161</v>
+        <v>-7.869925879846297</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.05120400571120598</v>
+        <v>-0.03529302728566019</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.15828467673711</v>
+        <v>-1.219455016315833</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.41806294292434</v>
+        <v>2.381360739177106</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.914189771111549</v>
+        <v>-7.874412325047685</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.05042706782033113</v>
+        <v>-0.03451608939478534</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.223941461517222</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.417942591774937</v>
+        <v>2.381240388027703</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.273720093615552</v>
+        <v>-8.233942647551688</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1888888935238819</v>
+        <v>-0.1729779150983362</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.162771121938499</v>
+        <v>-1.223941461517222</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.423292895072987</v>
+        <v>2.386590691325753</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.324069157069774</v>
+        <v>-8.28429171100591</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.2011124989483934</v>
+        <v>-0.1852015205228477</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.213120185392721</v>
+        <v>-1.274290524971444</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.400999476957631</v>
+        <v>2.364297273210398</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.42168843449117</v>
+        <v>-8.381910988427306</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2371184592951829</v>
+        <v>-0.2212074808696372</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.310739462814118</v>
+        <v>-1.371909802392841</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.345469661126562</v>
+        <v>2.308767457379328</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.475759933999528</v>
+        <v>-8.435982487935664</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.255853502776954</v>
+        <v>-0.2399425243514086</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.364810962322477</v>
+        <v>-1.4259813019012</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.315920317743119</v>
+        <v>2.279218113995885</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.680018109329392</v>
+        <v>-8.640240663265528</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3320435757902573</v>
+        <v>-0.3161325973647116</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.553620246515189</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.208147944346134</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.713670947837866</v>
+        <v>-8.673893501774002</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3410221567092107</v>
+        <v>-0.3251111782836649</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.654033614432227</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.152382478080348</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.640201116170417</v>
+        <v>-8.600423670106553</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.29626252254881</v>
+        <v>-0.2803515441232642</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.580563782764778</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.211836078574238</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.81532553355696</v>
+        <v>-8.775548087493096</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3517570687559104</v>
+        <v>-0.3358460903303646</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.755688200151322</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.121316648889828</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.04977762757145</v>
+        <v>-9.010000181507586</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4527570712633024</v>
+        <v>-0.4368460928377567</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.755688200151322</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.114097483988232</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.114374912534032</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5011791544478572</v>
+        <v>-0.4852681760223114</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.860062931177768</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.044800454598389</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.167161068134359</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5211778268494314</v>
+        <v>-0.5052668484238856</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.955738417760165</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>1.988510952487506</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.293197861502648</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5688988155676324</v>
+        <v>-0.5529878371420867</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.930486794950423</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.006355654802467</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.236126089606717</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5420797711228591</v>
+        <v>-0.5261687926973138</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.930486794950423</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.010345990488867</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.377797931330837</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6002237347112489</v>
+        <v>-0.5843127562857036</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.930486794950423</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.008870763590126</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.328207086906003</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5653339867764431</v>
+        <v>-0.5494230083508973</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.880895950525589</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.053678680409898</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.179288752434147</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5188177866343833</v>
+        <v>-0.5029068082088379</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.849646359790416</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.059377301204319</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-8.953443599714735</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.4029896740848646</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.807719684203252</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.094112379592826</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-8.828864943377143</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.3520190669937686</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.807719684203252</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.095251524148885</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-8.881760231421429</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.3705434080493757</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.802764338114806</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.100858505964061</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-8.809627056133548</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.3359564336955869</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.802764338114806</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.106592210202697</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-8.738260663523901</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.3171471390455931</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.731397945505158</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.139674783374621</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.644801629538676</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.2896470067644108</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.731397945505158</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.129791302061713</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.377559828670279</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.1845848469164255</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.731397945505158</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.127956741562339</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.279652789993788</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.1457223464192903</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.663412195644602</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.168447876505212</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.25569924901783</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.1354724238834133</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.639458654668644</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.18348850723628</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-7.991639310695034</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.04310876471604708</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.375398716345848</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.328664154068206</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.284559687190196</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.2369360510255873</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.375398716345848</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.325877120407905</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.244375388824006</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.2533533942599049</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.335214417979657</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.350331323315461</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.080975517884643</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.3180801638564068</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.171814547040294</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.447738067099835</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-6.847494295655045</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.4193970815860988</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.9383333248106958</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.595751229275447</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-6.69782790464753</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.4763714276761455</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.8454298335681598</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.648601113708009</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390427</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.565552431016643</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.524649103875527</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.7131543599372732</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.723333884633568</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.472465250200773</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.564699036889512</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.6200671791214031</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.782001253810727</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.223465451517192</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.6772052975866032</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.6200671791214031</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.794907595034386</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.329055441290296</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.5069933720781425</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.7256571688945075</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.603577671571304</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.347790343408893</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.5480437531077902</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.7312531785546388</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.648764407652312</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.199850302001294</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.4873408469826623</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.7109322626460812</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.541078034509279</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.146880779747305</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5089641519027821</v>
+        <v>0.4998146696307795</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6579627403920923</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.564145761608194</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.103332372976615</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5194229025159651</v>
+        <v>0.5102734202439625</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6579627403920923</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.557185149513101</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.04709546081784</v>
+        <v>-6.069969166497846</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5472305394886159</v>
+        <v>0.5380810572166133</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6579627403920923</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.571647503894244</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.938836323695318</v>
+        <v>-5.961710029375324</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5850663147968196</v>
+        <v>0.575916832524817</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.6579627403920923</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.566179624353439</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.815545188878187</v>
+        <v>-5.838418894558194</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6318808627342487</v>
+        <v>0.6227313804622461</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.5346716055749619</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.637652399254294</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.794395989974744</v>
+        <v>-5.81726969565475</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6480415205329515</v>
+        <v>0.6388920382609489</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.5135224066715185</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.658042896833685</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.550630547991299</v>
+        <v>-5.573504253671306</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7413284056733795</v>
+        <v>0.7321789234013769</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.5135224066715185</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.653823605180736</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.448867727714005</v>
+        <v>-5.471741433394011</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7841578477043138</v>
+        <v>0.7750083654323112</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.5003033382790898</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.663879360136209</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.19901733376493</v>
+        <v>-5.221891039444936</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8768400802676455</v>
+        <v>0.8676905979956429</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.5003033382790898</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.656621435119911</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.023125241297498</v>
+        <v>-5.045998946977504</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9507960407752671</v>
+        <v>0.941646558503265</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.5003033382790898</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.66022055864056</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.851678778275034</v>
+        <v>-4.87455248395504</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.032702132038806</v>
+        <v>1.023552649766804</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.3288568752566267</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.776415942508592</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.777389212536695</v>
+        <v>-4.800262918216701</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.061438435950439</v>
+        <v>1.052288953678437</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.2545673095182874</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.820010159567892</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.713753470302761</v>
+        <v>-4.736627175982767</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.09158753389833</v>
+        <v>1.082438051626328</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1909315672843528</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.86288640596257</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.625200416656846</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.117352496412494</v>
+        <v>1.108203014140491</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1909315672843528</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.844080664746366</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.36189621417198</v>
+        <v>-4.384769919851986</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.215267771759315</v>
+        <v>1.206118289487313</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.04949892952050744</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>2.990082039454159</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.289653646000786</v>
+        <v>-4.312527351680791</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.248094112862613</v>
+        <v>1.238944630590611</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.04949892952050744</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>2.994011353288979</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.236655323719398</v>
+        <v>-4.259529029399403</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.269972025692508</v>
+        <v>1.260822543420506</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1048351885224463</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>3.027891692607483</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.127850438239671</v>
+        <v>-4.150724143919676</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.310492051104393</v>
+        <v>1.301342568832391</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1048351885224463</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>3.024889763827476</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.90782964020266</v>
+        <v>-3.930703345882665</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.400079407329811</v>
+        <v>1.390929925057809</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.2460550335904265</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.111200707878878</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.774961951139382</v>
+        <v>-3.797835656819387</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.469120665756946</v>
+        <v>1.459971183484944</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.2460550335904265</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.127094890680702</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.654788867774883</v>
+        <v>-3.677662573454889</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518335743543047</v>
+        <v>1.509186261271045</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.3662281169549255</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.200344585139703</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.510116722675146</v>
+        <v>-3.532990428355151</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586292704144382</v>
+        <v>1.57714322187238</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.5109002620546629</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.297235974760985</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.569991550032838</v>
+        <v>-3.592865255712844</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.548380264602731</v>
+        <v>1.539230782330729</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.4510254346969708</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.247348569747796</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.450171319122</v>
+        <v>-3.473045024802006</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.611597526201274</v>
+        <v>1.602448043929272</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.4510254346969708</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.262637738982005</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.452641025583806</v>
+        <v>-3.475514731263812</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.518253842938994</v>
+        <v>1.509104360666991</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.4485557282351646</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.168800114427362</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.521011211907816</v>
+        <v>-3.543884917587822</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.410167629894691</v>
+        <v>1.401018147622689</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.4578314272713795</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.093627395334393</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.534799264754863</v>
+        <v>-3.557672970434869</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.395089117387764</v>
+        <v>1.385939635115761</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.4578314272713795</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.084064103966284</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.565792424083568</v>
+        <v>-3.588666129763574</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.207401418696668</v>
+        <v>1.198251936424666</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.4578314272713795</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.983066563800228</v>
+        <v>2.908773669006671</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.390318164291099</v>
+        <v>-3.413191869971105</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.282158354605444</v>
+        <v>1.273008872333441</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.4578314272713795</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.987633795792016</v>
+        <v>2.913340900998459</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.501254416932348</v>
+        <v>-3.524128122612353</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.213525882310151</v>
+        <v>1.204376400038149</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.4578314272713795</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.963375824553223</v>
+        <v>2.889082929759666</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.467590871460066</v>
+        <v>-3.490464577140072</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.155529613900514</v>
+        <v>1.146380131628512</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.4914949727436614</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.912112265238041</v>
+        <v>2.837819370444485</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.407738252256343</v>
+        <v>-3.430611957936348</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.189643048014136</v>
+        <v>1.180493565742133</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.4914949727436614</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.922284651670174</v>
+        <v>2.847991756876617</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.321494789229965</v>
+        <v>-3.344368494909971</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.219086703798547</v>
+        <v>1.209937221526544</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.4914949727436614</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.917230922244034</v>
+        <v>2.842938027450477</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.366801608628945</v>
+        <v>-3.389675314308951</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.19273975148348</v>
+        <v>1.183590269211478</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.4506848097344306</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.884520599883021</v>
+        <v>2.810227705089464</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.395834713331247</v>
+        <v>-3.418708419011252</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.181678382635661</v>
+        <v>1.172528900363659</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.4506848097344306</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.885072472916123</v>
+        <v>2.810779578122566</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.430052028835363</v>
+        <v>-3.325897937560393</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.09726414832538</v>
+        <v>1.138925784835368</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5402889855529089</v>
+        <v>0.5434952911852899</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.793814775505019</v>
+        <v>2.795738558884447</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.474441498164791</v>
+        <v>-3.370287406889821</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.08138183651821</v>
+        <v>1.123043473028198</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4958995162234813</v>
+        <v>0.4991058218558623</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.769054569831963</v>
+        <v>2.770978353211391</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.361770279928541</v>
+        <v>-3.257616188653571</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.121526032324433</v>
+        <v>1.163187668834421</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6085707344597315</v>
+        <v>0.6117770400921125</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.831733009285436</v>
+        <v>2.833656792664865</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.249393278745868</v>
+        <v>-3.145239187470898</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.17196812862817</v>
+        <v>1.213629765138158</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6085707344597315</v>
+        <v>0.6117770400921125</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.837224305116103</v>
+        <v>2.839148088495532</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.277173676647221</v>
+        <v>-3.173019585372251</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.172353171236167</v>
+        <v>1.214014807746155</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5807903365583784</v>
+        <v>0.5839966421907594</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.83205326814383</v>
+        <v>2.833977051523259</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.3601749576725</v>
+        <v>-3.25602086639753</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9775083788267089</v>
+        <v>1.019170015336697</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5622194520312047</v>
+        <v>0.5654257576635857</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.659266457428179</v>
+        <v>2.661190240807608</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.468789036115831</v>
+        <v>-3.364634944840861</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.054212408168582</v>
+        <v>1.09587404467857</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5622194520312047</v>
+        <v>0.5654257576635857</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.779416118147385</v>
+        <v>2.781339901526814</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.433379997867688</v>
+        <v>-3.329225906592718</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.082889049570162</v>
+        <v>1.12455068608015</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5622194520312047</v>
+        <v>0.5654257576635857</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.793929144249708</v>
+        <v>2.795852927629137</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.394996335309537</v>
+        <v>-3.290842244034567</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.095661955935791</v>
+        <v>1.137323592445779</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6006031145893559</v>
+        <v>0.6038094202217369</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.814378783126967</v>
+        <v>2.816302566506396</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.217880005274371</v>
+        <v>-3.113725913999401</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.16323751679516</v>
+        <v>1.204899153305148</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6006031145893559</v>
+        <v>0.6038094202217369</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.811107811972269</v>
+        <v>2.813031595351698</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.262972250107917</v>
+        <v>-3.158818158832947</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.145884010623655</v>
+        <v>1.187545647133643</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5387070714199661</v>
+        <v>0.5419133770523471</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.774653577832549</v>
+        <v>2.776577361211977</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.083596828869149</v>
+        <v>-2.979442737594179</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.211421154425576</v>
+        <v>1.253082790935564</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6954838295906848</v>
+        <v>0.6986901352230658</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.862506608041394</v>
+        <v>2.864430391420823</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.128611042389756</v>
+        <v>-3.024456951114785</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.174222924348923</v>
+        <v>1.215884560858911</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6651349342760802</v>
+        <v>0.6683412399084612</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.825104726184221</v>
+        <v>2.82702850956365</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.395615552662191</v>
+        <v>-3.291461461387221</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.073112682578895</v>
+        <v>1.114774319088883</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4707718962331316</v>
+        <v>0.4739782018655126</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.714178465697398</v>
+        <v>2.716102249076827</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.496813334099364</v>
+        <v>-3.392659242824394</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.031837491900527</v>
+        <v>1.073499128410515</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4023630826878124</v>
+        <v>0.4055693883201934</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.672337099466707</v>
+        <v>2.674260882846136</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.490302367485051</v>
+        <v>-3.386148276210081</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.032041840100569</v>
+        <v>1.073703476610557</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4023630826878124</v>
+        <v>0.4055693883201934</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.669937061021024</v>
+        <v>2.671860844400453</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.471264239777754</v>
+        <v>-3.367110148502784</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.036181810391733</v>
+        <v>1.077843446901721</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3441794713566179</v>
+        <v>0.3473857769889989</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.631551613430553</v>
+        <v>2.633475396809981</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.502390870928372</v>
+        <v>-3.398236779653402</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.201313026870166</v>
+        <v>1.242974663380154</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3441794713566179</v>
+        <v>0.3473857769889989</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.809133482369233</v>
+        <v>2.811057265748662</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.516257632262289</v>
+        <v>-3.412103540987319</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.196599651322733</v>
+        <v>1.238261287832721</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3063215546227949</v>
+        <v>0.3095278602551759</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.787252061315073</v>
+        <v>2.789175844694502</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.471453460722359</v>
+        <v>-3.367299369447389</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.220529850335631</v>
+        <v>1.262191486845619</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3063215546227949</v>
+        <v>0.3095278602551759</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.793260591711999</v>
+        <v>2.795184375091428</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.323710490487357</v>
+        <v>-3.219556399212387</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.177577259706831</v>
+        <v>1.219238896216819</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4741289118576781</v>
+        <v>0.4773352174900591</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.791895227330128</v>
+        <v>2.793819010709557</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.425725173018578</v>
+        <v>-3.321571081743608</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.139565008225824</v>
+        <v>1.181226644735812</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4741289118576781</v>
+        <v>0.4773352174900591</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.794688848861609</v>
+        <v>2.796612632241038</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.419572466965794</v>
+        <v>-3.315418375690824</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.142688439038596</v>
+        <v>1.184350075548584</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4802816179104624</v>
+        <v>0.4834879235428434</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.799042820884938</v>
+        <v>2.800966604264367</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.436381765116295</v>
+        <v>-3.332227673841325</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.135045196518505</v>
+        <v>1.176706833028494</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4634723197599607</v>
+        <v>0.4666786253923417</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.788037718734747</v>
+        <v>2.789961502114176</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.374083766340173</v>
+        <v>-3.269929675065203</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.226299949825775</v>
+        <v>1.267961586335763</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4634723197599607</v>
+        <v>0.4666786253923417</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.854373272531568</v>
+        <v>2.856297055910997</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.172293568675015</v>
+        <v>-3.068139477400045</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.109308030605965</v>
+        <v>1.150969667115953</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6614905119291151</v>
+        <v>0.6646968175614961</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.775476189547188</v>
+        <v>2.777399972926617</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.007480565596168</v>
+        <v>-2.903326474321198</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.245523464159679</v>
+        <v>1.287185100669668</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8263035150079621</v>
+        <v>0.8295098206403431</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.944654223716671</v>
+        <v>2.9465780070961</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.105221110221143</v>
+        <v>-3.001067018946173</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.221054982425733</v>
+        <v>1.262716618935721</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8104142368749818</v>
+        <v>0.8136205425073628</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.949748392952927</v>
+        <v>2.951672176332355</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.281558870344072</v>
+        <v>-3.177404779069102</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.149055859201233</v>
+        <v>1.190717495711221</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6340764767520524</v>
+        <v>0.6372827823844334</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.842481717703841</v>
+        <v>2.84440550108327</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.205136823912145</v>
+        <v>-3.100982732637175</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.178116295813932</v>
+        <v>1.21977793232392</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6340764767520524</v>
+        <v>0.6372827823844334</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.84097333574377</v>
+        <v>2.842897119123198</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.160763692273576</v>
+        <v>-3.056609600998606</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.195728415904796</v>
+        <v>1.237390052414784</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.678449608390621</v>
+        <v>0.681655914023002</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.867460082162347</v>
+        <v>2.869383865541775</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.037929471386409</v>
+        <v>-2.933775380111439</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.239255898398254</v>
+        <v>1.280917534908242</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.678449608390621</v>
+        <v>0.681655914023002</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.861853876300937</v>
+        <v>2.863777659680366</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.990273740825353</v>
+        <v>-2.886119649550383</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.264699947650481</v>
+        <v>1.306361584160469</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7261053389516766</v>
+        <v>0.7293116445840576</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.896829071665375</v>
+        <v>2.898752855044804</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.889755582326599</v>
+        <v>-2.785601491051628</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.309799584424707</v>
+        <v>1.351461220934695</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8266234974504312</v>
+        <v>0.8298298030828122</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.962032340139353</v>
+        <v>2.963956123518781</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.950422172728988</v>
+        <v>-2.846268081454018</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.272287620739624</v>
+        <v>1.313949257249612</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7449251807318975</v>
+        <v>0.7481314863642785</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.899768022584105</v>
+        <v>2.901691805963534</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.90558377112059</v>
+        <v>-2.80142967984562</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.294320683993612</v>
+        <v>1.3359823205036</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.749468613676767</v>
+        <v>0.752674919309148</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.906591784961655</v>
+        <v>2.908515568341084</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.006342406877588</v>
+        <v>-2.902188315602618</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.25817816932189</v>
+        <v>1.299839805831878</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6606430449497616</v>
+        <v>0.6638493505821426</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.85745738335653</v>
+        <v>2.859381166735958</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.962139569791688</v>
+        <v>-2.857985478516718</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.281738906684088</v>
+        <v>1.323400543194076</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.704845882035662</v>
+        <v>0.708052187668043</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.889858688135907</v>
+        <v>2.891782471515336</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.999118597455131</v>
+        <v>-2.894964506180161</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.265357296087958</v>
+        <v>1.307018932597946</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7418197838269925</v>
+        <v>0.7450260894593735</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.910453029679953</v>
+        <v>2.912376813059382</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284878</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.840827179915859</v>
+        <v>-2.736673088640889</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.379921628286706</v>
+        <v>1.421583264796694</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7418197838269925</v>
+        <v>0.7450260894593735</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.961700794862993</v>
+        <v>2.963624578242421</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.633185176281382</v>
+        <v>-2.529031085006412</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.46141913433475</v>
+        <v>1.503080770844738</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9494617874614687</v>
+        <v>0.9526680930938497</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.084726701637932</v>
+        <v>3.08665048501736</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475136</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.582153083558854</v>
+        <v>-2.477998992283884</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.476780199662031</v>
+        <v>1.518441836172019</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.000493880183997</v>
+        <v>1.003700185816378</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.110294185509718</v>
+        <v>3.112217968889147</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.516928902431649</v>
+        <v>-2.412774811156678</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.520057276205619</v>
+        <v>1.561718912715607</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.065718061311202</v>
+        <v>1.068924366943583</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.166616098278747</v>
+        <v>3.168539881658175</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.479501882360515</v>
+        <v>-2.375347791085545</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.530989056533352</v>
+        <v>1.57265069304334</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.070969599340384</v>
+        <v>1.074175904972765</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.165727993395536</v>
+        <v>3.167651776774965</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.499613538395223</v>
+        <v>-2.395459447120253</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.524201186450709</v>
+        <v>1.565862822960697</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.081996944337803</v>
+        <v>1.085203249970184</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.173601192725228</v>
+        <v>3.175524976104657</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.445868723968018</v>
+        <v>-2.341714632693048</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.706256883242802</v>
+        <v>1.74791851975279</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.092060253778265</v>
+        <v>1.095266559410646</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.340196949410716</v>
+        <v>3.342120732790145</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.371086462943006</v>
+        <v>-2.266932371668036</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.856282696870624</v>
+        <v>1.897944333380612</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.166842514803278</v>
+        <v>1.170048820435659</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.505179215243541</v>
+        <v>3.507102998622969</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.345002378679198</v>
+        <v>-2.240848287404228</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.858424306590007</v>
+        <v>1.900085943099994</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.166842514803278</v>
+        <v>1.170048820435659</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.4968871912574</v>
+        <v>3.498810974636828</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.266871197830251</v>
+        <v>-2.162717106555281</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.887869974513365</v>
+        <v>1.929531611023353</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.241019325686962</v>
+        <v>1.244225631319344</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.53958647337139</v>
+        <v>3.541510256750819</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.257978736436968</v>
+        <v>-2.153824645161998</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.908981364797469</v>
+        <v>1.950643001307457</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.241019325686962</v>
+        <v>1.244225631319344</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.557140879098181</v>
+        <v>3.55906466247761</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.426454853406846</v>
+        <v>-2.322300762131876</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.833445965414102</v>
+        <v>1.87510760192409</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.213071489970382</v>
+        <v>1.216277795602763</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.532227225072817</v>
+        <v>3.534151008452246</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.728655324545262</v>
+        <v>-1.624501233270292</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.093835474146597</v>
+        <v>2.135497110656585</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.142723430599971</v>
+        <v>1.145929736232352</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.471288086638432</v>
+        <v>3.473211870017861</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.70593422086211</v>
+        <v>-1.60178012958714</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.093587938116763</v>
+        <v>2.135249574626751</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.142723430599971</v>
+        <v>1.145929736232352</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.461952109135337</v>
+        <v>3.463875892514765</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.704209177572066</v>
+        <v>-1.600055086297096</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.253184081283949</v>
+        <v>2.294845717793937</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.144448473890015</v>
+        <v>1.147654779522396</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.621893260960532</v>
+        <v>3.623817044339961</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.858990184350322</v>
+        <v>-1.754836093075351</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.228349501066294</v>
+        <v>2.270011137576282</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.111080799835539</v>
+        <v>1.11428710546792</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.638950479021493</v>
+        <v>3.640874262400922</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.851935494135148</v>
+        <v>-1.747781402860178</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.227846733141909</v>
+        <v>2.269508369651896</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.118135490050712</v>
+        <v>1.121341795683094</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.639858649140142</v>
+        <v>3.641782432519571</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.82498426980866</v>
+        <v>-1.72083017853369</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.248633376517245</v>
+        <v>2.290295013027233</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.133015836078431</v>
+        <v>1.136222141710813</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.658793010401515</v>
+        <v>3.660716793780944</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.960937277864976</v>
+        <v>-1.856783186590006</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.378355305439678</v>
+        <v>2.420016941949667</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.133015836078431</v>
+        <v>1.136222141710813</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.842896142546475</v>
+        <v>3.844819925925904</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.983345395669848</v>
+        <v>-1.879191304394878</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.361508753220723</v>
+        <v>2.403170389730711</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.133015836078431</v>
+        <v>1.136222141710813</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.835012837449468</v>
+        <v>3.836936620828897</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.131351163149247</v>
+        <v>-2.027197071874277</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.3043604457786</v>
+        <v>2.346022082288588</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.04628882721489</v>
+        <v>1.049495132847271</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.785030631680981</v>
+        <v>3.78695441506041</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.140792089037777</v>
+        <v>-2.036637997762807</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.356837793145035</v>
+        <v>2.398499429655024</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.168715944758282</v>
+        <v>1.171922250390663</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.914740619928863</v>
+        <v>3.916664403308292</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.193065696373419</v>
+        <v>-2.088911605098449</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.33881944475608</v>
+        <v>2.380481081266068</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.11644233742264</v>
+        <v>1.119648643055021</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.886267550072779</v>
+        <v>3.888191333452208</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.269395673974325</v>
+        <v>-2.165241582699355</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.306399266609493</v>
+        <v>2.348060903119481</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.11644233742264</v>
+        <v>1.119648643055021</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.884379362966554</v>
+        <v>3.886303146345983</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.381152626589626</v>
+        <v>-2.276998535314656</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.256516715166235</v>
+        <v>2.298178351676222</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.004685384807339</v>
+        <v>1.00789169043972</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.812145421000236</v>
+        <v>3.814069204379665</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.379311607531374</v>
+        <v>-2.275157516256404</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.255687132999687</v>
+        <v>2.297348769509675</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.005953611478807</v>
+        <v>1.009159917111189</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.811340367213269</v>
+        <v>3.813264150592698</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.511612899628928</v>
+        <v>-2.407458808353958</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.215840023026585</v>
+        <v>2.257501659536573</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.005953611478807</v>
+        <v>1.009159917111189</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.824413774079188</v>
+        <v>3.826337557458617</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.513174542443788</v>
+        <v>-2.409020451168818</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.215215365900641</v>
+        <v>2.256877002410629</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.005953611478807</v>
+        <v>1.009159917111189</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.824413774079188</v>
+        <v>3.826337557458617</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.541075329553261</v>
+        <v>-2.436921238278291</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.202579092183854</v>
+        <v>2.244240728693842</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9713566873358727</v>
+        <v>0.9745629929682539</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.802179660720429</v>
+        <v>3.804103444099858</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172526</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.663601432256155</v>
+        <v>-2.559447340981185</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.150333095079895</v>
+        <v>2.191994731589883</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8488305846329788</v>
+        <v>0.85203689026536</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.725428443075891</v>
+        <v>3.72735222645532</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971078</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.683662753532662</v>
+        <v>-2.579508662257691</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.209014526159796</v>
+        <v>2.250676162669784</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8287692633564718</v>
+        <v>0.8319755689888531</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.780097609900491</v>
+        <v>3.78202139327992</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199803</v>
+        <v>3.640764248199805</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.940383571527486</v>
+        <v>-2.836229480252515</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.246637917963713</v>
+        <v>2.288299554473701</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.720354689212657</v>
+        <v>0.7235609948450382</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.855360584416049</v>
+        <v>3.857284367795478</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622234</v>
+        <v>3.668303164622236</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.094369989303626</v>
+        <v>-2.990215898028656</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.254023619998897</v>
+        <v>2.295685256508885</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.720354689212657</v>
+        <v>0.7235609948450382</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.924340853561689</v>
+        <v>3.926264636941117</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808526</v>
+        <v>3.619937176808528</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.04384808547596</v>
+        <v>-2.93969399420099</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.260283583650084</v>
+        <v>2.301945220160072</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.720354689212657</v>
+        <v>0.7235609948450382</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.91039205568181</v>
+        <v>3.912315839061239</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994891</v>
+        <v>3.656346893994893</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.296323239483685</v>
+        <v>-3.192169148208714</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.171164011102408</v>
+        <v>2.212825647612396</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.720354689212657</v>
+        <v>0.7235609948450382</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.922262544737224</v>
+        <v>3.924186328116653</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358295</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.565796041405393</v>
+        <v>-3.461641950130423</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.064585424852669</v>
+        <v>2.106247061362657</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.720354689212657</v>
+        <v>0.7235609948450382</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.923473079256167</v>
+        <v>3.925396862635596</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637083</v>
+        <v>3.663523617637085</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.723340113134834</v>
+        <v>-3.619186021859864</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.005689538388213</v>
+        <v>2.047351174898202</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6534528840723826</v>
+        <v>0.6566591897047638</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.887453738399324</v>
+        <v>3.889377521778753</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.65216331330134</v>
+        <v>3.652163313301342</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.85219066383688</v>
+        <v>-3.74803657256191</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.949227170843584</v>
+        <v>1.990888807353572</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.612459475221661</v>
+        <v>0.6156657808540422</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.857935545825081</v>
+        <v>3.85985932920451</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.969158356475771</v>
+        <v>-3.865004265200801</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.064644150487072</v>
+        <v>2.10630578699706</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.612459475221661</v>
+        <v>0.6156657808540422</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.020139602524125</v>
+        <v>4.022063385903554</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456689</v>
+        <v>3.696553628456691</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.053876298696725</v>
+        <v>-3.949722207421755</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.025603611562505</v>
+        <v>2.067265248072493</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5273434462936146</v>
+        <v>0.5305497519259958</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.963916623131111</v>
+        <v>3.96584040651054</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253287</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.135811116965608</v>
+        <v>-4.031657025690638</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.003059101823442</v>
+        <v>2.044720738333431</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5174087007065344</v>
+        <v>0.5206150063389157</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.968185193347354</v>
+        <v>3.970108976726783</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717831</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.082072943565346</v>
+        <v>-3.977918852290376</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.03348000963945</v>
+        <v>2.075141646149438</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.5711468741067965</v>
+        <v>0.5743531797391778</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.009353735843414</v>
+        <v>4.011277519222842</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616947</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.972066660088124</v>
+        <v>-3.867912568813154</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.069635410274514</v>
+        <v>2.111297046784502</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5943514460240718</v>
+        <v>0.597557751656453</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.015429366237955</v>
+        <v>4.017353149617383</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203661</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.829007084347199</v>
+        <v>-3.724852993072229</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.131109251292858</v>
+        <v>2.172770887802847</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.602364872614051</v>
+        <v>0.6055711782464323</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.024487432913916</v>
+        <v>4.026411216293345</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.527560358875362</v>
+        <v>-3.363316328820813</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.258948824364129</v>
+        <v>2.324646436385949</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.9038115980858883</v>
+        <v>0.9671078424978474</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.212616351079554</v>
+        <v>4.25059409772673</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.507155144905421</v>
+        <v>3.770982935628746</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.459661610718886</v>
+        <v>3.603725766449164</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.527560358875362</v>
+        <v>-3.363316328820813</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.258948824364129</v>
+        <v>2.324646436385949</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.9038115980858883</v>
+        <v>0.9671078424978474</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.452725407705254</v>
+        <v>3.596789563435531</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240719.xlsx
+++ b/tame_output/ON/bt/strategyON_20240719.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>49.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -844,37 +844,37 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>37.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-72.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.9%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.1%</t>
+          <t>122.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.5%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-640.6%</t>
+          <t>-644.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.8%</t>
+          <t>-48.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.8%</t>
+          <t>-68.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.3%</t>
+          <t>455.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-497.9%</t>
+          <t>-512.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-256.6%</t>
+          <t>-258.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.7%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>115.4%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-143.8%</t>
+          <t>-149.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-269.8%</t>
+          <t>-263.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-133.0%</t>
+          <t>-137.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-127.3%</t>
+          <t>-135.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.4%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>48.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-162.3%</t>
+          <t>-158.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-24.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.4%</t>
+          <t>-16.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-86.3%</t>
+          <t>-97.1%</t>
         </is>
       </c>
     </row>
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.1267217999702719</v>
+        <v>0.1878921395489951</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.172902467787304</v>
+        <v>3.197370603618793</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.507770035031599</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.027232193131902</v>
+        <v>4.063934396879136</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386091</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>-0.009461906236936657</v>
+        <v>-0.04923935230080001</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.153370069801962</v>
+        <v>3.137459091376417</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.507770035031599</v>
+        <v>1.568940374610322</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.062173277629444</v>
+        <v>4.098875481376678</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.367370539998558</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>-0.00442431550935013</v>
+        <v>-0.04420176157321348</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.153962546278335</v>
+        <v>3.13805156785279</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.563414491297916</v>
+        <v>1.62458483087664</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.094137391574573</v>
+        <v>4.130839595321806</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>-0.2616183502174069</v>
+        <v>-0.3013957962812702</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.02983131401885</v>
+        <v>3.013920335593304</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.30622045658986</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1841" t="n">
-        <v>3.918567352373476</v>
+        <v>3.95526955612071</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>-0.3273857402668189</v>
+        <v>-0.3671631863306823</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.004541967129555</v>
+        <v>2.988630988704009</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.30622045658986</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1842" t="n">
-        <v>3.919584961503945</v>
+        <v>3.95628716525118</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>-0.5326304173240635</v>
+        <v>-0.5724078633879268</v>
       </c>
       <c r="E1843" t="n">
-        <v>2.913072128294413</v>
+        <v>2.897161149868867</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.30622045658986</v>
+        <v>1.367390796168583</v>
       </c>
       <c r="G1843" t="n">
-        <v>3.910212993491701</v>
+        <v>3.946915197238935</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.6144023177518152</v>
+        <v>-0.6541797638156785</v>
       </c>
       <c r="E1844" t="n">
-        <v>2.87044609407855</v>
+        <v>2.854535115653005</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.333256029995996</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1844" t="n">
-        <v>3.916517063490621</v>
+        <v>3.953219267237856</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.6816114256236929</v>
+        <v>-0.7213888716875563</v>
       </c>
       <c r="E1845" t="n">
-        <v>2.848327767763501</v>
+        <v>2.832416789337956</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.333256029995996</v>
+        <v>1.394426369574719</v>
       </c>
       <c r="G1845" t="n">
-        <v>3.921282380324324</v>
+        <v>3.957984584071558</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.6702221889688915</v>
+        <v>-0.7099996350327549</v>
       </c>
       <c r="E1846" t="n">
-        <v>2.850708258544662</v>
+        <v>2.834797280119117</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.344645266650798</v>
+        <v>1.405815606229521</v>
       </c>
       <c r="G1846" t="n">
-        <v>3.925940718436445</v>
+        <v>3.962642922183679</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-1.087976212515729</v>
+        <v>-1.127753658579592</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.681533540630991</v>
+        <v>2.665622562205445</v>
       </c>
       <c r="F1847" t="n">
-        <v>0.9268912431039608</v>
+        <v>0.9880615826826838</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.673215195813406</v>
+        <v>3.70991739956064</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-1.37810787912116</v>
+        <v>-1.417885325185023</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.56534709058774</v>
+        <v>2.549436112162195</v>
       </c>
       <c r="F1848" t="n">
-        <v>0.9509730378441407</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.687530489256436</v>
+        <v>3.72423269300367</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.586111937474237</v>
+        <v>-1.625889383538101</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.487037611800434</v>
+        <v>2.471126633374889</v>
       </c>
       <c r="F1849" t="n">
-        <v>0.9509730378441407</v>
+        <v>1.012143377422864</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.692422633810361</v>
+        <v>3.729124837557595</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.648290348635207</v>
+        <v>-1.688067794699071</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.457247703674034</v>
+        <v>2.441336725248489</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8887946266831706</v>
+        <v>0.9499649662618935</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.650197043451767</v>
+        <v>3.686899247199001</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-2.01435907577986</v>
+        <v>-2.054136521843724</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.303904512122622</v>
+        <v>2.287993533697077</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5227258995385179</v>
+        <v>0.5838962391172409</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.423640106471424</v>
+        <v>3.460342310218659</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.222849857231545</v>
+        <v>-2.262627303295408</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.240846489280717</v>
+        <v>2.224935510855171</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3142351180868335</v>
+        <v>0.3754054576655564</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.318883927339182</v>
+        <v>3.355586131086416</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.470051041996767</v>
+        <v>-2.50982848806063</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.150064765783196</v>
+        <v>2.134153787357651</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.3343884715856459</v>
+        <v>0.3955588111643689</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.339074689847038</v>
+        <v>3.375776893594272</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.962436070020864</v>
+        <v>-3.002213516084727</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.95421714661729</v>
+        <v>1.938306168191745</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.1579965564384508</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.044750065076312</v>
+        <v>3.081452268823546</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.347616460950936</v>
+        <v>-3.387393907014799</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.798687529058124</v>
+        <v>1.782776550632579</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.1579965564384508</v>
+        <v>-0.09682621685972786</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.043292603889176</v>
+        <v>3.079994807636409</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.597487140965518</v>
+        <v>-3.637264587029381</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.700508380506908</v>
+        <v>1.684597402081363</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.1217338366079876</v>
+        <v>-0.06056349702926461</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.06681935924207</v>
+        <v>3.103521562989304</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.803998917852539</v>
+        <v>-3.843776363916402</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.614009728408357</v>
+        <v>1.598098749982812</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3282456134950091</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.939018351766115</v>
+        <v>2.975720555513349</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.123342992933041</v>
+        <v>-4.163120438996904</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.488045025076416</v>
+        <v>1.472134046650871</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3282456134950091</v>
+        <v>-0.2670752739162861</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.940791278466374</v>
+        <v>2.977493482213608</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.555148786082828</v>
+        <v>-4.594926232146691</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.301655595283905</v>
+        <v>1.28574461685836</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4646631099362761</v>
+        <v>-0.4034927703575531</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.845273668069018</v>
+        <v>2.881975871816252</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.78984278021538</v>
+        <v>-4.829620226279244</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.196062772632975</v>
+        <v>1.18015179420743</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.4583268427070209</v>
+        <v>-0.3971565031282979</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.837360203408662</v>
+        <v>2.874062407155896</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.125505427445833</v>
+        <v>-5.165282873509696</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.060378305396759</v>
+        <v>1.044467326971214</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5262578281959257</v>
+        <v>-0.4650874886172027</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.795182203771284</v>
+        <v>2.831884407518518</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.201949757648705</v>
+        <v>-5.241727203712568</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.036288133549852</v>
+        <v>1.020377155124307</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.4458123191022638</v>
+        <v>-0.3846419795235408</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.849937069461723</v>
+        <v>2.886639273208957</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.567077140287451</v>
+        <v>-5.606854586351314</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.889491695500185</v>
+        <v>0.8735807170746397</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7421231034012763</v>
+        <v>-0.6809527638225534</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.671405113888147</v>
+        <v>2.708107317635381</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.975665917468129</v>
+        <v>-6.015443363531993</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7248177286426727</v>
+        <v>0.7089067502171269</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.150711880581955</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.425013391594499</v>
+        <v>2.461715595341733</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.089426329490994</v>
+        <v>-6.129203775554858</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.6744989963049872</v>
+        <v>0.6585880178794419</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.150711880581955</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.42019882406596</v>
+        <v>2.456901027813193</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.505818203777991</v>
+        <v>-6.545595649841855</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5059362971990655</v>
+        <v>0.4900253187735202</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.150711880581955</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.418192874674837</v>
+        <v>2.454895078422071</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.750089604505061</v>
+        <v>-6.789867050568925</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4184864275769167</v>
+        <v>0.4025754491513713</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.150711880581955</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.428451565343516</v>
+        <v>2.46515376909075</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.955340623741821</v>
+        <v>-6.995118069805685</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.332485585027908</v>
+        <v>0.3165746066023623</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.150711880581955</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.424551130489212</v>
+        <v>2.461253334236445</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.003543440984165</v>
+        <v>-7.043320887048029</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3116093781859712</v>
+        <v>0.2956983997604259</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.150711880581955</v>
+        <v>-1.089541541003232</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.422956050544212</v>
+        <v>2.459658254291446</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.300204782794363</v>
+        <v>-7.339982228858227</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1967238173911006</v>
+        <v>0.1808128389655548</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.219455016315833</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.385489145033093</v>
+        <v>2.422191348780327</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.486924491103665</v>
+        <v>-7.526701937167529</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1180096295329762</v>
+        <v>0.1020986511074309</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.219455016315833</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.38146284049869</v>
+        <v>2.418165044245924</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.869925879846297</v>
+        <v>-7.909703325910161</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.03529302728566019</v>
+        <v>-0.05120400571120598</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.219455016315833</v>
+        <v>-1.15828467673711</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.381360739177106</v>
+        <v>2.41806294292434</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.874412325047685</v>
+        <v>-7.914189771111549</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.03451608939478534</v>
+        <v>-0.05042706782033113</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.223941461517222</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.381240388027703</v>
+        <v>2.417942591774937</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.233942647551688</v>
+        <v>-8.273720093615552</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1729779150983362</v>
+        <v>-0.1888888935238819</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.223941461517222</v>
+        <v>-1.162771121938499</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.386590691325753</v>
+        <v>2.423292895072987</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.28429171100591</v>
+        <v>-8.324069157069774</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1852015205228477</v>
+        <v>-0.2011124989483934</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.274290524971444</v>
+        <v>-1.213120185392721</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.364297273210398</v>
+        <v>2.400999476957631</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.381910988427306</v>
+        <v>-8.42168843449117</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2212074808696372</v>
+        <v>-0.2371184592951829</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.371909802392841</v>
+        <v>-1.310739462814118</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.308767457379328</v>
+        <v>2.345469661126562</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.435982487935664</v>
+        <v>-8.475759933999528</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2399425243514086</v>
+        <v>-0.255853502776954</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.4259813019012</v>
+        <v>-1.364810962322477</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.279218113995885</v>
+        <v>2.315920317743119</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.640240663265528</v>
+        <v>-8.680018109329392</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3161325973647116</v>
+        <v>-0.3320435757902573</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.553620246515189</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.208147944346134</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.673893501774002</v>
+        <v>-8.713670947837866</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3251111782836649</v>
+        <v>-0.3410221567092107</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.654033614432227</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.152382478080348</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.600423670106553</v>
+        <v>-8.640201116170417</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2803515441232642</v>
+        <v>-0.29626252254881</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.580563782764778</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.211836078574238</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.775548087493096</v>
+        <v>-8.81532553355696</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3358460903303646</v>
+        <v>-0.3517570687559104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.755688200151322</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.121316648889828</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.010000181507586</v>
+        <v>-9.04977762757145</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4368460928377567</v>
+        <v>-0.4527570712633024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.755688200151322</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.114097483988232</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.114374912534032</v>
+        <v>-9.154152358597896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4852681760223114</v>
+        <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.860062931177768</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.044800454598389</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.167161068134359</v>
+        <v>-9.206938514198223</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5052668484238856</v>
+        <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.955738417760165</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.988510952487506</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.293197861502648</v>
+        <v>-9.332975307566512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5529878371420867</v>
+        <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.930486794950423</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.006355654802467</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.236126089606717</v>
+        <v>-9.275903535670581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5261687926973138</v>
+        <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.930486794950423</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.010345990488867</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.377797931330837</v>
+        <v>-9.417575377394702</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5843127562857036</v>
+        <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.930486794950423</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.008870763590126</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.328207086906003</v>
+        <v>-9.367984532969867</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5494230083508973</v>
+        <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.880895950525589</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.053678680409898</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.179288752434147</v>
+        <v>-9.219066198498011</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5029068082088379</v>
+        <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.849646359790416</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.059377301204319</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.953443599714735</v>
+        <v>-8.993221045778601</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4029896740848646</v>
+        <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.807719684203252</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.094112379592826</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.828864943377143</v>
+        <v>-8.868642389441009</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3520190669937686</v>
+        <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.807719684203252</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.095251524148885</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.881760231421429</v>
+        <v>-8.921537677485295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3705434080493757</v>
+        <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.802764338114806</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.100858505964061</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.809627056133548</v>
+        <v>-8.849404502197414</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3359564336955869</v>
+        <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.802764338114806</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.106592210202697</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.738260663523901</v>
+        <v>-8.778038109587767</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3171471390455931</v>
+        <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.731397945505158</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.139674783374621</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.644801629538676</v>
+        <v>-8.684579075602542</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2896470067644108</v>
+        <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.731397945505158</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.129791302061713</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.377559828670279</v>
+        <v>-8.417337274734145</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1845848469164255</v>
+        <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.731397945505158</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.127956741562339</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.279652789993788</v>
+        <v>-8.319430236057654</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1457223464192903</v>
+        <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.663412195644602</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.168447876505212</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.25569924901783</v>
+        <v>-8.295476695081696</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1354724238834133</v>
+        <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.639458654668644</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.18348850723628</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.991639310695034</v>
+        <v>-8.031416756758899</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.04310876471604708</v>
+        <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.375398716345848</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.328664154068206</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.284559687190196</v>
+        <v>-7.324337133254061</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2369360510255873</v>
+        <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.375398716345848</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.325877120407905</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.244375388824006</v>
+        <v>-7.284152834887871</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2533533942599049</v>
+        <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.335214417979657</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.350331323315461</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.080975517884643</v>
+        <v>-7.120752963948508</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3180801638564068</v>
+        <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.171814547040294</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.447738067099835</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.847494295655045</v>
+        <v>-6.88727174171891</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4193970815860988</v>
+        <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9383333248106958</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.595751229275447</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.69782790464753</v>
+        <v>-6.737605350711394</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4763714276761455</v>
+        <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8454298335681598</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.648601113708009</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.565552431016643</v>
+        <v>-6.605329877080508</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.524649103875527</v>
+        <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7131543599372732</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.723333884633568</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.472465250200773</v>
+        <v>-6.449591544520766</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.564699036889512</v>
+        <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6200671791214031</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.782001253810727</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.223465451517192</v>
+        <v>-6.200591745837185</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6772052975866032</v>
+        <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6200671791214031</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.794907595034386</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.329055441290296</v>
+        <v>-6.30618173561029</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5069933720781425</v>
+        <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.7256571688945075</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.603577671571304</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.347790343408893</v>
+        <v>-6.324916637728887</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5480437531077902</v>
+        <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.7312531785546388</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.648764407652312</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.199850302001294</v>
+        <v>-6.176976596321287</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4873408469826623</v>
+        <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.7109322626460812</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.541078034509279</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.146880779747305</v>
+        <v>-6.124007074067299</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4998146696307795</v>
+        <v>0.5089641519027821</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.6579627403920923</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.564145761608194</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.103332372976615</v>
+        <v>-6.080458667296608</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5102734202439625</v>
+        <v>0.5194229025159651</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.6579627403920923</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.557185149513101</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.069969166497846</v>
+        <v>-6.04709546081784</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5380810572166133</v>
+        <v>0.5472305394886159</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.6579627403920923</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.571647503894244</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.961710029375324</v>
+        <v>-5.938836323695318</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.575916832524817</v>
+        <v>0.5850663147968196</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.6579627403920923</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.566179624353439</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.838418894558194</v>
+        <v>-5.815545188878187</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6227313804622461</v>
+        <v>0.6318808627342487</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.5346716055749619</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.637652399254294</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.81726969565475</v>
+        <v>-5.794395989974744</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6388920382609489</v>
+        <v>0.6480415205329515</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.5135224066715185</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.658042896833685</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.573504253671306</v>
+        <v>-5.550630547991299</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7321789234013769</v>
+        <v>0.7413284056733795</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.5135224066715185</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.653823605180736</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.471741433394011</v>
+        <v>-5.448867727714005</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7750083654323112</v>
+        <v>0.7841578477043138</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.5003033382790898</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.663879360136209</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.221891039444936</v>
+        <v>-5.19901733376493</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8676905979956429</v>
+        <v>0.8768400802676455</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.5003033382790898</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.656621435119911</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.045998946977504</v>
+        <v>-5.023125241297498</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.941646558503265</v>
+        <v>0.9507960407752671</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.5003033382790898</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.66022055864056</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.87455248395504</v>
+        <v>-4.851678778275034</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.023552649766804</v>
+        <v>1.032702132038806</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.3288568752566267</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.776415942508592</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.800262918216701</v>
+        <v>-4.777389212536695</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.052288953678437</v>
+        <v>1.061438435950439</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.2545673095182874</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.820010159567892</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.736627175982767</v>
+        <v>-4.713753470302761</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.082438051626328</v>
+        <v>1.09158753389833</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1909315672843528</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.86288640596257</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.625200416656846</v>
+        <v>-4.602326710976841</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.108203014140491</v>
+        <v>1.117352496412494</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1909315672843528</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.844080664746366</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.384769919851986</v>
+        <v>-4.36189621417198</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.206118289487313</v>
+        <v>1.215267771759315</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.04949892952050744</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.990082039454159</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.312527351680791</v>
+        <v>-4.289653646000786</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.238944630590611</v>
+        <v>1.248094112862613</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.04949892952050744</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.994011353288979</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.259529029399403</v>
+        <v>-4.236655323719398</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.260822543420506</v>
+        <v>1.269972025692508</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1048351885224463</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.027891692607483</v>
+        <v>3.10218458740104</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.150724143919676</v>
+        <v>-4.127850438239671</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.301342568832391</v>
+        <v>1.310492051104393</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1048351885224463</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.024889763827476</v>
+        <v>3.099182658621033</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.930703345882665</v>
+        <v>-3.90782964020266</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.390929925057809</v>
+        <v>1.400079407329811</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2460550335904265</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.111200707878878</v>
+        <v>3.185493602672435</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.797835656819387</v>
+        <v>-3.774961951139382</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.459971183484944</v>
+        <v>1.469120665756946</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2460550335904265</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.127094890680702</v>
+        <v>3.201387785474259</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.677662573454889</v>
+        <v>-3.654788867774883</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.509186261271045</v>
+        <v>1.518335743543047</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3662281169549255</v>
+        <v>0.4900496082775201</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.200344585139703</v>
+        <v>3.27463747993326</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.532990428355151</v>
+        <v>-3.510116722675146</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.57714322187238</v>
+        <v>1.586292704144382</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5109002620546629</v>
+        <v>0.6347217533772576</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.297235974760985</v>
+        <v>3.371528869554542</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.592865255712844</v>
+        <v>-3.569991550032838</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.539230782330729</v>
+        <v>1.548380264602731</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.4510254346969708</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.247348569747796</v>
+        <v>3.321641464541353</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.473045024802006</v>
+        <v>-3.450171319122</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.602448043929272</v>
+        <v>1.611597526201274</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.4510254346969708</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.262637738982005</v>
+        <v>3.336930633775562</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.475514731263812</v>
+        <v>-3.452641025583806</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.509104360666991</v>
+        <v>1.518253842938994</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4485557282351646</v>
+        <v>0.5723772195577592</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.168800114427362</v>
+        <v>3.243093009220919</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.543884917587822</v>
+        <v>-3.521011211907816</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.401018147622689</v>
+        <v>1.410167629894691</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.4578314272713795</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.093627395334393</v>
+        <v>3.16792029012795</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.557672970434869</v>
+        <v>-3.534799264754863</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.385939635115761</v>
+        <v>1.395089117387764</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.4578314272713795</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.084064103966284</v>
+        <v>3.158356998759841</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.588666129763574</v>
+        <v>-3.565792424083568</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.198251936424666</v>
+        <v>1.207401418696668</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.4578314272713795</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.908773669006671</v>
+        <v>2.983066563800228</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.413191869971105</v>
+        <v>-3.390318164291099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.273008872333441</v>
+        <v>1.282158354605444</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.4578314272713795</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.913340900998459</v>
+        <v>2.987633795792016</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.524128122612353</v>
+        <v>-3.501254416932348</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.204376400038149</v>
+        <v>1.213525882310151</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.4578314272713795</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.889082929759666</v>
+        <v>2.963375824553223</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.490464577140072</v>
+        <v>-3.467590871460066</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.146380131628512</v>
+        <v>1.155529613900514</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.4914949727436614</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.837819370444485</v>
+        <v>2.912112265238041</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.430611957936348</v>
+        <v>-3.407738252256343</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.180493565742133</v>
+        <v>1.189643048014136</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.4914949727436614</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.847991756876617</v>
+        <v>2.922284651670174</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.344368494909971</v>
+        <v>-3.321494789229965</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.209937221526544</v>
+        <v>1.219086703798547</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.4914949727436614</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.842938027450477</v>
+        <v>2.917230922244034</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.389675314308951</v>
+        <v>-3.366801608628945</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.183590269211478</v>
+        <v>1.19273975148348</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.4506848097344306</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.810227705089464</v>
+        <v>2.884520599883021</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.418708419011252</v>
+        <v>-3.395834713331247</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.172528900363659</v>
+        <v>1.181678382635661</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.4506848097344306</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.810779578122566</v>
+        <v>2.885072472916123</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.325897937560393</v>
+        <v>-3.303024231880388</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.138925784835368</v>
+        <v>1.148075267107371</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5434952911852899</v>
+        <v>0.6673167825078846</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.795738558884447</v>
+        <v>2.870031453678004</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.370287406889821</v>
+        <v>-3.347413701209815</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.123043473028198</v>
+        <v>1.132192955300201</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.4991058218558623</v>
+        <v>0.622927313178457</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.770978353211391</v>
+        <v>2.845271248004948</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472738</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.257616188653571</v>
+        <v>-3.234742482973565</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.163187668834421</v>
+        <v>1.172337151106424</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6117770400921125</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.833656792664865</v>
+        <v>2.907949687458421</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.145239187470898</v>
+        <v>-3.122365481790892</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.213629765138158</v>
+        <v>1.22277924741016</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6117770400921125</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.839148088495532</v>
+        <v>2.913440983289088</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498864</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.173019585372251</v>
+        <v>-3.150145879692245</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.214014807746155</v>
+        <v>1.223164290018158</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.5839966421907594</v>
+        <v>0.707818133513354</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.833977051523259</v>
+        <v>2.908269946316816</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705325</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.25602086639753</v>
+        <v>-3.233147160717524</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.019170015336697</v>
+        <v>1.028319497608699</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5654257576635857</v>
+        <v>0.6892472489861803</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.661190240807608</v>
+        <v>2.735483135601165</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271631072927</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.364634944840861</v>
+        <v>-3.341761239160856</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.09587404467857</v>
+        <v>1.105023526950573</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5654257576635857</v>
+        <v>0.6892472489861803</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.781339901526814</v>
+        <v>2.85563279632037</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.329225906592718</v>
+        <v>-3.306352200912713</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.12455068608015</v>
+        <v>1.133700168352153</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5654257576635857</v>
+        <v>0.6892472489861803</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.795852927629137</v>
+        <v>2.870145822422693</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913425</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.290842244034567</v>
+        <v>-3.267968538354562</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.137323592445779</v>
+        <v>1.146473074717782</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6038094202217369</v>
+        <v>0.7276309115443315</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.816302566506396</v>
+        <v>2.890595461299953</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.113725913999401</v>
+        <v>-3.090852208319395</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.204899153305148</v>
+        <v>1.21404863557715</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6038094202217369</v>
+        <v>0.7276309115443315</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.813031595351698</v>
+        <v>2.887324490145255</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.158818158832947</v>
+        <v>-3.135944453152941</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.187545647133643</v>
+        <v>1.196695129405645</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5419133770523471</v>
+        <v>0.6657348683749417</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.776577361211977</v>
+        <v>2.850870256005534</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.979442737594179</v>
+        <v>-2.956569031914174</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.253082790935564</v>
+        <v>1.262232273207566</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6986901352230658</v>
+        <v>0.8225116265456603</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.864430391420823</v>
+        <v>2.93872328621438</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.024456951114785</v>
+        <v>-3.00158324543478</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.215884560858911</v>
+        <v>1.225034043130914</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6683412399084612</v>
+        <v>0.7921627312310557</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.82702850956365</v>
+        <v>2.901321404357207</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.291461461387221</v>
+        <v>-3.268587755707215</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.114774319088883</v>
+        <v>1.123923801360885</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4739782018655126</v>
+        <v>0.5977996931881071</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.716102249076827</v>
+        <v>2.790395143870383</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.392659242824394</v>
+        <v>-3.369785537144388</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.073499128410515</v>
+        <v>1.082648610682517</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4055693883201934</v>
+        <v>0.529390879642788</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.674260882846136</v>
+        <v>2.748553777639693</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.386148276210081</v>
+        <v>-3.363274570530075</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.073703476610557</v>
+        <v>1.082852958882559</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4055693883201934</v>
+        <v>0.529390879642788</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.671860844400453</v>
+        <v>2.74615373919401</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.367110148502784</v>
+        <v>-3.344236442822778</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.077843446901721</v>
+        <v>1.086992929173723</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3473857769889989</v>
+        <v>0.4712072683115934</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.633475396809981</v>
+        <v>2.707768291603538</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.73106447313125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.398236779653402</v>
+        <v>-3.375363073973396</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.242974663380154</v>
+        <v>1.252124145652157</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3473857769889989</v>
+        <v>0.4712072683115934</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.811057265748662</v>
+        <v>2.885350160542218</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067865</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.412103540987319</v>
+        <v>-3.389229835307313</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.238261287832721</v>
+        <v>1.247410770104723</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3095278602551759</v>
+        <v>0.4333493515777705</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.789175844694502</v>
+        <v>2.863468739488058</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.367299369447389</v>
+        <v>-3.344425663767383</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.262191486845619</v>
+        <v>1.271340969117621</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3095278602551759</v>
+        <v>0.4333493515777705</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.795184375091428</v>
+        <v>2.869477269884984</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.219556399212387</v>
+        <v>-3.196682693532381</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.219238896216819</v>
+        <v>1.228388378488821</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.4773352174900591</v>
+        <v>0.6011567088126537</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.793819010709557</v>
+        <v>2.868111905503114</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.321571081743608</v>
+        <v>-3.298697376063602</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.181226644735812</v>
+        <v>1.190376127007814</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.4773352174900591</v>
+        <v>0.6011567088126537</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.796612632241038</v>
+        <v>2.870905527034595</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.315418375690824</v>
+        <v>-3.292544670010818</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.184350075548584</v>
+        <v>1.193499557820586</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.4834879235428434</v>
+        <v>0.607309414865438</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.800966604264367</v>
+        <v>2.875259499057924</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.332227673841325</v>
+        <v>-3.309353968161319</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.176706833028494</v>
+        <v>1.185856315300496</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.4666786253923417</v>
+        <v>0.5905001167149364</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.789961502114176</v>
+        <v>2.864254396907733</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.269929675065203</v>
+        <v>-3.247055969385197</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.267961586335763</v>
+        <v>1.277111068607765</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.4666786253923417</v>
+        <v>0.5905001167149364</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.856297055910997</v>
+        <v>2.930589950704554</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.068139477400045</v>
+        <v>-3.04526577172004</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.150969667115953</v>
+        <v>1.160119149387956</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.6646968175614961</v>
+        <v>0.7885183088840908</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.777399972926617</v>
+        <v>2.851692867720173</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.903326474321198</v>
+        <v>-2.880452768641192</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.287185100669668</v>
+        <v>1.29633458294167</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8295098206403431</v>
+        <v>0.9533313119629377</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.9465780070961</v>
+        <v>3.020870901889657</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.001067018946173</v>
+        <v>-2.978193313266167</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.262716618935721</v>
+        <v>1.271866101207723</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8136205425073628</v>
+        <v>0.9374420338299576</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.951672176332355</v>
+        <v>3.025965071125913</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.177404779069102</v>
+        <v>-3.154531073389096</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.190717495711221</v>
+        <v>1.199866977983223</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6372827823844334</v>
+        <v>0.7611042737070282</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.84440550108327</v>
+        <v>2.918698395876826</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.100982732637175</v>
+        <v>-3.078109026957169</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.21977793232392</v>
+        <v>1.228927414595923</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6372827823844334</v>
+        <v>0.7611042737070282</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.842897119123198</v>
+        <v>2.917190013916755</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.056609600998606</v>
+        <v>-3.033735895318601</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.237390052414784</v>
+        <v>1.246539534686786</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.681655914023002</v>
+        <v>0.8054774053455968</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.869383865541775</v>
+        <v>2.943676760335332</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.933775380111439</v>
+        <v>-2.910901674431433</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.280917534908242</v>
+        <v>1.290067017180244</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.681655914023002</v>
+        <v>0.8054774053455968</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.863777659680366</v>
+        <v>2.938070554473923</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.886119649550383</v>
+        <v>-2.863245943870377</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.306361584160469</v>
+        <v>1.315511066432471</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7293116445840576</v>
+        <v>0.8531331359066524</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.898752855044804</v>
+        <v>2.973045749838361</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.785601491051628</v>
+        <v>-2.762727785371623</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.351461220934695</v>
+        <v>1.360610703206698</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8298298030828122</v>
+        <v>0.953651294405407</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.963956123518781</v>
+        <v>3.038249018312338</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.846268081454018</v>
+        <v>-2.823394375774012</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.313949257249612</v>
+        <v>1.323098739521614</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7481314863642785</v>
+        <v>0.8719529776868733</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.901691805963534</v>
+        <v>2.975984700757091</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.80142967984562</v>
+        <v>-2.778555974165614</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.3359823205036</v>
+        <v>1.345131802775602</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.752674919309148</v>
+        <v>0.8764964106317428</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.908515568341084</v>
+        <v>2.982808463134641</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.902188315602618</v>
+        <v>-2.879314609922612</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.299839805831878</v>
+        <v>1.30898928810388</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.6638493505821426</v>
+        <v>0.7876708419047374</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.859381166735958</v>
+        <v>2.933674061529516</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.857985478516718</v>
+        <v>-2.835111772836712</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.323400543194076</v>
+        <v>1.332550025466078</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.708052187668043</v>
+        <v>0.8318736789906378</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.891782471515336</v>
+        <v>2.966075366308893</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.894964506180161</v>
+        <v>-2.872090800500155</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.307018932597946</v>
+        <v>1.316168414869948</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7450260894593735</v>
+        <v>0.8688475807819683</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.912376813059382</v>
+        <v>2.986669707852939</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.736673088640889</v>
+        <v>-2.713799382960883</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.421583264796694</v>
+        <v>1.430732747068697</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7450260894593735</v>
+        <v>0.8688475807819683</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.963624578242421</v>
+        <v>3.037917473035979</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.529031085006412</v>
+        <v>-2.506157379326407</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.503080770844738</v>
+        <v>1.51223025311674</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9526680930938497</v>
+        <v>1.076489584416445</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.08665048501736</v>
+        <v>3.160943379810917</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.477998992283884</v>
+        <v>-2.455125286603879</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.518441836172019</v>
+        <v>1.527591318444022</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.003700185816378</v>
+        <v>1.127521677138973</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.112217968889147</v>
+        <v>3.186510863682704</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.412774811156678</v>
+        <v>-2.389901105476673</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.561718912715607</v>
+        <v>1.570868394987609</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.068924366943583</v>
+        <v>1.192745858266178</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.168539881658175</v>
+        <v>3.242832776451732</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.375347791085545</v>
+        <v>-2.352474085405539</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.57265069304334</v>
+        <v>1.581800175315343</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.074175904972765</v>
+        <v>1.19799739629536</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.167651776774965</v>
+        <v>3.241944671568522</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.395459447120253</v>
+        <v>-2.372585741440247</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.565862822960697</v>
+        <v>1.5750123052327</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.085203249970184</v>
+        <v>1.209024741292779</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.175524976104657</v>
+        <v>3.249817870898214</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.341714632693048</v>
+        <v>-2.318840927013043</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.74791851975279</v>
+        <v>1.757068002024792</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.095266559410646</v>
+        <v>1.219088050733241</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.342120732790145</v>
+        <v>3.416413627583702</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.266932371668036</v>
+        <v>-2.24405866598803</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.897944333380612</v>
+        <v>1.907093815652614</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.170048820435659</v>
+        <v>1.293870311758254</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.507102998622969</v>
+        <v>3.581395893416526</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.240848287404228</v>
+        <v>-2.217974581724222</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.900085943099994</v>
+        <v>1.909235425371997</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.170048820435659</v>
+        <v>1.293870311758254</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.498810974636828</v>
+        <v>3.573103869430385</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896924</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.162717106555281</v>
+        <v>-2.139843400875275</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.929531611023353</v>
+        <v>1.938681093295355</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.244225631319344</v>
+        <v>1.368047122641939</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.541510256750819</v>
+        <v>3.615803151544376</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.153824645161998</v>
+        <v>-2.130950939481992</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.950643001307457</v>
+        <v>1.959792483579459</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.244225631319344</v>
+        <v>1.368047122641939</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.55906466247761</v>
+        <v>3.633357557271167</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.322300762131876</v>
+        <v>-2.29942705645187</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.87510760192409</v>
+        <v>1.884257084196092</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.216277795602763</v>
+        <v>1.340099286925358</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.534151008452246</v>
+        <v>3.608443903245802</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.624501233270292</v>
+        <v>-1.601627527590287</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.135497110656585</v>
+        <v>2.144646592928587</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.145929736232352</v>
+        <v>1.269751227554947</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.473211870017861</v>
+        <v>3.547504764811418</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.60178012958714</v>
+        <v>-1.578906423907134</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.135249574626751</v>
+        <v>2.144399056898753</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.145929736232352</v>
+        <v>1.269751227554947</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.463875892514765</v>
+        <v>3.538168787308322</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.600055086297096</v>
+        <v>-1.57718138061709</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.294845717793937</v>
+        <v>2.303995200065939</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.147654779522396</v>
+        <v>1.271476270844991</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.623817044339961</v>
+        <v>3.698109939133518</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.754836093075351</v>
+        <v>-1.731962387395346</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.270011137576282</v>
+        <v>2.279160619848284</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.11428710546792</v>
+        <v>1.238108596790515</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.640874262400922</v>
+        <v>3.715167157194479</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.747781402860178</v>
+        <v>-1.724907697180172</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.269508369651896</v>
+        <v>2.278657851923898</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.121341795683094</v>
+        <v>1.245163287005689</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.641782432519571</v>
+        <v>3.716075327313128</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.72083017853369</v>
+        <v>-1.697956472853684</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.290295013027233</v>
+        <v>2.299444495299236</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.136222141710813</v>
+        <v>1.260043633033408</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.660716793780944</v>
+        <v>3.735009688574501</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.856783186590006</v>
+        <v>-1.83390948091</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.420016941949667</v>
+        <v>2.429166424221669</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.136222141710813</v>
+        <v>1.260043633033408</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.844819925925904</v>
+        <v>3.919112820719461</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.879191304394878</v>
+        <v>-1.856317598714872</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.403170389730711</v>
+        <v>2.412319872002713</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.136222141710813</v>
+        <v>1.260043633033408</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.836936620828897</v>
+        <v>3.911229515622454</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.027197071874277</v>
+        <v>-2.004323366194272</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.346022082288588</v>
+        <v>2.355171564560591</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.049495132847271</v>
+        <v>1.173316624169866</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.78695441506041</v>
+        <v>3.861247309853967</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.036637997762807</v>
+        <v>-2.121523038391352</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.398499429655024</v>
+        <v>2.364545413403606</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.171922250390663</v>
+        <v>1.155180113315116</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.916664403308292</v>
+        <v>3.906619121062964</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.088911605098449</v>
+        <v>-2.173796645726993</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.380481081266068</v>
+        <v>2.34652706501465</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.119648643055021</v>
+        <v>1.102906505979475</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.888191333452208</v>
+        <v>3.87814605120688</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.165241582699355</v>
+        <v>-2.250126623327899</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.348060903119481</v>
+        <v>2.314106886868063</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.119648643055021</v>
+        <v>1.102906505979475</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.886303146345983</v>
+        <v>3.876257864100655</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.276998535314656</v>
+        <v>-2.3618835759432</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.298178351676222</v>
+        <v>2.264224335424805</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.00789169043972</v>
+        <v>0.9911495533641741</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.814069204379665</v>
+        <v>3.804023922134337</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.275157516256404</v>
+        <v>-2.360042556884949</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.297348769509675</v>
+        <v>2.263394753258257</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.009159917111189</v>
+        <v>0.9924177800356424</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.813264150592698</v>
+        <v>3.80321886834737</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.407458808353958</v>
+        <v>-2.492343848982502</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.257501659536573</v>
+        <v>2.223547643285155</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.009159917111189</v>
+        <v>0.9924177800356424</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.826337557458617</v>
+        <v>3.816292275213289</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.409020451168818</v>
+        <v>-2.493905491797362</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.256877002410629</v>
+        <v>2.222922986159211</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.009159917111189</v>
+        <v>0.9924177800356424</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.826337557458617</v>
+        <v>3.816292275213289</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.436921238278291</v>
+        <v>-2.521806278906835</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.244240728693842</v>
+        <v>2.210286712442424</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9745629929682539</v>
+        <v>0.9578208558927076</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.804103444099858</v>
+        <v>3.79405816185453</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172526</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.559447340981185</v>
+        <v>-2.644332381609729</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.191994731589883</v>
+        <v>2.158040715338465</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.85203689026536</v>
+        <v>0.8352947531898137</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.72735222645532</v>
+        <v>3.717306944209992</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971078</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.579508662257691</v>
+        <v>-2.664393702886236</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.250676162669784</v>
+        <v>2.216722146418366</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8319755689888531</v>
+        <v>0.8152334319133068</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.78202139327992</v>
+        <v>3.771976111034592</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199805</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.836229480252515</v>
+        <v>-2.92111452088106</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.288299554473701</v>
+        <v>2.254345538222283</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.7235609948450382</v>
+        <v>0.7068188577694919</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.857284367795478</v>
+        <v>3.84723908555015</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622236</v>
+        <v>3.668303164622234</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.990215898028656</v>
+        <v>-3.0751009386572</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.295685256508885</v>
+        <v>2.261731240257467</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.7235609948450382</v>
+        <v>0.7068188577694919</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.926264636941117</v>
+        <v>3.91621935469579</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808528</v>
+        <v>3.619937176808526</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.93969399420099</v>
+        <v>-3.024579034829534</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.301945220160072</v>
+        <v>2.267991203908654</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.7235609948450382</v>
+        <v>0.7068188577694919</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.912315839061239</v>
+        <v>3.902270556815911</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994893</v>
+        <v>3.656346893994891</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.192169148208714</v>
+        <v>-3.277054188837259</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.212825647612396</v>
+        <v>2.178871631360979</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.7235609948450382</v>
+        <v>0.7068188577694919</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.924186328116653</v>
+        <v>3.914141045871324</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.674042696358295</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.461641950130423</v>
+        <v>-3.546526990758967</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.106247061362657</v>
+        <v>2.072293045111239</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.7235609948450382</v>
+        <v>0.7068188577694919</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.925396862635596</v>
+        <v>3.915351580390269</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637085</v>
+        <v>3.663523617637083</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.619186021859864</v>
+        <v>-3.704071062488408</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.047351174898202</v>
+        <v>2.013397158646784</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6566591897047638</v>
+        <v>0.6399170526292175</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.889377521778753</v>
+        <v>3.879332239533425</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301342</v>
+        <v>3.65216331330134</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.74803657256191</v>
+        <v>-3.832921613190455</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.990888807353572</v>
+        <v>1.956934791102155</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6156657808540422</v>
+        <v>0.5989236437784959</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.85985932920451</v>
+        <v>3.849814046959182</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.667976467215467</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.865004265200801</v>
+        <v>-3.949889305829346</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.10630578699706</v>
+        <v>2.072351770745643</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6156657808540422</v>
+        <v>0.5989236437784959</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.022063385903554</v>
+        <v>4.012018103658225</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456691</v>
+        <v>3.696553628456689</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.949722207421755</v>
+        <v>-4.0346072480503</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.067265248072493</v>
+        <v>2.033311231821076</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5305497519259958</v>
+        <v>0.5138076148504496</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.96584040651054</v>
+        <v>3.955795124265212</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253287</v>
+        <v>3.750058176253285</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.031657025690638</v>
+        <v>-4.116542066319183</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.044720738333431</v>
+        <v>2.010766722082013</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5206150063389157</v>
+        <v>0.5038728692633694</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.970108976726783</v>
+        <v>3.960063694481455</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717831</v>
+        <v>3.783647027717829</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.977918852290376</v>
+        <v>-4.062803892918921</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.075141646149438</v>
+        <v>2.041187629898021</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.5743531797391778</v>
+        <v>0.5576110426636315</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.011277519222842</v>
+        <v>4.001232236977515</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616947</v>
+        <v>3.798310944616945</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.867912568813154</v>
+        <v>-3.952797609441699</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.111297046784502</v>
+        <v>2.077343030533084</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.597557751656453</v>
+        <v>0.5808156145809067</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.017353149617383</v>
+        <v>4.007307867372055</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203661</v>
+        <v>3.785578085203659</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.724852993072229</v>
+        <v>-3.809738033700774</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.172770887802847</v>
+        <v>2.138816871551429</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.6055711782464323</v>
+        <v>0.588829041170886</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.026411216293345</v>
+        <v>4.016365934048017</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.77725157243693</v>
+        <v>3.777251572436928</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.363316328820813</v>
+        <v>-3.508291308228936</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.324646436385949</v>
+        <v>2.2666564446227</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.9671078424978474</v>
+        <v>0.8902757666427232</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.25059409772673</v>
+        <v>4.204494852213656</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.770982935628746</v>
+        <v>3.502537343954342</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.603725766449164</v>
+        <v>3.495707000725822</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.363316328820813</v>
+        <v>-3.508291308228936</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.324646436385949</v>
+        <v>2.2666564446227</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.9671078424978474</v>
+        <v>0.8902757666427232</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.596789563435531</v>
+        <v>3.48877079771219</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240719.xlsx
+++ b/tame_output/ON/bt/strategyON_20240719.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.9%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>28.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.7%</t>
+          <t>-73.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>110.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.6%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.2%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.2%</t>
+          <t>-69.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.5%</t>
+          <t>455.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-512.4%</t>
+          <t>-528.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>22.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-10.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-149.6%</t>
+          <t>-155.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-137.9%</t>
+          <t>-136.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-135.0%</t>
+          <t>-139.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.2%</t>
+          <t>-24.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.2%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-97.1%</t>
+          <t>-95.7%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386091</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998558</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006531</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539461</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.213502399279831</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5011791544478572</v>
+        <v>-0.5249191707206307</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.858242632280979</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.045892633936462</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.266288554880157</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5211778268494314</v>
+        <v>-0.5449178431222053</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.953918118863376</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>1.98960313182558</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.392325348248447</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5688988155676324</v>
+        <v>-0.5926388318404063</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.928666496053634</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.00744783414054</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.335253576352516</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5420797711228591</v>
+        <v>-0.565819787395633</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.928666496053634</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.011438169826941</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.476925418076636</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6002237347112489</v>
+        <v>-0.6239637509840228</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.928666496053634</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.009962942928199</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.427334573651802</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5653339867764431</v>
+        <v>-0.589074003049217</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.8790756516288</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.054770859747971</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770578</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.278416239179945</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5188177866343833</v>
+        <v>-0.5425578029071572</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.847826060893627</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.060469480542392</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-9.052571086460535</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.4426406687831848</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.805899385306463</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.095204558930899</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-8.927992430122943</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.3916700616920887</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.805899385306463</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.096343703486958</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-8.98088771816723</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.4101944027476958</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.800944039218017</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.101950685302134</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-8.908754542879349</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.375607428393907</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.800944039218017</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.10768438954077</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-8.837388150269701</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.3567981337439132</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.729577646608369</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.140766962712694</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.743929116284477</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.3292980014627309</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.729577646608369</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.130883481399786</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.476687315416079</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.2242358416147456</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.729577646608369</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.129048920900412</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.378780276739588</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.1853733411176104</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.661591896747813</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.169540055843285</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.354826735763631</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.1751234185817334</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.637638355771855</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.184580686574353</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-8.090766797440834</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.08275975941436675</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.373578417449059</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.329756333406279</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.383687173935995</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.1972850563272677</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.373578417449059</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.326969299745978</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.343502875569805</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.2137023995615852</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.333394119082868</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.351423502653534</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.180103004630443</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.2784291691580871</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.169994248143506</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.448830246437908</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-6.946621782400844</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.3797460868877787</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.9365130259139072</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.59684340861352</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-6.796955391393329</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.4367204329778258</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.8436095346713712</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.649693293046082</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.664679917762443</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.4849981091772073</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.7113340610404846</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.724426063971641</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.508941585202701</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.5501085028887407</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.555595728480743</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.820684124195123</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.25994178651912</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.6626147635858319</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.555595728480743</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.833590465418782</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.365531776292224</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.4924028380773713</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.6611857182538474</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.6422605419557</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.384266678410821</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.5334532191070189</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.6667817279139787</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.687447278036708</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710814</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.236326637003222</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.4727503129818911</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.6464608120054212</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.579760904893675</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409206</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.183357114749233</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5089641519027821</v>
+        <v>0.4852241356300082</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5934912897514323</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.60282863199259</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098111</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.139808707978543</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5194229025159651</v>
+        <v>0.4956828862431912</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5934912897514323</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.595868019897497</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493422</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.04709546081784</v>
+        <v>-6.106445501499774</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5472305394886159</v>
+        <v>0.523490523215842</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5934912897514323</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.61033037427864</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.938836323695318</v>
+        <v>-5.998186364377252</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5850663147968196</v>
+        <v>0.5613262985240457</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5934912897514323</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.604862494737835</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.815545188878187</v>
+        <v>-5.874895229560122</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6318808627342487</v>
+        <v>0.6081408464614748</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.4702001549343018</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.67633526963869</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.794395989974744</v>
+        <v>-5.853746030656678</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6480415205329515</v>
+        <v>0.6243015042601776</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4490509560308584</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.696725767218081</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.550630547991299</v>
+        <v>-5.609980588673234</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7413284056733795</v>
+        <v>0.7175883894006061</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.4490509560308584</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.692506475565132</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.448867727714005</v>
+        <v>-5.508217768395939</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7841578477043138</v>
+        <v>0.76041783143154</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4358318876384297</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.702562230520605</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.19901733376493</v>
+        <v>-5.258367374446864</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8768400802676455</v>
+        <v>0.853100063994872</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4358318876384297</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.695304305504307</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.8359579870115</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.023125241297498</v>
+        <v>-5.082475281979432</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9507960407752671</v>
+        <v>0.9270560245024932</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.4358318876384297</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.698903429024956</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.851678778275034</v>
+        <v>-4.911028818956969</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.032702132038806</v>
+        <v>1.008962115766032</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.2643854246159666</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.815098812892987</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.777389212536695</v>
+        <v>-4.83673925321863</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.061438435950439</v>
+        <v>1.037698419677665</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.1900958588776273</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.858693029952288</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883075</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.713753470302761</v>
+        <v>-4.773103510984695</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.09158753389833</v>
+        <v>1.067847517625556</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1264601166436928</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.901569276346966</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.602326710976841</v>
+        <v>-4.661676751658775</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.117352496412494</v>
+        <v>1.09361248013972</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.1264601166436928</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.882763535130762</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.36189621417198</v>
+        <v>-4.421246254853915</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.215267771759315</v>
+        <v>1.191527755486541</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1139703801611675</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>3.028764909838555</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.289653646000786</v>
+        <v>-4.34900368668272</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.248094112862613</v>
+        <v>1.224354096589839</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1139703801611675</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>3.032694223673376</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.236655323719398</v>
+        <v>-4.296005364401332</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.269972025692508</v>
+        <v>1.246232009419735</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1693066391631063</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>3.066574562991879</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.127850438239671</v>
+        <v>-4.187200478921605</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.310492051104393</v>
+        <v>1.286752034831619</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.1693066391631063</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>3.063572634211873</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.90782964020266</v>
+        <v>-3.967179680884594</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.400079407329811</v>
+        <v>1.376339391057037</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.3105264842310866</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.149883578263275</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.774961951139382</v>
+        <v>-3.834311991821316</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.469120665756946</v>
+        <v>1.445380649484172</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.3105264842310866</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.165777761065098</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496264</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.654788867774883</v>
+        <v>-3.714138908456817</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.518335743543047</v>
+        <v>1.494595727270273</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.4306995675955855</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.239027455524099</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551577</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.510116722675146</v>
+        <v>-3.56946676335708</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.586292704144382</v>
+        <v>1.562552687871608</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.5753717126953229</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.335918845145382</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.569991550032838</v>
+        <v>-3.629341590714772</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.548380264602731</v>
+        <v>1.524640248329957</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.5154968853376308</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.286031440132192</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.450171319122</v>
+        <v>-3.509521359803935</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.611597526201274</v>
+        <v>1.587857509928501</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.5154968853376308</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.3013206093664</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430694</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.452641025583806</v>
+        <v>-3.511991066265741</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.518253842938994</v>
+        <v>1.49451382666622</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.5130271788758247</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.207482984811759</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003604</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.521011211907816</v>
+        <v>-3.580361252589751</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.410167629894691</v>
+        <v>1.386427613621917</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5223028779120397</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.132310265718789</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.534799264754863</v>
+        <v>-3.594149305436797</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.395089117387764</v>
+        <v>1.37134910111499</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5223028779120397</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.12274697435068</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.565792424083568</v>
+        <v>-3.625142464765503</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.207401418696668</v>
+        <v>1.183661402423895</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5223028779120397</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.983066563800228</v>
+        <v>2.947456539391067</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.390318164291099</v>
+        <v>-3.449668204973034</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.282158354605444</v>
+        <v>1.25841833833267</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5223028779120397</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.987633795792016</v>
+        <v>2.952023771382855</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.501254416932348</v>
+        <v>-3.560604457614282</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.213525882310151</v>
+        <v>1.189785866037378</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5223028779120397</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.963375824553223</v>
+        <v>2.927765800144062</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111297</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.467590871460066</v>
+        <v>-3.526940912142</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.155529613900514</v>
+        <v>1.13178959762774</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5559664233843216</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.912112265238041</v>
+        <v>2.876502240828881</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264166</v>
       </c>
       <c r="C1942" t="n">
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.407738252256343</v>
+        <v>-3.467088292938277</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.189643048014136</v>
+        <v>1.165903031741362</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5559664233843216</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.922284651670174</v>
+        <v>2.886674627261013</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742302</v>
       </c>
       <c r="C1943" t="n">
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.321494789229965</v>
+        <v>-3.3808448299119</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.219086703798547</v>
+        <v>1.195346687525773</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.5559664233843216</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.917230922244034</v>
+        <v>2.881620897834873</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316049</v>
       </c>
       <c r="C1944" t="n">
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.366801608628945</v>
+        <v>-3.42615164931088</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.19273975148348</v>
+        <v>1.168999735210707</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.5151562603750908</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.884520599883021</v>
+        <v>2.848910575473861</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803194</v>
       </c>
       <c r="C1945" t="n">
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.395834713331247</v>
+        <v>-3.455184754013181</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.181678382635661</v>
+        <v>1.157938366362887</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.5151562603750908</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.885072472916123</v>
+        <v>2.849462448506962</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.733390600809502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.303024231880388</v>
+        <v>-3.362374272562322</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.148075267107371</v>
+        <v>1.124335250834597</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6673167825078846</v>
+        <v>0.6079667418259501</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.870031453678004</v>
+        <v>2.834421429268843</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.347413701209815</v>
+        <v>-3.40676374189175</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.132192955300201</v>
+        <v>1.108452939027427</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.622927313178457</v>
+        <v>0.5635772724965225</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.845271248004948</v>
+        <v>2.809661223595787</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.72107719547274</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.234742482973565</v>
+        <v>-3.294092523655499</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.172337151106424</v>
+        <v>1.14859713483365</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.6762484907327726</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.907949687458421</v>
+        <v>2.872339663049261</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.122365481790892</v>
+        <v>-3.181715522472827</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.22277924741016</v>
+        <v>1.199039231137386</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.6762484907327726</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.913440983289088</v>
+        <v>2.877830958879928</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498867</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.150145879692245</v>
+        <v>-3.20949592037418</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.223164290018158</v>
+        <v>1.199424273745384</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.707818133513354</v>
+        <v>0.6484680928314195</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.908269946316816</v>
+        <v>2.872659921907655</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705327</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.233147160717524</v>
+        <v>-3.292497201399459</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.028319497608699</v>
+        <v>1.004579481335925</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.6298972083042458</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.735483135601165</v>
+        <v>2.699873111192004</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.341761239160856</v>
+        <v>-3.40111127984279</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.105023526950573</v>
+        <v>1.081283510677799</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.6298972083042458</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.85563279632037</v>
+        <v>2.82002277191121</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.306352200912713</v>
+        <v>-3.365702241594647</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.133700168352153</v>
+        <v>1.109960152079379</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.6298972083042458</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.870145822422693</v>
+        <v>2.834535798013533</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913428</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.267968538354562</v>
+        <v>-3.327318579036496</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.146473074717782</v>
+        <v>1.122733058445008</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7276309115443315</v>
+        <v>0.668280870862397</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.890595461299953</v>
+        <v>2.854985436890792</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.090852208319395</v>
+        <v>-3.15020224900133</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.21404863557715</v>
+        <v>1.190308619304376</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7276309115443315</v>
+        <v>0.668280870862397</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.887324490145255</v>
+        <v>2.851714465736094</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.135944453152941</v>
+        <v>-3.195294493834876</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.196695129405645</v>
+        <v>1.172955113132871</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6657348683749417</v>
+        <v>0.6063848276930072</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.850870256005534</v>
+        <v>2.815260231596373</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.956569031914174</v>
+        <v>-3.015919072596108</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.262232273207566</v>
+        <v>1.238492256934792</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8225116265456603</v>
+        <v>0.7631615858637258</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.93872328621438</v>
+        <v>2.903113261805219</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.71699171898223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.00158324543478</v>
+        <v>-3.060933286116714</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.225034043130914</v>
+        <v>1.20129402685814</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7921627312310557</v>
+        <v>0.7328126905491212</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.901321404357207</v>
+        <v>2.865711379948046</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.268587755707215</v>
+        <v>-3.32793779638915</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.123923801360885</v>
+        <v>1.100183785088111</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5977996931881071</v>
+        <v>0.5384496525061726</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.790395143870383</v>
+        <v>2.754785119461222</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760814</v>
       </c>
       <c r="C1960" t="n">
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.369785537144388</v>
+        <v>-3.429135577826322</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.082648610682517</v>
+        <v>1.058908594409744</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.529390879642788</v>
+        <v>0.4700408389608534</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.748553777639693</v>
+        <v>2.712943753230532</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815458</v>
       </c>
       <c r="C1961" t="n">
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.363274570530075</v>
+        <v>-3.42262461121201</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.082852958882559</v>
+        <v>1.059112942609786</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.529390879642788</v>
+        <v>0.4700408389608534</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.74615373919401</v>
+        <v>2.710543714784849</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378102</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.344236442822778</v>
+        <v>-3.403586483504712</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.086992929173723</v>
+        <v>1.063252912900949</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4712072683115934</v>
+        <v>0.4118572276296589</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.707768291603538</v>
+        <v>2.672158267194377</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106447313125</v>
+        <v>3.731064473131252</v>
       </c>
       <c r="C1963" t="n">
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.375363073973396</v>
+        <v>-3.43471311465533</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.252124145652157</v>
+        <v>1.228384129379383</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4712072683115934</v>
+        <v>0.4118572276296589</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.885350160542218</v>
+        <v>2.849740136133058</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067865</v>
+        <v>3.722447362067868</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.389229835307313</v>
+        <v>-3.448579875989248</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.247410770104723</v>
+        <v>1.223670753831949</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4333493515777705</v>
+        <v>0.3739993108958359</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.863468739488058</v>
+        <v>2.827858715078897</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789126</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.344425663767383</v>
+        <v>-3.403775704449318</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.271340969117621</v>
+        <v>1.247600952844847</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4333493515777705</v>
+        <v>0.3739993108958359</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.869477269884984</v>
+        <v>2.833867245475823</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519911</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.196682693532381</v>
+        <v>-3.256032734214316</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.228388378488821</v>
+        <v>1.204648362216048</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6011567088126537</v>
+        <v>0.5418066681307191</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.868111905503114</v>
+        <v>2.832501881093953</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181172</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.298697376063602</v>
+        <v>-3.358047416745537</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.190376127007814</v>
+        <v>1.16663611073504</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6011567088126537</v>
+        <v>0.5418066681307191</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.870905527034595</v>
+        <v>2.835295502625434</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.292544670010818</v>
+        <v>-3.351894710692752</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.193499557820586</v>
+        <v>1.169759541547812</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.607309414865438</v>
+        <v>0.5479593741835034</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.875259499057924</v>
+        <v>2.839649474648763</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890612</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.309353968161319</v>
+        <v>-3.368704008843254</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.185856315300496</v>
+        <v>1.162116299027722</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5905001167149364</v>
+        <v>0.5311500760330017</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.864254396907733</v>
+        <v>2.828644372498572</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798428</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.247055969385197</v>
+        <v>-3.306406010067132</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.277111068607765</v>
+        <v>1.253371052334991</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5905001167149364</v>
+        <v>0.5311500760330017</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.930589950704554</v>
+        <v>2.894979926295393</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.04526577172004</v>
+        <v>-3.104615812401974</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.160119149387956</v>
+        <v>1.136379133115182</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7885183088840908</v>
+        <v>0.7291682682021561</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.851692867720173</v>
+        <v>2.816082843311013</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852427</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.880452768641192</v>
+        <v>-2.939802809323127</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.29633458294167</v>
+        <v>1.272594566668896</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9533313119629377</v>
+        <v>0.893981271281003</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.020870901889657</v>
+        <v>2.985260877480496</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319547</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.978193313266167</v>
+        <v>-3.037543353948101</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.271866101207723</v>
+        <v>1.24812608493495</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9374420338299576</v>
+        <v>0.8780919931480229</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.025965071125913</v>
+        <v>2.990355046716751</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.154531073389096</v>
+        <v>-3.213881114071031</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.199866977983223</v>
+        <v>1.17612696171045</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7611042737070282</v>
+        <v>0.7017542330250934</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.918698395876826</v>
+        <v>2.883088371467665</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.078109026957169</v>
+        <v>-3.137459067639104</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.228927414595923</v>
+        <v>1.205187398323149</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7611042737070282</v>
+        <v>0.7017542330250934</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.917190013916755</v>
+        <v>2.881579989507594</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.033735895318601</v>
+        <v>-3.093085936000535</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.246539534686786</v>
+        <v>1.222799518414013</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8054774053455968</v>
+        <v>0.746127364663662</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.943676760335332</v>
+        <v>2.908066735926171</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105968</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.910901674431433</v>
+        <v>-2.970251715113368</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.290067017180244</v>
+        <v>1.26632700090747</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8054774053455968</v>
+        <v>0.746127364663662</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.938070554473923</v>
+        <v>2.902460530064762</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190326</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.863245943870377</v>
+        <v>-2.922595984552312</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.315511066432471</v>
+        <v>1.291771050159697</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8531331359066524</v>
+        <v>0.7937830952247177</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.973045749838361</v>
+        <v>2.9374357254292</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569618</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.762727785371623</v>
+        <v>-2.822077826053557</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.360610703206698</v>
+        <v>1.336870686933924</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.953651294405407</v>
+        <v>0.8943012537234722</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.038249018312338</v>
+        <v>3.002638993903178</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557294</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.823394375774012</v>
+        <v>-2.882744416455946</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.323098739521614</v>
+        <v>1.29935872324884</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8719529776868733</v>
+        <v>0.8126029370049386</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.975984700757091</v>
+        <v>2.940374676347929</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932768</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.778555974165614</v>
+        <v>-2.837906014847548</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.345131802775602</v>
+        <v>1.321391786502828</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8764964106317428</v>
+        <v>0.817146369949808</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.982808463134641</v>
+        <v>2.94719843872548</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917052</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.879314609922612</v>
+        <v>-2.938664650604547</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.30898928810388</v>
+        <v>1.285249271831107</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7876708419047374</v>
+        <v>0.7283208012228026</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.933674061529516</v>
+        <v>2.898064037120355</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.82668474540596</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.835111772836712</v>
+        <v>-2.894461813518646</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.332550025466078</v>
+        <v>1.308810009193304</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8318736789906378</v>
+        <v>0.7725236383087031</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.966075366308893</v>
+        <v>2.930465341899732</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265645</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.872090800500155</v>
+        <v>-2.93144084118209</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.316168414869948</v>
+        <v>1.292428398597174</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8688475807819683</v>
+        <v>0.8094975401000336</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.986669707852939</v>
+        <v>2.951059683443778</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.713799382960883</v>
+        <v>-2.773149423642817</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.430732747068697</v>
+        <v>1.406992730795923</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8688475807819683</v>
+        <v>0.8094975401000336</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.037917473035979</v>
+        <v>3.002307448626818</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.865338681321023</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.506157379326407</v>
+        <v>-2.565507420008341</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.51223025311674</v>
+        <v>1.488490236843967</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.076489584416445</v>
+        <v>1.01713954373451</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.160943379810917</v>
+        <v>3.125333355401756</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.455125286603879</v>
+        <v>-2.514475327285813</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.527591318444022</v>
+        <v>1.503851302171248</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.127521677138973</v>
+        <v>1.068171636457038</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.186510863682704</v>
+        <v>3.150900839273543</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404854</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.389901105476673</v>
+        <v>-2.449251146158607</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.570868394987609</v>
+        <v>1.547128378714835</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.192745858266178</v>
+        <v>1.133395817584243</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.242832776451732</v>
+        <v>3.207222752042572</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882558</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.352474085405539</v>
+        <v>-2.411824126087474</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.581800175315343</v>
+        <v>1.558060159042569</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.19799739629536</v>
+        <v>1.138647355613425</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.241944671568522</v>
+        <v>3.206334647159361</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.372585741440247</v>
+        <v>-2.431935782122182</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.5750123052327</v>
+        <v>1.551272288959926</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.209024741292779</v>
+        <v>1.149674700610844</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.249817870898214</v>
+        <v>3.214207846489053</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.318840927013043</v>
+        <v>-2.378190967694977</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.757068002024792</v>
+        <v>1.733327985752019</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.219088050733241</v>
+        <v>1.159738010051306</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.416413627583702</v>
+        <v>3.380803603174541</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.24405866598803</v>
+        <v>-2.303408706669964</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.907093815652614</v>
+        <v>1.883353799379841</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.293870311758254</v>
+        <v>1.234520271076319</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.581395893416526</v>
+        <v>3.545785869007366</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998755</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.217974581724222</v>
+        <v>-2.277324622406157</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.909235425371997</v>
+        <v>1.885495409099223</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.293870311758254</v>
+        <v>1.234520271076319</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.573103869430385</v>
+        <v>3.537493845021225</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896924</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.139843400875275</v>
+        <v>-2.19919344155721</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.938681093295355</v>
+        <v>1.914941077022581</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.368047122641939</v>
+        <v>1.308697081960004</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.615803151544376</v>
+        <v>3.580193127135215</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959856</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.130950939481992</v>
+        <v>-2.269028318429841</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.959792483579459</v>
+        <v>1.90456153200032</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.368047122641939</v>
+        <v>1.308697081960004</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.633357557271167</v>
+        <v>3.597747532862006</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.29942705645187</v>
+        <v>-2.437504435399719</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.884257084196092</v>
+        <v>1.829026132616953</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.340099286925358</v>
+        <v>1.280749246243423</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.608443903245802</v>
+        <v>3.572833878836642</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782706</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.601627527590287</v>
+        <v>-1.739704906538135</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.144646592928587</v>
+        <v>2.089415641349448</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.269751227554947</v>
+        <v>1.210401186873012</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.547504764811418</v>
+        <v>3.511894740402257</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632634</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.578906423907134</v>
+        <v>-1.716983802854983</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.144399056898753</v>
+        <v>2.089168105319613</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.269751227554947</v>
+        <v>1.210401186873012</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.538168787308322</v>
+        <v>3.502558762899162</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777671</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.57718138061709</v>
+        <v>-1.715258759564939</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.303995200065939</v>
+        <v>2.2487642484868</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.271476270844991</v>
+        <v>1.212126230163056</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.698109939133518</v>
+        <v>3.662499914724357</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.77993372564441</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.731962387395346</v>
+        <v>-1.870039766343194</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.279160619848284</v>
+        <v>2.223929668269145</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.238108596790515</v>
+        <v>1.17875855610858</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.715167157194479</v>
+        <v>3.679557132785318</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799963</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.724907697180172</v>
+        <v>-1.862985076128021</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.278657851923898</v>
+        <v>2.223426900344759</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.245163287005689</v>
+        <v>1.185813246323754</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.716075327313128</v>
+        <v>3.680465302903967</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.697956472853684</v>
+        <v>-1.836033851801533</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.299444495299236</v>
+        <v>2.244213543720096</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.260043633033408</v>
+        <v>1.200693592351473</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.735009688574501</v>
+        <v>3.69939966416534</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784105</v>
+        <v>3.768052067784107</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.83390948091</v>
+        <v>-1.971986859857849</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.429166424221669</v>
+        <v>2.373935472642529</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.260043633033408</v>
+        <v>1.200693592351473</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.919112820719461</v>
+        <v>3.8835027963103</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714423</v>
+        <v>3.743925505714425</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.856317598714872</v>
+        <v>-1.994394977662721</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.412319872002713</v>
+        <v>2.357088920423574</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.260043633033408</v>
+        <v>1.200693592351473</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.911229515622454</v>
+        <v>3.875619491213293</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.71911862715503</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.004323366194272</v>
+        <v>-2.14240074514212</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.355171564560591</v>
+        <v>2.299940612981451</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.173316624169866</v>
+        <v>1.113966583487931</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.861247309853967</v>
+        <v>3.825637285444806</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.121523038391352</v>
+        <v>-2.15184167103065</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.364545413403606</v>
+        <v>2.352417960347887</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.155180113315116</v>
+        <v>1.236393701031323</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.906619121062964</v>
+        <v>3.955347273692688</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.173796645726993</v>
+        <v>-2.204115278366291</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.34652706501465</v>
+        <v>2.334399611958931</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.102906505979475</v>
+        <v>1.184120093695681</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.87814605120688</v>
+        <v>3.926874203836604</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347703</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.250126623327899</v>
+        <v>-2.280445255967197</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.314106886868063</v>
+        <v>2.301979433812344</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.102906505979475</v>
+        <v>1.184120093695681</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.876257864100655</v>
+        <v>3.924986016730379</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.710654104887747</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.3618835759432</v>
+        <v>-2.392202208582498</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.264224335424805</v>
+        <v>2.252096882369086</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.9911495533641741</v>
+        <v>1.07236314108038</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.804023922134337</v>
+        <v>3.85275207476406</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343065</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.360042556884949</v>
+        <v>-2.390361189524247</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.263394753258257</v>
+        <v>2.251267300202538</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.9924177800356424</v>
+        <v>1.073631367751849</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.80321886834737</v>
+        <v>3.851947020977094</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.754911907647105</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.492343848982502</v>
+        <v>-2.5226624816218</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.223547643285155</v>
+        <v>2.211420190229436</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.9924177800356424</v>
+        <v>1.073631367751849</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.816292275213289</v>
+        <v>3.865020427843012</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.749896851763531</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.493905491797362</v>
+        <v>-2.52422412443666</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.222922986159211</v>
+        <v>2.210795533103492</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9924177800356424</v>
+        <v>1.073631367751849</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.816292275213289</v>
+        <v>3.865020427843012</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.715834055392115</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.521806278906835</v>
+        <v>-2.552124911546133</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.210286712442424</v>
+        <v>2.198159259386705</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9578208558927076</v>
+        <v>1.039034443608914</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.79405816185453</v>
+        <v>3.842786314484254</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.684909939172525</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.644332381609729</v>
+        <v>-2.674651014249027</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.158040715338465</v>
+        <v>2.145913262282746</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8352947531898137</v>
+        <v>0.9165083409060202</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.717306944209992</v>
+        <v>3.766035096839716</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.664393702886236</v>
+        <v>-2.820186498744192</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.216722146418366</v>
+        <v>2.154405028075184</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.8152334319133068</v>
+        <v>0.7709728564108553</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.771976111034592</v>
+        <v>3.745419765733121</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199803</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.92111452088106</v>
+        <v>-3.076907316739016</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.254345538222283</v>
+        <v>2.192028419879101</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.7068188577694919</v>
+        <v>0.6625582822670405</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.84723908555015</v>
+        <v>3.820682740248679</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622234</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.0751009386572</v>
+        <v>-3.230893734515157</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.261731240257467</v>
+        <v>2.199414121914284</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.7068188577694919</v>
+        <v>0.6625582822670405</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.91621935469579</v>
+        <v>3.889663009394319</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808526</v>
+        <v>3.619937176808528</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.024579034829534</v>
+        <v>-3.180371830687491</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.267991203908654</v>
+        <v>2.205674085565472</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.7068188577694919</v>
+        <v>0.6625582822670405</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.902270556815911</v>
+        <v>3.87571421151444</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994891</v>
+        <v>3.656346893994893</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.277054188837259</v>
+        <v>-3.432846984695216</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.178871631360979</v>
+        <v>2.116554513017796</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.7068188577694919</v>
+        <v>0.6625582822670405</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.914141045871324</v>
+        <v>3.887584700569854</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358295</v>
+        <v>3.674042696358297</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.546526990758967</v>
+        <v>-3.702319786616924</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.072293045111239</v>
+        <v>2.009975926768056</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.7068188577694919</v>
+        <v>0.6625582822670405</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.915351580390269</v>
+        <v>3.888795235088797</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637083</v>
+        <v>3.663523617637086</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.704071062488408</v>
+        <v>-3.859863858346365</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.013397158646784</v>
+        <v>1.951080040303601</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6399170526292175</v>
+        <v>0.5956564771267661</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.879332239533425</v>
+        <v>3.852775894231954</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.65216331330134</v>
+        <v>3.652163313301343</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.832921613190455</v>
+        <v>-3.988714409048411</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.956934791102155</v>
+        <v>1.894617672758972</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5989236437784959</v>
+        <v>0.5546630682760445</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.849814046959182</v>
+        <v>3.823257701657711</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215467</v>
+        <v>3.667976467215469</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.949889305829346</v>
+        <v>-4.105682101687303</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.072351770745643</v>
+        <v>2.010034652402459</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5989236437784959</v>
+        <v>0.5546630682760445</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.012018103658225</v>
+        <v>3.985461758356755</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456689</v>
+        <v>3.696553628456692</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.0346072480503</v>
+        <v>-4.190400043908256</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.033311231821076</v>
+        <v>1.970994113477892</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5138076148504496</v>
+        <v>0.4695470393479981</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.955795124265212</v>
+        <v>3.929238778963741</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253285</v>
+        <v>3.750058176253288</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.116542066319183</v>
+        <v>-4.272334862177139</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.010766722082013</v>
+        <v>1.94844960373883</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5038728692633694</v>
+        <v>0.4596122937609179</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.960063694481455</v>
+        <v>3.933507349179984</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717829</v>
+        <v>3.783647027717832</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.062803892918921</v>
+        <v>-4.218596688776877</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.041187629898021</v>
+        <v>1.978870511554837</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.5576110426636315</v>
+        <v>0.51335046716118</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.001232236977515</v>
+        <v>3.974675891676044</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616945</v>
+        <v>3.798310944616948</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.952797609441699</v>
+        <v>-4.108590405299656</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.077343030533084</v>
+        <v>2.015025912189901</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5808156145809067</v>
+        <v>0.5365550390784553</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.007307867372055</v>
+        <v>3.980751522070585</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203659</v>
+        <v>3.785578085203662</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.809738033700774</v>
+        <v>-3.96553082955873</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.138816871551429</v>
+        <v>2.076499753208246</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.588829041170886</v>
+        <v>0.5445684656684345</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.016365934048017</v>
+        <v>3.989809588746546</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436928</v>
+        <v>3.777251572436929</v>
       </c>
       <c r="C2029" t="n">
         <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.508291308228936</v>
+        <v>-3.664084104086893</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.2666564446227</v>
+        <v>2.204339326279517</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.8902757666427232</v>
+        <v>0.8460151911402718</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.204494852213656</v>
+        <v>4.177938506912184</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.502537343954342</v>
+        <v>3.566123051468638</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.495707000725822</v>
+        <v>3.51011543715249</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.508291308228936</v>
+        <v>-3.664084104086893</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.2666564446227</v>
+        <v>2.204339326279517</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.8902757666427232</v>
+        <v>0.8460151911402718</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.48877079771219</v>
+        <v>3.503179234138857</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240719.xlsx
+++ b/tame_output/ON/bt/strategyON_20240719.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.5%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>78.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>62.0%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-21</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -834,47 +834,47 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>63.0%</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>30.5%</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>59.2%</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>31.2%</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1.9</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>50.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.5%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.2%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.9%</t>
+          <t>122.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.2%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-69.1%</t>
+          <t>-67.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>455.3%</t>
+          <t>456.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-528.0%</t>
+          <t>-515.5%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-36.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-10.9%</t>
+          <t>-9.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.8%</t>
+          <t>-155.6%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-26.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-136.0%</t>
+          <t>-131.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-139.4%</t>
+          <t>-128.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>82.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.8%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-95.7%</t>
+          <t>-26.4%</t>
         </is>
       </c>
     </row>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191734</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097818</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094113</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199282</v>
+        <v>3.405960511199281</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.42463335496959</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297744</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539461</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.213502399279831</v>
+        <v>-9.154152358597896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5249191707206307</v>
+        <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.858242632280979</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.045892633936462</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.266288554880157</v>
+        <v>-9.295888482867587</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5449178431222053</v>
+        <v>-0.5567578143171774</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.953918118863376</v>
+        <v>-1.918838052095117</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.98960313182558</v>
+        <v>2.010651171886535</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.392325348248447</v>
+        <v>-9.421925276235877</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5926388318404063</v>
+        <v>-0.6044788030353785</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.928666496053634</v>
+        <v>-1.893586429285374</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.00744783414054</v>
+        <v>2.028495874201496</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.335253576352516</v>
+        <v>-9.364853504339946</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.565819787395633</v>
+        <v>-0.5776597585906051</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.928666496053634</v>
+        <v>-1.893586429285374</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.011438169826941</v>
+        <v>2.032486209887896</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.476925418076636</v>
+        <v>-9.506525346064066</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6239637509840228</v>
+        <v>-0.6358037221789949</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.928666496053634</v>
+        <v>-1.893586429285374</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.009962942928199</v>
+        <v>2.031010982989154</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.427334573651802</v>
+        <v>-9.456934501639232</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.589074003049217</v>
+        <v>-0.6009139742441891</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.8790756516288</v>
+        <v>-1.84399558486054</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.054770859747971</v>
+        <v>2.075818899808927</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.278416239179945</v>
+        <v>-9.308016167167375</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5425578029071572</v>
+        <v>-0.5543977741021293</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.847826060893627</v>
+        <v>-1.812745994125367</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.060469480542392</v>
+        <v>2.081517520603348</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.052571086460535</v>
+        <v>-9.082171014447965</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4426406687831848</v>
+        <v>-0.4544806399781565</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.805899385306463</v>
+        <v>-1.770819318538204</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.095204558930899</v>
+        <v>2.116252598991855</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.927992430122943</v>
+        <v>-8.957592358110373</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3916700616920887</v>
+        <v>-0.4035100328870609</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.805899385306463</v>
+        <v>-1.770819318538204</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.096343703486958</v>
+        <v>2.117391743547913</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.98088771816723</v>
+        <v>-9.01048764615466</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4101944027476958</v>
+        <v>-0.422034373942668</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.800944039218017</v>
+        <v>-1.765863972449758</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.101950685302134</v>
+        <v>2.122998725363089</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.908754542879349</v>
+        <v>-8.938354470866779</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.375607428393907</v>
+        <v>-0.3874473995888792</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.800944039218017</v>
+        <v>-1.765863972449758</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.10768438954077</v>
+        <v>2.128732429601726</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.837388150269701</v>
+        <v>-8.866988078257132</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3567981337439132</v>
+        <v>-0.3686381049388854</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.729577646608369</v>
+        <v>-1.69449757984011</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.140766962712694</v>
+        <v>2.161815002773649</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.743929116284477</v>
+        <v>-8.773529044271907</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3292980014627309</v>
+        <v>-0.3411379726577031</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.729577646608369</v>
+        <v>-1.69449757984011</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.130883481399786</v>
+        <v>2.151931521460742</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.476687315416079</v>
+        <v>-8.506287243403509</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2242358416147456</v>
+        <v>-0.2360758128097178</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.729577646608369</v>
+        <v>-1.69449757984011</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.129048920900412</v>
+        <v>2.150096960961368</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311947</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.378780276739588</v>
+        <v>-8.408380204727019</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1853733411176104</v>
+        <v>-0.1972133123125821</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.661591896747813</v>
+        <v>-1.626511829979553</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.169540055843285</v>
+        <v>2.190588095904241</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097242</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.354826735763631</v>
+        <v>-8.384426663751061</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1751234185817334</v>
+        <v>-0.1869633897767056</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.637638355771855</v>
+        <v>-1.602558289003596</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.184580686574353</v>
+        <v>2.205628726635309</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78931111201777</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.090766797440834</v>
+        <v>-8.120366725428264</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.08275975941436675</v>
+        <v>-0.09459973060933891</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.373578417449059</v>
+        <v>-1.338498350680799</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.329756333406279</v>
+        <v>2.350804373467235</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839723</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.383687173935995</v>
+        <v>-7.413287101923426</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1972850563272677</v>
+        <v>0.1854450851322955</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.373578417449059</v>
+        <v>-1.338498350680799</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.326969299745978</v>
+        <v>2.348017339806934</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388726</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.343502875569805</v>
+        <v>-7.373102803557235</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2137023995615852</v>
+        <v>0.2018624283666131</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.333394119082868</v>
+        <v>-1.298314052314609</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.351423502653534</v>
+        <v>2.37247154271449</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626472</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.180103004630443</v>
+        <v>-7.209702932617873</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2784291691580871</v>
+        <v>0.266589197963115</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.169994248143506</v>
+        <v>-1.134914181375246</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.448830246437908</v>
+        <v>2.469878286498864</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.946621782400844</v>
+        <v>-6.976221710388274</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3797460868877787</v>
+        <v>0.367906115692807</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9365130259139072</v>
+        <v>-0.9014329591456476</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.59684340861352</v>
+        <v>2.617891448674476</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.796955391393329</v>
+        <v>-6.826555319380759</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4367204329778258</v>
+        <v>0.4248804617828537</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8436095346713712</v>
+        <v>-0.8085294679031116</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.649693293046082</v>
+        <v>2.670741333107038</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.664679917762443</v>
+        <v>-6.694279845749873</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4849981091772073</v>
+        <v>0.4731581379822352</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.7113340610404846</v>
+        <v>-0.676253994272225</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.724426063971641</v>
+        <v>2.745474104032597</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.508941585202701</v>
+        <v>-6.538541513190131</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5501085028887407</v>
+        <v>0.5382685316937685</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.555595728480743</v>
+        <v>-0.5205156617124834</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.820684124195123</v>
+        <v>2.841732164256078</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960987</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.25994178651912</v>
+        <v>-6.28954171450655</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6626147635858319</v>
+        <v>0.6507747923908598</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.555595728480743</v>
+        <v>-0.5205156617124834</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.833590465418782</v>
+        <v>2.854638505479737</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.365531776292224</v>
+        <v>-6.395131704279654</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4924028380773713</v>
+        <v>0.4805628668823996</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6611857182538474</v>
+        <v>-0.6261056514855878</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.6422605419557</v>
+        <v>2.663308582016656</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.384266678410821</v>
+        <v>-6.413866606398251</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5334532191070189</v>
+        <v>0.5216132479120468</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6667817279139787</v>
+        <v>-0.6317016611457191</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.687447278036708</v>
+        <v>2.708495318097663</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710814</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.236326637003222</v>
+        <v>-6.265926564990652</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4727503129818911</v>
+        <v>0.4609103417869189</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6464608120054212</v>
+        <v>-0.6113807452371616</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.579760904893675</v>
+        <v>2.600808944954631</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409206</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.183357114749233</v>
+        <v>-6.212957042736663</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4852241356300082</v>
+        <v>0.4733841644350365</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5934912897514323</v>
+        <v>-0.5584112229831727</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.60282863199259</v>
+        <v>2.623876672053546</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098111</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.139808707978543</v>
+        <v>-6.169408635965973</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4956828862431912</v>
+        <v>0.4838429150482195</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5934912897514323</v>
+        <v>-0.5584112229831727</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.595868019897497</v>
+        <v>2.616916059958453</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493422</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.106445501499774</v>
+        <v>-6.136045429487204</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.523490523215842</v>
+        <v>0.5116505520208698</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5934912897514323</v>
+        <v>-0.5584112229831727</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.61033037427864</v>
+        <v>2.631378414339596</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.998186364377252</v>
+        <v>-6.027786292364683</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5613262985240457</v>
+        <v>0.5494863273290735</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5934912897514323</v>
+        <v>-0.5584112229831727</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.604862494737835</v>
+        <v>2.625910534798791</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.874895229560122</v>
+        <v>-5.904495157547552</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6081408464614748</v>
+        <v>0.5963008752665031</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4702001549343018</v>
+        <v>-0.4351200881660422</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.67633526963869</v>
+        <v>2.697383309699646</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.853746030656678</v>
+        <v>-5.883345958644108</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6243015042601776</v>
+        <v>0.6124615330652055</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.4490509560308584</v>
+        <v>-0.4139708892625988</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.696725767218081</v>
+        <v>2.717773807279037</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318094</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.609980588673234</v>
+        <v>-5.639580516660664</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7175883894006061</v>
+        <v>0.7057484182056339</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.4490509560308584</v>
+        <v>-0.4139708892625988</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.692506475565132</v>
+        <v>2.713554515626088</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.508217768395939</v>
+        <v>-5.537817696383369</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.76041783143154</v>
+        <v>0.7485778602365678</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4358318876384297</v>
+        <v>-0.4007518208701701</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.702562230520605</v>
+        <v>2.723610270581561</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.258367374446864</v>
+        <v>-5.287967302434295</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.853100063994872</v>
+        <v>0.8412600927998999</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4358318876384297</v>
+        <v>-0.4007518208701701</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.695304305504307</v>
+        <v>2.716352345565263</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.8359579870115</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.082475281979432</v>
+        <v>-5.112075209966862</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9270560245024932</v>
+        <v>0.9152160533075215</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4358318876384297</v>
+        <v>-0.4007518208701701</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.698903429024956</v>
+        <v>2.719951469085912</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392989</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.911028818956969</v>
+        <v>-4.940628746944399</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.008962115766032</v>
+        <v>0.9971221445710605</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2643854246159666</v>
+        <v>-0.229305357847707</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.815098812892987</v>
+        <v>2.836146852953943</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632783</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.83673925321863</v>
+        <v>-4.86633918120606</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.037698419677665</v>
+        <v>1.025858448482693</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1900958588776273</v>
+        <v>-0.1550157921093677</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.858693029952288</v>
+        <v>2.879741070013244</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883075</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.773103510984695</v>
+        <v>-4.802703438972125</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.067847517625556</v>
+        <v>1.056007546430584</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1264601166436928</v>
+        <v>-0.09138004987543319</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.901569276346966</v>
+        <v>2.922617316407922</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.661676751658775</v>
+        <v>-4.691276679646205</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.09361248013972</v>
+        <v>1.081772508944748</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1264601166436928</v>
+        <v>-0.09138004987543319</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.882763535130762</v>
+        <v>2.903811575191718</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242295</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.421246254853915</v>
+        <v>-4.450846182841345</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.191527755486541</v>
+        <v>1.179687784291569</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1139703801611675</v>
+        <v>0.1490504469294271</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.028764909838555</v>
+        <v>3.049812949899511</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367686</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.34900368668272</v>
+        <v>-4.37860361467015</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.224354096589839</v>
+        <v>1.212514125394867</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1139703801611675</v>
+        <v>0.1490504469294271</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.032694223673376</v>
+        <v>3.053742263734331</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879967</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.296005364401332</v>
+        <v>-4.325605292388762</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.246232009419735</v>
+        <v>1.234392038224763</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1693066391631063</v>
+        <v>0.2043867059313659</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.066574562991879</v>
+        <v>3.087622603052834</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.187200478921605</v>
+        <v>-4.216800406909035</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.286752034831619</v>
+        <v>1.274912063636647</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1693066391631063</v>
+        <v>0.2043867059313659</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.063572634211873</v>
+        <v>3.084620674272828</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.967179680884594</v>
+        <v>-3.996779608872024</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.376339391057037</v>
+        <v>1.364499419862065</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3105264842310866</v>
+        <v>0.3456065509993462</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.149883578263275</v>
+        <v>3.17093161832423</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539951</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.834311991821316</v>
+        <v>-3.863911919808746</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.445380649484172</v>
+        <v>1.4335406782892</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3105264842310866</v>
+        <v>0.3456065509993462</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.165777761065098</v>
+        <v>3.186825801126054</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496264</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.714138908456817</v>
+        <v>-3.743738836444248</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.494595727270273</v>
+        <v>1.482755756075301</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4306995675955855</v>
+        <v>0.4657796343638451</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.239027455524099</v>
+        <v>3.260075495585055</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551577</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.56946676335708</v>
+        <v>-3.59906669134451</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.562552687871608</v>
+        <v>1.550712716676636</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5753717126953229</v>
+        <v>0.6104517794635825</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.335918845145382</v>
+        <v>3.356966885206337</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.629341590714772</v>
+        <v>-3.658941518702203</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.524640248329957</v>
+        <v>1.512800277134985</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5154968853376308</v>
+        <v>0.5505769521058904</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.286031440132192</v>
+        <v>3.307079480193148</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674515</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.509521359803935</v>
+        <v>-3.539121287791365</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.587857509928501</v>
+        <v>1.576017538733528</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5154968853376308</v>
+        <v>0.5505769521058904</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.3013206093664</v>
+        <v>3.322368649427356</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430694</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.511991066265741</v>
+        <v>-3.541590994253171</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.49451382666622</v>
+        <v>1.482673855471248</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5130271788758247</v>
+        <v>0.5481072456440843</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.207482984811759</v>
+        <v>3.228531024872714</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003604</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.580361252589751</v>
+        <v>-3.609961180577181</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.386427613621917</v>
+        <v>1.374587642426945</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5223028779120397</v>
+        <v>0.5573829446802993</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.132310265718789</v>
+        <v>3.153358305779745</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508372</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.594149305436797</v>
+        <v>-3.623749233424228</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.37134910111499</v>
+        <v>1.359509129920018</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5223028779120397</v>
+        <v>0.5573829446802993</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.12274697435068</v>
+        <v>3.143795014411636</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.625142464765503</v>
+        <v>-3.654742392752933</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.183661402423895</v>
+        <v>1.171821431228922</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5223028779120397</v>
+        <v>0.5573829446802993</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.947456539391067</v>
+        <v>2.968504579452023</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.449668204973034</v>
+        <v>-3.479268132960464</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.25841833833267</v>
+        <v>1.246578367137698</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5223028779120397</v>
+        <v>0.5573829446802993</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.952023771382855</v>
+        <v>2.97307181144381</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.560604457614282</v>
+        <v>-3.590204385601712</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.189785866037378</v>
+        <v>1.177945894842406</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5223028779120397</v>
+        <v>0.5573829446802993</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.927765800144062</v>
+        <v>2.948813840205017</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111297</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.526940912142</v>
+        <v>-3.556540840129431</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.13178959762774</v>
+        <v>1.119949626432768</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5559664233843216</v>
+        <v>0.5910464901525811</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.876502240828881</v>
+        <v>2.897550280889837</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264166</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.467088292938277</v>
+        <v>-3.496688220925707</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.165903031741362</v>
+        <v>1.15406306054639</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5559664233843216</v>
+        <v>0.5910464901525811</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.886674627261013</v>
+        <v>2.907722667321969</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742302</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.3808448299119</v>
+        <v>-3.41044475789933</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.195346687525773</v>
+        <v>1.183506716330801</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5559664233843216</v>
+        <v>0.5910464901525811</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.881620897834873</v>
+        <v>2.902668937895829</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316049</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.42615164931088</v>
+        <v>-3.45575157729831</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.168999735210707</v>
+        <v>1.157159764015735</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5151562603750908</v>
+        <v>0.5502363271433504</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.848910575473861</v>
+        <v>2.869958615534816</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803194</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.455184754013181</v>
+        <v>-3.484784682000611</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.157938366362887</v>
+        <v>1.146098395167916</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5151562603750908</v>
+        <v>0.5502363271433504</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.849462448506962</v>
+        <v>2.870510488567918</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809502</v>
+        <v>3.733390600809498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.362374272562322</v>
+        <v>-3.391974200549752</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.124335250834597</v>
+        <v>1.112495279639625</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6079667418259501</v>
+        <v>0.6430468085942097</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.834421429268843</v>
+        <v>2.855469469329799</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560427</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.40676374189175</v>
+        <v>-3.43636366987918</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.108452939027427</v>
+        <v>1.096612967832455</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5635772724965225</v>
+        <v>0.598657339264782</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.809661223595787</v>
+        <v>2.830709263656743</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.72107719547274</v>
+        <v>3.721077195472737</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.294092523655499</v>
+        <v>-3.32369245164293</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.14859713483365</v>
+        <v>1.136757163638678</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6762484907327726</v>
+        <v>0.7113285575010322</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.872339663049261</v>
+        <v>2.893387703110216</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798539</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.181715522472827</v>
+        <v>-3.211315450460257</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.199039231137386</v>
+        <v>1.187199259942414</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6762484907327726</v>
+        <v>0.7113285575010322</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.877830958879928</v>
+        <v>2.898878998940884</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498867</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.20949592037418</v>
+        <v>-3.23909584836161</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.199424273745384</v>
+        <v>1.187584302550412</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6484680928314195</v>
+        <v>0.6835481595996791</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.872659921907655</v>
+        <v>2.893707961968611</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705327</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.292497201399459</v>
+        <v>-3.322097129386889</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.004579481335925</v>
+        <v>0.9927395101409535</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6298972083042458</v>
+        <v>0.6649772750725054</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.699873111192004</v>
+        <v>2.72092115125296</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729272</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.40111127984279</v>
+        <v>-3.43071120783022</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.081283510677799</v>
+        <v>1.069443539482827</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6298972083042458</v>
+        <v>0.6649772750725054</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.82002277191121</v>
+        <v>2.841070811972165</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190771</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.365702241594647</v>
+        <v>-3.395302169582077</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.109960152079379</v>
+        <v>1.098120180884407</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6298972083042458</v>
+        <v>0.6649772750725054</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.834535798013533</v>
+        <v>2.855583838074488</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913428</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.327318579036496</v>
+        <v>-3.356918507023926</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.122733058445008</v>
+        <v>1.110893087250036</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.668280870862397</v>
+        <v>0.7033609376306565</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.854985436890792</v>
+        <v>2.876033476951748</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532488</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.15020224900133</v>
+        <v>-3.17980217698876</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.190308619304376</v>
+        <v>1.178468648109404</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.668280870862397</v>
+        <v>0.7033609376306565</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.851714465736094</v>
+        <v>2.87276250579705</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.195294493834876</v>
+        <v>-3.224894421822306</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.172955113132871</v>
+        <v>1.161115141937899</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6063848276930072</v>
+        <v>0.6414648944612668</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.815260231596373</v>
+        <v>2.836308271657329</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011236</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.015919072596108</v>
+        <v>-3.045519000583538</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.238492256934792</v>
+        <v>1.226652285739821</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7631615858637258</v>
+        <v>0.7982416526319854</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.903113261805219</v>
+        <v>2.924161301866175</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.71699171898223</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.060933286116714</v>
+        <v>-3.090533214104144</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.20129402685814</v>
+        <v>1.189454055663168</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7328126905491212</v>
+        <v>0.7678927573173808</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.865711379948046</v>
+        <v>2.886759420009001</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.32793779638915</v>
+        <v>-3.35753772437658</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.100183785088111</v>
+        <v>1.088343813893139</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5384496525061726</v>
+        <v>0.5735297192744322</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.754785119461222</v>
+        <v>2.775833159522178</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760814</v>
+        <v>3.70230945476081</v>
       </c>
       <c r="C1960" t="n">
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.429135577826322</v>
+        <v>-3.458735505813753</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.058908594409744</v>
+        <v>1.047068623214772</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4700408389608534</v>
+        <v>0.5051209057291131</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.712943753230532</v>
+        <v>2.733991793291488</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815458</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.42262461121201</v>
+        <v>-3.45222453919944</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.059112942609786</v>
+        <v>1.047272971414813</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4700408389608534</v>
+        <v>0.5051209057291131</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.710543714784849</v>
+        <v>2.731591754845805</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378102</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.403586483504712</v>
+        <v>-3.433186411492143</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.063252912900949</v>
+        <v>1.051412941705977</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4118572276296589</v>
+        <v>0.4469372943979185</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.672158267194377</v>
+        <v>2.693206307255333</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131252</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.602625799555262</v>
+        <v>2.553515657498219</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.43471311465533</v>
+        <v>-3.464313042642761</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.228384129379383</v>
+        <v>1.167434016127367</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4118572276296589</v>
+        <v>0.4469372943979185</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.849740136133058</v>
+        <v>2.82167803413697</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067868</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.603459128541396</v>
+        <v>2.554348986484352</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.448579875989248</v>
+        <v>-3.478179803976678</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.223670753831949</v>
+        <v>1.162720640579934</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3739993108958359</v>
+        <v>0.4090793776640956</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.827858715078897</v>
+        <v>2.79979661308281</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789126</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.609467658938322</v>
+        <v>2.560357516881278</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.403775704449318</v>
+        <v>-3.433375632436748</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.247600952844847</v>
+        <v>1.186650839592831</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3739993108958359</v>
+        <v>0.4090793776640956</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.833867245475823</v>
+        <v>2.805805143479736</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519911</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.507417880215521</v>
+        <v>2.458307738158477</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.256032734214316</v>
+        <v>-3.285632662201746</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.204648362216048</v>
+        <v>1.143698248964032</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5418066681307191</v>
+        <v>0.5768867348989788</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.832501881093953</v>
+        <v>2.804439779097865</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181172</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.510211501747002</v>
+        <v>2.461101359689958</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.358047416745537</v>
+        <v>-3.387647344732967</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.16663611073504</v>
+        <v>1.105685997483024</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5418066681307191</v>
+        <v>0.5768867348989788</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.835295502625434</v>
+        <v>2.807233400629346</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.51087385013866</v>
+        <v>2.461763708081617</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.351894710692752</v>
+        <v>-3.381494638680183</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.169759541547812</v>
+        <v>1.108809428295797</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5479593741835034</v>
+        <v>0.5830394409517631</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.839649474648763</v>
+        <v>2.811587372652675</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890612</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.509954326878771</v>
+        <v>2.460844184821727</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.368704008843254</v>
+        <v>-3.398303936830684</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.162116299027722</v>
+        <v>1.101166185775706</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5311500760330017</v>
+        <v>0.5662301428012615</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.828644372498572</v>
+        <v>2.800582270502484</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798428</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.576289880675592</v>
+        <v>2.527179738618548</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.306406010067132</v>
+        <v>-3.336005938054562</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.253371052334991</v>
+        <v>1.192420939082976</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5311500760330017</v>
+        <v>0.5662301428012615</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.894979926295393</v>
+        <v>2.866917824299305</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.378581882389719</v>
+        <v>2.329471740332675</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.104615812401974</v>
+        <v>-3.134215740389404</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.136379133115182</v>
+        <v>1.075429019863166</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7291682682021561</v>
+        <v>0.7642483349704159</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.816082843311013</v>
+        <v>2.788020741314925</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852427</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.448872114711894</v>
+        <v>2.39976197265485</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.939802809323127</v>
+        <v>-2.969402737310557</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.272594566668896</v>
+        <v>1.21164445341688</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.893981271281003</v>
+        <v>0.9290613380492628</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.985260877480496</v>
+        <v>2.957198775484408</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319547</v>
+        <v>3.819063300319543</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.463499850827938</v>
+        <v>2.414389708770894</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.037543353948101</v>
+        <v>-3.067143281935532</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.24812608493495</v>
+        <v>1.187175971682934</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8780919931480229</v>
+        <v>0.9131720599162827</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.990355046716751</v>
+        <v>2.962292944720664</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.462035831652609</v>
+        <v>2.412925689595566</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.213881114071031</v>
+        <v>-3.243481042058461</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.17612696171045</v>
+        <v>1.115176848458434</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7017542330250934</v>
+        <v>0.7368342997933532</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.883088371467665</v>
+        <v>2.855026269471578</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.460527449692538</v>
+        <v>2.411417307635494</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.137459067639104</v>
+        <v>-3.167058995626534</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.205187398323149</v>
+        <v>1.144237285071133</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7017542330250934</v>
+        <v>0.7368342997933532</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.881579989507594</v>
+        <v>2.853517887511506</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316251</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.460390317127974</v>
+        <v>2.41128017507093</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.093085936000535</v>
+        <v>-3.122685863987965</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.222799518414013</v>
+        <v>1.161849405161997</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.746127364663662</v>
+        <v>0.7812074314319218</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.908066735926171</v>
+        <v>2.880004633930084</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105968</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.454784111266564</v>
+        <v>2.405673969209521</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.970251715113368</v>
+        <v>-2.999851643100798</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.26632700090747</v>
+        <v>1.205376887655454</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.746127364663662</v>
+        <v>0.7812074314319218</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.902460530064762</v>
+        <v>2.874398428068674</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190326</v>
+        <v>3.833011148190322</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.461165868294369</v>
+        <v>2.412055726237325</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.922595984552312</v>
+        <v>-2.952195912539742</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.291771050159697</v>
+        <v>1.230820936907681</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7937830952247177</v>
+        <v>0.8288631619929775</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.9374357254292</v>
+        <v>2.909373623433112</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569618</v>
+        <v>3.822678210569615</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.466058241669094</v>
+        <v>2.41694809961205</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.822077826053557</v>
+        <v>-2.851677754040987</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.336870686933924</v>
+        <v>1.275920573681908</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8943012537234722</v>
+        <v>0.9293813204917321</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.002638993903178</v>
+        <v>2.974576891907089</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557294</v>
+        <v>3.82880887755729</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.452812914144966</v>
+        <v>2.403702772087922</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.882744416455946</v>
+        <v>-2.912344344443377</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.29935872324884</v>
+        <v>1.238408609996824</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8126029370049386</v>
+        <v>0.8476830037731984</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.940374676347929</v>
+        <v>2.912312574351841</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932768</v>
+        <v>3.816837033932765</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.456910616755595</v>
+        <v>2.407800474698551</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.837906014847548</v>
+        <v>-2.867505942834979</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.321391786502828</v>
+        <v>1.260441673250812</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.817146369949808</v>
+        <v>0.8522264367180679</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.94719843872548</v>
+        <v>2.919136336729391</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917052</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.461071556386673</v>
+        <v>2.411961414329629</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.938664650604547</v>
+        <v>-2.968264578591977</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.285249271831107</v>
+        <v>1.224299158579091</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7283208012228026</v>
+        <v>0.7634008679910624</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.898064037120355</v>
+        <v>2.870001935124266</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82668474540596</v>
+        <v>3.826684745405957</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.46695115891451</v>
+        <v>2.417841016857466</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.894461813518646</v>
+        <v>-2.924061741506077</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.308810009193304</v>
+        <v>1.247859895941288</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7725236383087031</v>
+        <v>0.8076037050769629</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.930465341899732</v>
+        <v>2.902403239903644</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265645</v>
+        <v>3.838199629265643</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.465361159383757</v>
+        <v>2.416251017326713</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.93144084118209</v>
+        <v>-2.96104076916952</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.292428398597174</v>
+        <v>1.231478285345158</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8094975401000336</v>
+        <v>0.8445776068682934</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.951059683443778</v>
+        <v>2.92299758144769</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.516608924566797</v>
+        <v>2.467498782509753</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.773149423642817</v>
+        <v>-2.802749351630248</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.406992730795923</v>
+        <v>1.346042617543907</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8094975401000336</v>
+        <v>0.8445776068682934</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.002307448626818</v>
+        <v>2.974245346630729</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321023</v>
+        <v>3.865338681321019</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.51504962916105</v>
+        <v>2.465939487104006</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.565507420008341</v>
+        <v>-2.595107347995771</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.488490236843967</v>
+        <v>1.42754012359195</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.01713954373451</v>
+        <v>1.05221961050277</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.125333355401756</v>
+        <v>3.097271253405668</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475135</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.50999785739932</v>
+        <v>2.460887715342276</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.514475327285813</v>
+        <v>-2.544075255273243</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.503851302171248</v>
+        <v>1.442901188919232</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.068171636457038</v>
+        <v>1.103251703225298</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.150900839273543</v>
+        <v>3.122838737277455</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404854</v>
+        <v>3.84254736040485</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.527185261492025</v>
+        <v>2.478075119434981</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.449251146158607</v>
+        <v>-2.478851074146037</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.547128378714835</v>
+        <v>1.486178265462819</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.133395817584243</v>
+        <v>1.168475884352503</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.207222752042572</v>
+        <v>3.179160650046483</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882558</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.523146233791306</v>
+        <v>2.474036091734261</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.411824126087474</v>
+        <v>-2.441424054074904</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.558060159042569</v>
+        <v>1.497110045790553</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.138647355613425</v>
+        <v>1.173727422381685</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.206334647159361</v>
+        <v>3.178272545163273</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.845169808992657</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.524403026122546</v>
+        <v>2.475292884065502</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.431935782122182</v>
+        <v>-2.461535710109612</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.551272288959926</v>
+        <v>1.49032217570791</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.149674700610844</v>
+        <v>1.184754767379104</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.214207846489053</v>
+        <v>3.186145744492965</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636284</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.684960797143757</v>
+        <v>2.635850655086712</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.378190967694977</v>
+        <v>-2.407790895682407</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.733327985752019</v>
+        <v>1.672377872500002</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.159738010051306</v>
+        <v>1.194818076819566</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.380803603174541</v>
+        <v>3.352741501178452</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957625</v>
+        <v>3.813222820957622</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.805073706361574</v>
+        <v>2.75596356430453</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.303408706669964</v>
+        <v>-2.333008634657395</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.883353799379841</v>
+        <v>1.822403686127825</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.234520271076319</v>
+        <v>1.269600337844579</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.545785869007366</v>
+        <v>3.517723767011277</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998755</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.796781682375433</v>
+        <v>2.747671540318389</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.277324622406157</v>
+        <v>-2.306924550393587</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.885495409099223</v>
+        <v>1.824545295847207</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.234520271076319</v>
+        <v>1.269600337844579</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.537493845021225</v>
+        <v>3.509431743025136</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.794974877959212</v>
+        <v>2.745864735902168</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.19919344155721</v>
+        <v>-2.22879336954464</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.914941077022581</v>
+        <v>1.853990963770565</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.308697081960004</v>
+        <v>1.343777148728264</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.580193127135215</v>
+        <v>3.552131025139126</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959856</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.812529283686004</v>
+        <v>2.76341914162896</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.269028318429841</v>
+        <v>-2.219900908151357</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.90456153200032</v>
+        <v>1.87510235405467</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.308697081960004</v>
+        <v>1.343777148728264</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.597747532862006</v>
+        <v>3.569685430865918</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.804384331090588</v>
+        <v>2.755274189033543</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.437504435399719</v>
+        <v>-2.388377025121235</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.829026132616953</v>
+        <v>1.799566954671302</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.280749246243423</v>
+        <v>1.315829313011683</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.572833878836642</v>
+        <v>3.544771776840554</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782705</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.785654028278449</v>
+        <v>2.736543886221405</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.739704906538135</v>
+        <v>-1.690577496259651</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.089415641349448</v>
+        <v>2.059956463403798</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.210401186873012</v>
+        <v>1.245481253641272</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.511894740402257</v>
+        <v>3.483832638406169</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632633</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.776318050775354</v>
+        <v>2.72720790871831</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.716983802854983</v>
+        <v>-1.667856392576499</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.089168105319613</v>
+        <v>2.059708927373963</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.210401186873012</v>
+        <v>1.245481253641272</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.502558762899162</v>
+        <v>3.474496660903073</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.78320569677767</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.935224176626523</v>
+        <v>2.886114034569479</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.715258759564939</v>
+        <v>-1.666131349286455</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.2487642484868</v>
+        <v>2.21930507054115</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.212126230163056</v>
+        <v>1.247206296931316</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.662499914724357</v>
+        <v>3.634437812728269</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644412</v>
+        <v>3.779933725644409</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.97230199912017</v>
+        <v>2.923191857063125</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.870039766343194</v>
+        <v>-1.82091235606471</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.223929668269145</v>
+        <v>2.194470490323494</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.17875855610858</v>
+        <v>1.21383862287684</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.679557132785318</v>
+        <v>3.65149503078923</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799963</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.968977355109715</v>
+        <v>2.919867213052671</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.862985076128021</v>
+        <v>-1.813857665849537</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.223426900344759</v>
+        <v>2.193967722399109</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.185813246323754</v>
+        <v>1.220893313092014</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.680465302903967</v>
+        <v>3.652403200907879</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.978983508754456</v>
+        <v>2.929873366697412</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.836033851801533</v>
+        <v>-1.786906441523049</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.244213543720096</v>
+        <v>2.214754365774446</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.200693592351473</v>
+        <v>1.235773659119733</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.69939966416534</v>
+        <v>3.671337562169252</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784107</v>
+        <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.163086640899416</v>
+        <v>3.113976498842372</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.971986859857849</v>
+        <v>-1.922859449579365</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.373935472642529</v>
+        <v>2.344476294696879</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.200693592351473</v>
+        <v>1.235773659119733</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.8835027963103</v>
+        <v>3.855440694314212</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714425</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.155203335802409</v>
+        <v>3.106093193745365</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.994394977662721</v>
+        <v>-1.945267567384237</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.357088920423574</v>
+        <v>2.327629742477923</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.200693592351473</v>
+        <v>1.235773659119733</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.875619491213293</v>
+        <v>3.847557389217205</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155032</v>
+        <v>3.719118627155029</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.157257335352047</v>
+        <v>3.108147193295002</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.14240074514212</v>
+        <v>-2.093273334863636</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.299940612981451</v>
+        <v>2.2704814350358</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.113966583487931</v>
+        <v>1.149046650256191</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.825637285444806</v>
+        <v>3.797575183448718</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161978</v>
+        <v>3.729452285161974</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.213511053073894</v>
+        <v>3.16440091101685</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.15184167103065</v>
+        <v>-2.102714260752166</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.352417960347887</v>
+        <v>2.322958782402236</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.236393701031323</v>
+        <v>1.271473767799583</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.955347273692688</v>
+        <v>3.9272851716966</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321635</v>
+        <v>3.714941193321631</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.216402147619195</v>
+        <v>3.167292005562151</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.204115278366291</v>
+        <v>-2.154987868087808</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.334399611958931</v>
+        <v>2.30494043401328</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.184120093695681</v>
+        <v>1.219200160463942</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.926874203836604</v>
+        <v>3.898812101840516</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347703</v>
+        <v>3.7278981863477</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.21451396051297</v>
+        <v>3.165403818455926</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.280445255967197</v>
+        <v>-2.231317845688713</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.301979433812344</v>
+        <v>2.272520255866693</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.184120093695681</v>
+        <v>1.219200160463942</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.924986016730379</v>
+        <v>3.896923914734291</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887747</v>
+        <v>3.710654104887744</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.209334190115832</v>
+        <v>3.160224048058788</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.392202208582498</v>
+        <v>-2.343074798304015</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.252096882369086</v>
+        <v>2.222637704423435</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.07236314108038</v>
+        <v>1.10744320784864</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.85275207476406</v>
+        <v>3.824689972767973</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343065</v>
+        <v>3.712897612343061</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.207768200325984</v>
+        <v>3.15865805826894</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.390361189524247</v>
+        <v>-2.341233779245763</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.251267300202538</v>
+        <v>2.221808122256888</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.073631367751849</v>
+        <v>1.108711434520109</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.851947020977094</v>
+        <v>3.823884918981006</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647105</v>
+        <v>3.754911907647101</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.220841607191903</v>
+        <v>3.171731465134859</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.5226624816218</v>
+        <v>-2.473535071343317</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.211420190229436</v>
+        <v>2.181961012283785</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.073631367751849</v>
+        <v>1.108711434520109</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.865020427843012</v>
+        <v>3.836958325846925</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763531</v>
+        <v>3.749896851763528</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.220841607191903</v>
+        <v>3.171731465134859</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.52422412443666</v>
+        <v>-2.475096714158177</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.210795533103492</v>
+        <v>2.181336355157841</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.073631367751849</v>
+        <v>1.108711434520109</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.865020427843012</v>
+        <v>3.836958325846925</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392115</v>
+        <v>3.715834055392111</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.219365648318905</v>
+        <v>3.170255506261861</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.552124911546133</v>
+        <v>-2.50299750126765</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.198159259386705</v>
+        <v>2.168700081441054</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.039034443608914</v>
+        <v>1.074114510377174</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.842786314484254</v>
+        <v>3.814724212488166</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172525</v>
+        <v>3.684909939172522</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.216130092296104</v>
+        <v>3.16701995023906</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.674651014249027</v>
+        <v>-2.625523603970544</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.145913262282746</v>
+        <v>2.116454084337095</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9165083409060202</v>
+        <v>0.9515884076742802</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.766035096839716</v>
+        <v>3.737972994843628</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.619362241971074</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.282836051886608</v>
+        <v>3.233725909829563</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.820186498744192</v>
+        <v>-2.64558492524705</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.154405028075184</v>
+        <v>2.175135515416996</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7709728564108553</v>
+        <v>0.9315270863977732</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.745419765733121</v>
+        <v>3.792642161668228</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.640764248199801</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.423147770888455</v>
+        <v>3.37403762883141</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.076907316739016</v>
+        <v>-2.902305743241874</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.192028419879101</v>
+        <v>2.212758907220914</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6625582822670405</v>
+        <v>0.8231125122539583</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.820682740248679</v>
+        <v>3.867905136183786</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.668303164622232</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.492128040034094</v>
+        <v>3.44301789797705</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.230893734515157</v>
+        <v>-3.056292161018015</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.199414121914284</v>
+        <v>2.220144609256097</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6625582822670405</v>
+        <v>0.8231125122539583</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.889663009394319</v>
+        <v>3.936885405329425</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808528</v>
+        <v>3.619937176808524</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.478179242154215</v>
+        <v>3.429069100097171</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.180371830687491</v>
+        <v>-3.005770257190349</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.205674085565472</v>
+        <v>2.226404572907284</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6625582822670405</v>
+        <v>0.8231125122539583</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.87571421151444</v>
+        <v>3.922936607449547</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994893</v>
+        <v>3.656346893994889</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.490049731209629</v>
+        <v>3.440939589152585</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.432846984695216</v>
+        <v>-3.258245411198073</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.116554513017796</v>
+        <v>2.137285000359609</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6625582822670405</v>
+        <v>0.8231125122539583</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.887584700569854</v>
+        <v>3.934807096504961</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358297</v>
+        <v>3.674042696358293</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.491260265728573</v>
+        <v>3.442150123671529</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.702319786616924</v>
+        <v>-3.527718213119782</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.009975926768056</v>
+        <v>2.030706414109869</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6625582822670405</v>
+        <v>0.8231125122539583</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.888795235088797</v>
+        <v>3.936017631023904</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637086</v>
+        <v>3.663523617637082</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.495382007955894</v>
+        <v>3.44627186589885</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.859863858346365</v>
+        <v>-3.685262284849223</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.951080040303601</v>
+        <v>1.971810527645414</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5956564771267661</v>
+        <v>0.7562107071136839</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.852775894231954</v>
+        <v>3.899998290167061</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301343</v>
+        <v>3.652163313301338</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.490459860692084</v>
+        <v>3.44134971863504</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.988714409048411</v>
+        <v>-3.814112835551269</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.894617672758972</v>
+        <v>1.915348160100785</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5546630682760445</v>
+        <v>0.7152172982629623</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.823257701657711</v>
+        <v>3.870480097592818</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215469</v>
+        <v>3.667976467215465</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.652663917391128</v>
+        <v>3.603553775334084</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.105682101687303</v>
+        <v>-3.93108052819016</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.010034652402459</v>
+        <v>2.030765139744273</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5546630682760445</v>
+        <v>0.7152172982629623</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.985461758356755</v>
+        <v>4.032684154291862</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456692</v>
+        <v>3.696553628456687</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.647510555354942</v>
+        <v>3.598400413297898</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.190400043908256</v>
+        <v>-4.015798470411114</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.970994113477892</v>
+        <v>1.991724600819705</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4695470393479981</v>
+        <v>0.6301012693349159</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.929238778963741</v>
+        <v>3.976461174898848</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253288</v>
+        <v>3.750058176253283</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.657739972923433</v>
+        <v>3.608629830866389</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.272334862177139</v>
+        <v>-4.097733288679997</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.94844960373883</v>
+        <v>1.969180091080643</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4596122937609179</v>
+        <v>0.6201665237478358</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.933507349179984</v>
+        <v>3.980729745115091</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717832</v>
+        <v>3.783647027717827</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.666665611379336</v>
+        <v>3.617555469322292</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.218596688776877</v>
+        <v>-4.043995115279735</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.978870511554837</v>
+        <v>1.99960099889665</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.51335046716118</v>
+        <v>0.6739046971480979</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.974675891676044</v>
+        <v>4.02189828761115</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616948</v>
+        <v>3.798310944616944</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.658818498623511</v>
+        <v>3.609708356566467</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.108590405299656</v>
+        <v>-3.933988831802513</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.015025912189901</v>
+        <v>2.035756399531715</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5365550390784553</v>
+        <v>0.6971092690653731</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.980751522070585</v>
+        <v>4.027973918005691</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203662</v>
+        <v>3.785578085203658</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.663068509345485</v>
+        <v>3.613958367288441</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.96553082955873</v>
+        <v>-3.790929256061588</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.076499753208246</v>
+        <v>2.097230240550059</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.5445684656684345</v>
+        <v>0.7051226956553523</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.989809588746546</v>
+        <v>4.037031984681652</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436929</v>
+        <v>3.777251572436924</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.670329392228021</v>
+        <v>3.621219250170977</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.664084104086893</v>
+        <v>-3.489482530589751</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.204339326279517</v>
+        <v>2.22506981362133</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.8460151911402718</v>
+        <v>1.00656942112719</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.177938506912184</v>
+        <v>4.225160902847291</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.566123051468638</v>
+        <v>3.840500396882913</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.51011543715249</v>
+        <v>3.622190427923688</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.664084104086893</v>
+        <v>-3.538860961258333</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.204339326279517</v>
+        <v>2.206289619106607</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.8460151911402718</v>
+        <v>0.9571909904586066</v>
       </c>
       <c r="G2030" t="n">
-        <v>3.503179234138857</v>
+        <v>4.196505022198852</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240719.xlsx
+++ b/tame_output/ON/bt/strategyON_20240719.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.5%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>14.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.6%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.09</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>62.0%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-72.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>110.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.7%</t>
+          <t>122.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-47.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.8%</t>
+          <t>-67.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.9%</t>
+          <t>454.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-515.5%</t>
+          <t>-502.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.1%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>22.6%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>77.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-9.8%</t>
+          <t>-11.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.6%</t>
+          <t>-145.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>-26.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-3.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.9%</t>
+          <t>-132.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-128.3%</t>
+          <t>-136.5%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.3%</t>
+          <t>82.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.6%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760737</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706668</v>
+        <v>3.298730590706667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296835</v>
+        <v>3.299918119296834</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.295888482867587</v>
+        <v>-9.206938514198223</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5567578143171774</v>
+        <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.918838052095117</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.010651171886535</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.421925276235877</v>
+        <v>-9.332975307566512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6044788030353785</v>
+        <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.893586429285374</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.028495874201496</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.364853504339946</v>
+        <v>-9.275903535670581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5776597585906051</v>
+        <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.893586429285374</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.032486209887896</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.506525346064066</v>
+        <v>-9.417575377394702</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6358037221789949</v>
+        <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.893586429285374</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.031010982989154</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.456934501639232</v>
+        <v>-9.367984532969867</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6009139742441891</v>
+        <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.84399558486054</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.075818899808927</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.308016167167375</v>
+        <v>-9.219066198498011</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5543977741021293</v>
+        <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.812745994125367</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.081517520603348</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.082171014447965</v>
+        <v>-8.993221045778601</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4544806399781565</v>
+        <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.770819318538204</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.116252598991855</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.957592358110373</v>
+        <v>-8.868642389441009</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4035100328870609</v>
+        <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.770819318538204</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.117391743547913</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.01048764615466</v>
+        <v>-8.921537677485295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.422034373942668</v>
+        <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.765863972449758</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.122998725363089</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.938354470866779</v>
+        <v>-8.849404502197414</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3874473995888792</v>
+        <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.765863972449758</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.128732429601726</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.866988078257132</v>
+        <v>-8.778038109587767</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3686381049388854</v>
+        <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.69449757984011</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.161815002773649</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.773529044271907</v>
+        <v>-8.684579075602542</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3411379726577031</v>
+        <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.69449757984011</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.151931521460742</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.506287243403509</v>
+        <v>-8.417337274734145</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2360758128097178</v>
+        <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.69449757984011</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.150096960961368</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.408380204727019</v>
+        <v>-8.319430236057654</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1972133123125821</v>
+        <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.626511829979553</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.190588095904241</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.384426663751061</v>
+        <v>-8.295476695081696</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1869633897767056</v>
+        <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.602558289003596</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.205628726635309</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.120366725428264</v>
+        <v>-8.031416756758899</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.09459973060933891</v>
+        <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.338498350680799</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.350804373467235</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839723</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.413287101923426</v>
+        <v>-7.324337133254061</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1854450851322955</v>
+        <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.338498350680799</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.348017339806934</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388726</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.373102803557235</v>
+        <v>-7.284152834887871</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2018624283666131</v>
+        <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.298314052314609</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.37247154271449</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.856161751626472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.209702932617873</v>
+        <v>-7.120752963948508</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.266589197963115</v>
+        <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.134914181375246</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.469878286498864</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.976221710388274</v>
+        <v>-6.88727174171891</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.367906115692807</v>
+        <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.9014329591456476</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.617891448674476</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.826555319380759</v>
+        <v>-6.737605350711394</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4248804617828537</v>
+        <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.8085294679031116</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.670741333107038</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.694279845749873</v>
+        <v>-6.605329877080508</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4731581379822352</v>
+        <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.676253994272225</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.745474104032597</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.538541513190131</v>
+        <v>-6.449591544520766</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5382685316937685</v>
+        <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.5205156617124834</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.841732164256078</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.28954171450655</v>
+        <v>-6.200591745837185</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6507747923908598</v>
+        <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.5205156617124834</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.854638505479737</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.395131704279654</v>
+        <v>-6.30618173561029</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4805628668823996</v>
+        <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6261056514855878</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.663308582016656</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.413866606398251</v>
+        <v>-6.324916637728887</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5216132479120468</v>
+        <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6317016611457191</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.708495318097663</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.265926564990652</v>
+        <v>-6.176976596321287</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4609103417869189</v>
+        <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.6113807452371616</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.600808944954631</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.212957042736663</v>
+        <v>-6.124007074067299</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4733841644350365</v>
+        <v>0.5089641519027821</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5584112229831727</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.623876672053546</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.169408635965973</v>
+        <v>-6.080458667296608</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4838429150482195</v>
+        <v>0.5194229025159651</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5584112229831727</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.616916059958453</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.136045429487204</v>
+        <v>-6.04709546081784</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5116505520208698</v>
+        <v>0.5472305394886159</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5584112229831727</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.631378414339596</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.027786292364683</v>
+        <v>-5.938836323695318</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5494863273290735</v>
+        <v>0.5850663147968196</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5584112229831727</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.625910534798791</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.904495157547552</v>
+        <v>-5.815545188878187</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5963008752665031</v>
+        <v>0.6318808627342487</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4351200881660422</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.697383309699646</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.883345958644108</v>
+        <v>-5.794395989974744</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6124615330652055</v>
+        <v>0.6480415205329515</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.4139708892625988</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.717773807279037</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.639580516660664</v>
+        <v>-5.550630547991299</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7057484182056339</v>
+        <v>0.7413284056733795</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.4139708892625988</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.713554515626088</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.537817696383369</v>
+        <v>-5.448867727714005</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7485778602365678</v>
+        <v>0.7841578477043138</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4007518208701701</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.723610270581561</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.287967302434295</v>
+        <v>-5.19901733376493</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8412600927998999</v>
+        <v>0.8768400802676455</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4007518208701701</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.716352345565263</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.112075209966862</v>
+        <v>-5.023125241297498</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9152160533075215</v>
+        <v>0.9507960407752671</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4007518208701701</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.719951469085912</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.940628746944399</v>
+        <v>-4.851678778275034</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9971221445710605</v>
+        <v>1.032702132038806</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.229305357847707</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.836146852953943</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.86633918120606</v>
+        <v>-4.777389212536695</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.025858448482693</v>
+        <v>1.061438435950439</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1550157921093677</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.879741070013244</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.802703438972125</v>
+        <v>-4.713753470302761</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.056007546430584</v>
+        <v>1.09158753389833</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.09138004987543319</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.922617316407922</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.691276679646205</v>
+        <v>-4.602326710976841</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.081772508944748</v>
+        <v>1.117352496412494</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.09138004987543319</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.903811575191718</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.450846182841345</v>
+        <v>-4.36189621417198</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.179687784291569</v>
+        <v>1.215267771759315</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1490504469294271</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.049812949899511</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.37860361467015</v>
+        <v>-4.289653646000786</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.212514125394867</v>
+        <v>1.248094112862613</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1490504469294271</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.053742263734331</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.325605292388762</v>
+        <v>-4.236655323719398</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.234392038224763</v>
+        <v>1.269972025692508</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2043867059313659</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.087622603052834</v>
+        <v>3.10218458740104</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.216800406909035</v>
+        <v>-4.127850438239671</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.274912063636647</v>
+        <v>1.310492051104393</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2043867059313659</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.084620674272828</v>
+        <v>3.099182658621033</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.996779608872024</v>
+        <v>-3.90782964020266</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.364499419862065</v>
+        <v>1.400079407329811</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3456065509993462</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.17093161832423</v>
+        <v>3.185493602672435</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.84327452753995</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.863911919808746</v>
+        <v>-3.774961951139382</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.4335406782892</v>
+        <v>1.469120665756946</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3456065509993462</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.186825801126054</v>
+        <v>3.201387785474259</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.743738836444248</v>
+        <v>-3.654788867774883</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.482755756075301</v>
+        <v>1.518335743543047</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4657796343638451</v>
+        <v>0.4900496082775201</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.260075495585055</v>
+        <v>3.27463747993326</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.59906669134451</v>
+        <v>-3.510116722675146</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.550712716676636</v>
+        <v>1.586292704144382</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6104517794635825</v>
+        <v>0.6347217533772576</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.356966885206337</v>
+        <v>3.371528869554542</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.658941518702203</v>
+        <v>-3.569991550032838</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.512800277134985</v>
+        <v>1.548380264602731</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5505769521058904</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.307079480193148</v>
+        <v>3.321641464541353</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.539121287791365</v>
+        <v>-3.450171319122</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.576017538733528</v>
+        <v>1.611597526201274</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5505769521058904</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.322368649427356</v>
+        <v>3.336930633775562</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.541590994253171</v>
+        <v>-3.452641025583806</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.482673855471248</v>
+        <v>1.518253842938994</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5481072456440843</v>
+        <v>0.5723772195577592</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.228531024872714</v>
+        <v>3.243093009220919</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.609961180577181</v>
+        <v>-3.521011211907816</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.374587642426945</v>
+        <v>1.410167629894691</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5573829446802993</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.153358305779745</v>
+        <v>3.16792029012795</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.623749233424228</v>
+        <v>-3.534799264754863</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.359509129920018</v>
+        <v>1.395089117387764</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5573829446802993</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.143795014411636</v>
+        <v>3.158356998759841</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.654742392752933</v>
+        <v>-3.565792424083568</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.171821431228922</v>
+        <v>1.207401418696668</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5573829446802993</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.968504579452023</v>
+        <v>2.983066563800228</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.479268132960464</v>
+        <v>-3.390318164291099</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.246578367137698</v>
+        <v>1.282158354605444</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5573829446802993</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.97307181144381</v>
+        <v>2.987633795792016</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.590204385601712</v>
+        <v>-3.501254416932348</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.177945894842406</v>
+        <v>1.213525882310151</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5573829446802993</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.948813840205017</v>
+        <v>2.963375824553223</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111295</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.556540840129431</v>
+        <v>-3.467590871460066</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.119949626432768</v>
+        <v>1.155529613900514</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5910464901525811</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.897550280889837</v>
+        <v>2.912112265238041</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.496688220925707</v>
+        <v>-3.407738252256343</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.15406306054639</v>
+        <v>1.189643048014136</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5910464901525811</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.907722667321969</v>
+        <v>2.922284651670174</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.41044475789933</v>
+        <v>-3.321494789229965</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.183506716330801</v>
+        <v>1.219086703798547</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5910464901525811</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.902668937895829</v>
+        <v>2.917230922244034</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.45575157729831</v>
+        <v>-3.366801608628945</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.157159764015735</v>
+        <v>1.19273975148348</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5502363271433504</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.869958615534816</v>
+        <v>2.884520599883021</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.484784682000611</v>
+        <v>-3.395834713331247</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.146098395167916</v>
+        <v>1.181678382635661</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5502363271433504</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.870510488567918</v>
+        <v>2.885072472916123</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809498</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.391974200549752</v>
+        <v>-3.303024231880388</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.112495279639625</v>
+        <v>1.148075267107371</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6430468085942097</v>
+        <v>0.6673167825078846</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.855469469329799</v>
+        <v>2.870031453678004</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.43636366987918</v>
+        <v>-3.347413701209815</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.096612967832455</v>
+        <v>1.132192955300201</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.598657339264782</v>
+        <v>0.622927313178457</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.830709263656743</v>
+        <v>2.845271248004948</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472737</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.32369245164293</v>
+        <v>-3.434799851472536</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.136757163638678</v>
+        <v>1.092314203706835</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7113285575010322</v>
+        <v>0.5355411629157356</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.893387703110216</v>
+        <v>2.787915266359038</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.211315450460257</v>
+        <v>-3.322422850289864</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.187199259942414</v>
+        <v>1.142756300010571</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7113285575010322</v>
+        <v>0.5355411629157356</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.898878998940884</v>
+        <v>2.793406562189706</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.23909584836161</v>
+        <v>-3.350203248191217</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.187584302550412</v>
+        <v>1.143141342618569</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6835481595996791</v>
+        <v>0.5077607650143825</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.893707961968611</v>
+        <v>2.788235525217433</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.322097129386889</v>
+        <v>-3.433204529216496</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9927395101409535</v>
+        <v>0.9482965502091107</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6649772750725054</v>
+        <v>0.4891898804872088</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.72092115125296</v>
+        <v>2.615448714501782</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.68271631072927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.43071120783022</v>
+        <v>-3.541818607659827</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.069443539482827</v>
+        <v>1.025000579550984</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6649772750725054</v>
+        <v>0.4891898804872088</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.841070811972165</v>
+        <v>2.735598375220988</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.395302169582077</v>
+        <v>-3.506409569411684</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.098120180884407</v>
+        <v>1.053677220952564</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6649772750725054</v>
+        <v>0.4891898804872088</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.855583838074488</v>
+        <v>2.750111401323311</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.356918507023926</v>
+        <v>-3.468025906853533</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.110893087250036</v>
+        <v>1.066450127318193</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7033609376306565</v>
+        <v>0.52757354304536</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.876033476951748</v>
+        <v>2.77056104020057</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.17980217698876</v>
+        <v>-3.290909576818367</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.178468648109404</v>
+        <v>1.134025688177561</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7033609376306565</v>
+        <v>0.52757354304536</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.87276250579705</v>
+        <v>2.767290069045872</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.224894421822306</v>
+        <v>-3.336001821651912</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.161115141937899</v>
+        <v>1.116672182006057</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6414648944612668</v>
+        <v>0.4656774998759702</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.836308271657329</v>
+        <v>2.730835834906151</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.045519000583538</v>
+        <v>-3.156626400413145</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.226652285739821</v>
+        <v>1.182209325807978</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.7982416526319854</v>
+        <v>0.6224542580466889</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.924161301866175</v>
+        <v>2.818688865114996</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.090533214104144</v>
+        <v>-3.201640613933751</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.189454055663168</v>
+        <v>1.145011095731325</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7678927573173808</v>
+        <v>0.5921053627320843</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.886759420009001</v>
+        <v>2.781286983257824</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.35753772437658</v>
+        <v>-3.468645124206186</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.088343813893139</v>
+        <v>1.043900853961297</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5735297192744322</v>
+        <v>0.3977423246891357</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.775833159522178</v>
+        <v>2.670360722771</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.70230945476081</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.458735505813753</v>
+        <v>-3.569842905643359</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.047068623214772</v>
+        <v>1.002625663282929</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5051209057291131</v>
+        <v>0.3293335111438165</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.733991793291488</v>
+        <v>2.62851935654031</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.45222453919944</v>
+        <v>-3.563331939029046</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.047272971414813</v>
+        <v>1.002830011482971</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5051209057291131</v>
+        <v>0.3293335111438165</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.731591754845805</v>
+        <v>2.626119318094627</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.433186411492143</v>
+        <v>-3.544293811321749</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.051412941705977</v>
+        <v>1.006969981774135</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4469372943979185</v>
+        <v>0.2711498998126219</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.693206307255333</v>
+        <v>2.587733870504155</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.553515657498219</v>
+        <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.464313042642761</v>
+        <v>-3.575420442472367</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.167434016127367</v>
+        <v>1.172101198252568</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4469372943979185</v>
+        <v>0.2711498998126219</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.82167803413697</v>
+        <v>2.765315739442836</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.554348986484352</v>
+        <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.478179803976678</v>
+        <v>-3.589287203806284</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.162720640579934</v>
+        <v>1.167387822705135</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4090793776640956</v>
+        <v>0.233291983078799</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.79979661308281</v>
+        <v>2.743434318388676</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789124</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.560357516881278</v>
+        <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.433375632436748</v>
+        <v>-3.544483032266355</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.186650839592831</v>
+        <v>1.191318021718033</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4090793776640956</v>
+        <v>0.233291983078799</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.805805143479736</v>
+        <v>2.749442848785602</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.458307738158477</v>
+        <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.285632662201746</v>
+        <v>-3.396740062031352</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.143698248964032</v>
+        <v>1.148365431089233</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5768867348989788</v>
+        <v>0.4010993403136822</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.804439779097865</v>
+        <v>2.748077484403731</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.461101359689958</v>
+        <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.387647344732967</v>
+        <v>-3.498754744562573</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.105685997483024</v>
+        <v>1.110353179608226</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5768867348989788</v>
+        <v>0.4010993403136822</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.807233400629346</v>
+        <v>2.750871105935212</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.461763708081617</v>
+        <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.381494638680183</v>
+        <v>-3.492602038509789</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.108809428295797</v>
+        <v>1.113476610420998</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5830394409517631</v>
+        <v>0.4072520463664664</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.811587372652675</v>
+        <v>2.755225077958541</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.460844184821727</v>
+        <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.398303936830684</v>
+        <v>-3.50941133666029</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.101166185775706</v>
+        <v>1.105833367900907</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5662301428012615</v>
+        <v>0.3904427482159648</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.800582270502484</v>
+        <v>2.74421997580835</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.527179738618548</v>
+        <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.336005938054562</v>
+        <v>-3.447113337884169</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.192420939082976</v>
+        <v>1.197088121208177</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5662301428012615</v>
+        <v>0.4357370124904069</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.866917824299305</v>
+        <v>2.837732088169836</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.329471740332675</v>
+        <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.134215740389404</v>
+        <v>-3.245323140219011</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.075429019863166</v>
+        <v>1.080096201988367</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7642483349704159</v>
+        <v>0.6337552046595613</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.788020741314925</v>
+        <v>2.758835005185456</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852424</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.39976197265485</v>
+        <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.969402737310557</v>
+        <v>-3.080510137140164</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.21164445341688</v>
+        <v>1.216311635542081</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9290613380492628</v>
+        <v>0.7985682077384082</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.957198775484408</v>
+        <v>2.928013039354939</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319543</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.414389708770894</v>
+        <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.067143281935532</v>
+        <v>-3.178250681765138</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.187175971682934</v>
+        <v>1.191843153808135</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9131720599162827</v>
+        <v>0.782678929605428</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.962292944720664</v>
+        <v>2.933107208591195</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.412925689595566</v>
+        <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.243481042058461</v>
+        <v>-3.354588441888067</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.115176848458434</v>
+        <v>1.119844030583635</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7368342997933532</v>
+        <v>0.6063411694824985</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.855026269471578</v>
+        <v>2.825840533342109</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.411417307635494</v>
+        <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.167058995626534</v>
+        <v>-3.27816639545614</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.144237285071133</v>
+        <v>1.148904467196334</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7368342997933532</v>
+        <v>0.6063411694824985</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.853517887511506</v>
+        <v>2.824332151382037</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316247</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.41128017507093</v>
+        <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.122685863987965</v>
+        <v>-3.233793263817572</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.161849405161997</v>
+        <v>1.166516587287198</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7812074314319218</v>
+        <v>0.6507143011210671</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.880004633930084</v>
+        <v>2.850818897800615</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.405673969209521</v>
+        <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.999851643100798</v>
+        <v>-3.110959042930404</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.205376887655454</v>
+        <v>1.210044069780655</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7812074314319218</v>
+        <v>0.6507143011210671</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.874398428068674</v>
+        <v>2.845212691939205</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190322</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.412055726237325</v>
+        <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.952195912539742</v>
+        <v>-3.063303312369348</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.230820936907681</v>
+        <v>1.235488119032882</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8288631619929775</v>
+        <v>0.6983700316821227</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.909373623433112</v>
+        <v>2.880187887303643</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569615</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.41694809961205</v>
+        <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.851677754040987</v>
+        <v>-2.962785153870594</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.275920573681908</v>
+        <v>1.280587755807109</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9293813204917321</v>
+        <v>0.7988881901808773</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.974576891907089</v>
+        <v>2.94539115577762</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.82880887755729</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.403702772087922</v>
+        <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.912344344443377</v>
+        <v>-3.023451744272983</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.238408609996824</v>
+        <v>1.243075792122026</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8476830037731984</v>
+        <v>0.7171898734623436</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.912312574351841</v>
+        <v>2.883126838222373</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932765</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.407800474698551</v>
+        <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.867505942834979</v>
+        <v>-2.978613342664585</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.260441673250812</v>
+        <v>1.265108855376013</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8522264367180679</v>
+        <v>0.7217333064072131</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.919136336729391</v>
+        <v>2.889950600599923</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.411961414329629</v>
+        <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.968264578591977</v>
+        <v>-3.079371978421583</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.224299158579091</v>
+        <v>1.228966340704292</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7634008679910624</v>
+        <v>0.6329077376802077</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.870001935124266</v>
+        <v>2.840816198994798</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405957</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.417841016857466</v>
+        <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.924061741506077</v>
+        <v>-3.035169141335683</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.247859895941288</v>
+        <v>1.252527078066489</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8076037050769629</v>
+        <v>0.6771105747661081</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.902403239903644</v>
+        <v>2.873217503774175</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.416251017326713</v>
+        <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.96104076916952</v>
+        <v>-3.072148168999126</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.231478285345158</v>
+        <v>1.23614546747036</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8445776068682934</v>
+        <v>0.7140844765574387</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.92299758144769</v>
+        <v>2.893811845318221</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.467498782509753</v>
+        <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.802749351630248</v>
+        <v>-2.913856751459854</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.346042617543907</v>
+        <v>1.350709799669108</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8445776068682934</v>
+        <v>0.7140844765574387</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.974245346630729</v>
+        <v>2.945059610501261</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321019</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.465939487104006</v>
+        <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.595107347995771</v>
+        <v>-2.706214747825378</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.42754012359195</v>
+        <v>1.432207305717152</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.05221961050277</v>
+        <v>0.9217264801919148</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.097271253405668</v>
+        <v>3.0680855172762</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475135</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.460887715342276</v>
+        <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.544075255273243</v>
+        <v>-2.65518265510285</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.442901188919232</v>
+        <v>1.447568371044433</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.103251703225298</v>
+        <v>0.9727585729144428</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.122838737277455</v>
+        <v>3.093653001147986</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.84254736040485</v>
+        <v>3.842547360404852</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.478075119434981</v>
+        <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.478851074146037</v>
+        <v>-2.589958473975644</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.486178265462819</v>
+        <v>1.49084544758802</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.168475884352503</v>
+        <v>1.037982754041648</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.179160650046483</v>
+        <v>3.149974913917014</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882554</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.474036091734261</v>
+        <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.441424054074904</v>
+        <v>-2.55253145390451</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.497110045790553</v>
+        <v>1.501777227915754</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.173727422381685</v>
+        <v>1.04323429207083</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.178272545163273</v>
+        <v>3.149086809033804</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992657</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.475292884065502</v>
+        <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.461535710109612</v>
+        <v>-2.572643109939218</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.49032217570791</v>
+        <v>1.494989357833111</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.184754767379104</v>
+        <v>1.054261637068249</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.186145744492965</v>
+        <v>3.156960008363496</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636284</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.635850655086712</v>
+        <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.407790895682407</v>
+        <v>-2.518898295512014</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.672377872500002</v>
+        <v>1.677045054625204</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.194818076819566</v>
+        <v>1.064324946508711</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.352741501178452</v>
+        <v>3.323555765048984</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957622</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.75596356430453</v>
+        <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.333008634657395</v>
+        <v>-2.444116034487001</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.822403686127825</v>
+        <v>1.827070868253026</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.269600337844579</v>
+        <v>1.139107207533724</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.517723767011277</v>
+        <v>3.488538030881808</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.747671540318389</v>
+        <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.306924550393587</v>
+        <v>-2.418031950223193</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.824545295847207</v>
+        <v>1.829212477972408</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.269600337844579</v>
+        <v>1.139107207533724</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.509431743025136</v>
+        <v>3.480246006895667</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896925</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.745864735902168</v>
+        <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.22879336954464</v>
+        <v>-2.339900769374246</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.853990963770565</v>
+        <v>1.858658145895767</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.343777148728264</v>
+        <v>1.213284018417409</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.552131025139126</v>
+        <v>3.522945289009658</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959854</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.76341914162896</v>
+        <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.219900908151357</v>
+        <v>-2.331008307980963</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.87510235405467</v>
+        <v>1.879769536179871</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.343777148728264</v>
+        <v>1.213284018417409</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.569685430865918</v>
+        <v>3.540499694736449</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945364</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.755274189033543</v>
+        <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.388377025121235</v>
+        <v>-2.499484424950841</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.799566954671302</v>
+        <v>1.804234136796504</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.315829313011683</v>
+        <v>1.185336182700828</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.544771776840554</v>
+        <v>3.515586040711085</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782705</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.736543886221405</v>
+        <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.690577496259651</v>
+        <v>-1.801684896089258</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.059956463403798</v>
+        <v>2.064623645528999</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.245481253641272</v>
+        <v>1.114988123330417</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.483832638406169</v>
+        <v>3.4546469022767</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632633</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.72720790871831</v>
+        <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.667856392576499</v>
+        <v>-1.778963792406105</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.059708927373963</v>
+        <v>2.064376109499165</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.245481253641272</v>
+        <v>1.114988123330417</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.474496660903073</v>
+        <v>3.445310924773604</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.78320569677767</v>
+        <v>3.783205696777671</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.886114034569479</v>
+        <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.666131349286455</v>
+        <v>-1.777238749116062</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.21930507054115</v>
+        <v>2.223972252666351</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.247206296931316</v>
+        <v>1.116713166620461</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.634437812728269</v>
+        <v>3.6052520765988</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644409</v>
+        <v>3.77993372564441</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.923191857063125</v>
+        <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.82091235606471</v>
+        <v>-1.932019755894317</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.194470490323494</v>
+        <v>2.199137672448696</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.21383862287684</v>
+        <v>1.083345492565985</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.65149503078923</v>
+        <v>3.622309294659761</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.919867213052671</v>
+        <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.813857665849537</v>
+        <v>-1.924965065679143</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.193967722399109</v>
+        <v>2.19863490452431</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.220893313092014</v>
+        <v>1.090400182781159</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.652403200907879</v>
+        <v>3.62321746477841</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331114</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.929873366697412</v>
+        <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.786906441523049</v>
+        <v>-1.898013841352655</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.214754365774446</v>
+        <v>2.219421547899647</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.235773659119733</v>
+        <v>1.105280528808878</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.671337562169252</v>
+        <v>3.642151826039783</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784105</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.113976498842372</v>
+        <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.922859449579365</v>
+        <v>-2.033966849408971</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.344476294696879</v>
+        <v>2.34914347682208</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.235773659119733</v>
+        <v>1.105280528808878</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.855440694314212</v>
+        <v>3.826254958184743</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714423</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.106093193745365</v>
+        <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.945267567384237</v>
+        <v>-2.056374967213843</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.327629742477923</v>
+        <v>2.332296924603125</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.235773659119733</v>
+        <v>1.105280528808878</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.847557389217205</v>
+        <v>3.818371653087736</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155029</v>
+        <v>3.71911862715503</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.108147193295002</v>
+        <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.093273334863636</v>
+        <v>-2.204380734693243</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.2704814350358</v>
+        <v>2.275148617161002</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.149046650256191</v>
+        <v>1.018553519945336</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.797575183448718</v>
+        <v>3.768389447319249</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161974</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.16440091101685</v>
+        <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.102714260752166</v>
+        <v>-2.213821660581773</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.322958782402236</v>
+        <v>2.327625964527437</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.271473767799583</v>
+        <v>1.140980637488728</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.9272851716966</v>
+        <v>3.898099435567131</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321631</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.167292005562151</v>
+        <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.154987868087808</v>
+        <v>-2.266095267917414</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.30494043401328</v>
+        <v>2.309607616138482</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.219200160463942</v>
+        <v>1.088707030153087</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.898812101840516</v>
+        <v>3.869626365711047</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.7278981863477</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.165403818455926</v>
+        <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.231317845688713</v>
+        <v>-2.34242524551832</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.272520255866693</v>
+        <v>2.277187437991895</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.219200160463942</v>
+        <v>1.088707030153087</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.896923914734291</v>
+        <v>3.867738178604822</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887744</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.160224048058788</v>
+        <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.343074798304015</v>
+        <v>-2.454182198133621</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.222637704423435</v>
+        <v>2.227304886548636</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.10744320784864</v>
+        <v>0.9769500775377855</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.824689972767973</v>
+        <v>3.795504236638504</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343061</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.15865805826894</v>
+        <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.341233779245763</v>
+        <v>-2.45234117907537</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.221808122256888</v>
+        <v>2.226475304382089</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.108711434520109</v>
+        <v>0.9782183042092539</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.823884918981006</v>
+        <v>3.794699182851537</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647101</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.171731465134859</v>
+        <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.473535071343317</v>
+        <v>-2.584642471172923</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.181961012283785</v>
+        <v>2.186628194408986</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.108711434520109</v>
+        <v>0.9782183042092539</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.836958325846925</v>
+        <v>3.807772589717456</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763528</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.171731465134859</v>
+        <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.475096714158177</v>
+        <v>-2.586204113987783</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.181336355157841</v>
+        <v>2.186003537283042</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.108711434520109</v>
+        <v>0.9782183042092539</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.836958325846925</v>
+        <v>3.807772589717456</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392111</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.170255506261861</v>
+        <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.50299750126765</v>
+        <v>-2.614104901097256</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.168700081441054</v>
+        <v>2.173367263566255</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.074114510377174</v>
+        <v>0.9436213800663191</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.814724212488166</v>
+        <v>3.785538476358697</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172522</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.16701995023906</v>
+        <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.625523603970544</v>
+        <v>-2.73663100380015</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.116454084337095</v>
+        <v>2.121121266462296</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9515884076742802</v>
+        <v>0.8210952773634252</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.737972994843628</v>
+        <v>3.708787258714159</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971074</v>
+        <v>3.619362241971075</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.233725909829563</v>
+        <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.64558492524705</v>
+        <v>-2.756692325076657</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.175135515416996</v>
+        <v>2.179802697542198</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.9315270863977732</v>
+        <v>0.8010339560869182</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.792642161668228</v>
+        <v>3.763456425538759</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199801</v>
+        <v>3.640764248199803</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.37403762883141</v>
+        <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.902305743241874</v>
+        <v>-3.013413143071481</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.212758907220914</v>
+        <v>2.217426089346115</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8231125122539583</v>
+        <v>0.6926193819431034</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.867905136183786</v>
+        <v>3.838719400054317</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622232</v>
+        <v>3.668303164622234</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.44301789797705</v>
+        <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.056292161018015</v>
+        <v>-3.167399560847621</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.220144609256097</v>
+        <v>2.224811791381299</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8231125122539583</v>
+        <v>0.6926193819431034</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.936885405329425</v>
+        <v>3.907699669199957</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808524</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.429069100097171</v>
+        <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.005770257190349</v>
+        <v>-3.116877657019955</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.226404572907284</v>
+        <v>2.231071755032486</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8231125122539583</v>
+        <v>0.6926193819431034</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.922936607449547</v>
+        <v>3.893750871320078</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994889</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.440939589152585</v>
+        <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.258245411198073</v>
+        <v>-3.36935281102768</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.137285000359609</v>
+        <v>2.14195218248481</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8231125122539583</v>
+        <v>0.6926193819431034</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.934807096504961</v>
+        <v>3.905621360375492</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358293</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.442150123671529</v>
+        <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.527718213119782</v>
+        <v>-3.638825612949388</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.030706414109869</v>
+        <v>2.035373596235071</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8231125122539583</v>
+        <v>0.6926193819431034</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.936017631023904</v>
+        <v>3.906831894894435</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637082</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.44627186589885</v>
+        <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.685262284849223</v>
+        <v>-3.796369684678829</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.971810527645414</v>
+        <v>1.976477709770616</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.7562107071136839</v>
+        <v>0.6257175768028289</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.899998290167061</v>
+        <v>3.870812554037592</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301338</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.44134971863504</v>
+        <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.814112835551269</v>
+        <v>-3.925220235380876</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.915348160100785</v>
+        <v>1.920015342225986</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7152172982629623</v>
+        <v>0.5847241679521074</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.870480097592818</v>
+        <v>3.841294361463349</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215465</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.603553775334084</v>
+        <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.93108052819016</v>
+        <v>-4.042187928019767</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.030765139744273</v>
+        <v>2.035432321869474</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7152172982629623</v>
+        <v>0.5847241679521074</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.032684154291862</v>
+        <v>4.003498418162392</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456687</v>
+        <v>3.69655362845669</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.598400413297898</v>
+        <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.015798470411114</v>
+        <v>-4.12690587024072</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.991724600819705</v>
+        <v>1.996391782944907</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6301012693349159</v>
+        <v>0.499608139024061</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.976461174898848</v>
+        <v>3.947275438769379</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253283</v>
+        <v>3.750058176253286</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.608629830866389</v>
+        <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.097733288679997</v>
+        <v>-4.208840688509603</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.969180091080643</v>
+        <v>1.973847273205845</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6201665237478358</v>
+        <v>0.4896733934369808</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.980729745115091</v>
+        <v>3.951544008985622</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717827</v>
+        <v>3.78364702771783</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.617555469322292</v>
+        <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.043995115279735</v>
+        <v>-4.155102515109341</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.99960099889665</v>
+        <v>2.004268181021852</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.6739046971480979</v>
+        <v>0.5434115668372429</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.02189828761115</v>
+        <v>3.992712551481682</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616944</v>
+        <v>3.798310944616946</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.609708356566467</v>
+        <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.933988831802513</v>
+        <v>-4.04509623163212</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.035756399531715</v>
+        <v>2.040423581656916</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.6971092690653731</v>
+        <v>0.5666161387545181</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.027973918005691</v>
+        <v>3.998788181876222</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203658</v>
+        <v>3.78557808520366</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.613958367288441</v>
+        <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.790929256061588</v>
+        <v>-3.902036655891194</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.097230240550059</v>
+        <v>2.10189742267526</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7051226956553523</v>
+        <v>0.5746295653444974</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.037031984681652</v>
+        <v>4.007846248552184</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777251572436924</v>
+        <v>3.777251572436927</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.621219250170977</v>
+        <v>3.670329392228021</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.489482530589751</v>
+        <v>-3.600589930419357</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.22506981362133</v>
+        <v>2.229736995746531</v>
       </c>
       <c r="F2029" t="n">
-        <v>1.00656942112719</v>
+        <v>0.8760762908163346</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.225160902847291</v>
+        <v>4.195975166717822</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.840500396882913</v>
+        <v>3.426025089541242</v>
       </c>
       <c r="C2030" t="n">
-        <v>3.622190427923688</v>
+        <v>3.671300569980732</v>
       </c>
       <c r="D2030" t="n">
-        <v>-3.538860961258333</v>
+        <v>-3.412663597523644</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.206289619106607</v>
+        <v>2.305878706657527</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.9571909904586066</v>
+        <v>0.8747632020884017</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.196505022198852</v>
+        <v>4.196158491233773</v>
       </c>
     </row>
   </sheetData>
